--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N176"/>
+  <dimension ref="A1:N180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4069,40 +4069,40 @@
         <v>305</v>
       </c>
       <c r="B83" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C83" t="n">
         <v>305</v>
       </c>
       <c r="D83" t="n">
-        <v>86.15287970112803</v>
+        <v>85.96689449914007</v>
       </c>
       <c r="E83" t="n">
-        <v>447.95</v>
+        <v>446.065</v>
       </c>
       <c r="F83" t="n">
-        <v>164.4192257473755</v>
+        <v>165.1140353391027</v>
       </c>
       <c r="G83" t="n">
-        <v>34759.1428788493</v>
+        <v>35182.595902612</v>
       </c>
       <c r="H83" t="n">
-        <v>-8540.368589083148</v>
+        <v>-8422.060199215268</v>
       </c>
       <c r="I83" t="n">
-        <v>4.965</v>
+        <v>4.795</v>
       </c>
       <c r="J83" t="n">
-        <v>10.525</v>
+        <v>10.265</v>
       </c>
       <c r="K83" t="n">
-        <v>1.77</v>
+        <v>1.685</v>
       </c>
       <c r="L83" t="n">
-        <v>2.625</v>
+        <v>2.47</v>
       </c>
       <c r="M83" t="n">
-        <v>208.1278673001732</v>
+        <v>300.0734614592056</v>
       </c>
       <c r="N83" t="n">
         <v>7.24261145101418</v>
@@ -4113,43 +4113,43 @@
         <v>305</v>
       </c>
       <c r="B84" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" t="n">
         <v>305</v>
       </c>
       <c r="D84" t="n">
-        <v>85.74857125932778</v>
+        <v>86.15287970112803</v>
       </c>
       <c r="E84" t="n">
-        <v>442.48</v>
+        <v>447.95</v>
       </c>
       <c r="F84" t="n">
-        <v>166.4517993435565</v>
+        <v>164.4192257473755</v>
       </c>
       <c r="G84" t="n">
-        <v>36168.03387750834</v>
+        <v>34759.1428788493</v>
       </c>
       <c r="H84" t="n">
-        <v>-8867.970665994213</v>
+        <v>-8540.368589083148</v>
       </c>
       <c r="I84" t="n">
-        <v>4.7</v>
+        <v>4.965</v>
       </c>
       <c r="J84" t="n">
-        <v>10.045</v>
+        <v>10.525</v>
       </c>
       <c r="K84" t="n">
-        <v>1.595</v>
+        <v>1.77</v>
       </c>
       <c r="L84" t="n">
-        <v>2.375</v>
+        <v>2.625</v>
       </c>
       <c r="M84" t="n">
-        <v>300.0734631925171</v>
+        <v>208.1278673001732</v>
       </c>
       <c r="N84" t="n">
-        <v>7.242643590519569</v>
+        <v>7.24261145101418</v>
       </c>
     </row>
     <row r="85">
@@ -4157,40 +4157,40 @@
         <v>305</v>
       </c>
       <c r="B85" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C85" t="n">
         <v>305</v>
       </c>
       <c r="D85" t="n">
-        <v>85.53276250155793</v>
+        <v>85.74857125932778</v>
       </c>
       <c r="E85" t="n">
-        <v>444.64</v>
+        <v>442.48</v>
       </c>
       <c r="F85" t="n">
-        <v>165.6431993827295</v>
+        <v>166.4517993435565</v>
       </c>
       <c r="G85" t="n">
-        <v>36725.2777434966</v>
+        <v>36168.03387750834</v>
       </c>
       <c r="H85" t="n">
-        <v>-8778.845410104459</v>
+        <v>-8867.970665994213</v>
       </c>
       <c r="I85" t="n">
-        <v>4.815</v>
+        <v>4.7</v>
       </c>
       <c r="J85" t="n">
-        <v>10.25</v>
+        <v>10.045</v>
       </c>
       <c r="K85" t="n">
-        <v>1.685</v>
+        <v>1.595</v>
       </c>
       <c r="L85" t="n">
-        <v>2.47</v>
+        <v>2.375</v>
       </c>
       <c r="M85" t="n">
-        <v>300.0734621616424</v>
+        <v>300.0734631925171</v>
       </c>
       <c r="N85" t="n">
         <v>7.242643590519569</v>
@@ -4201,40 +4201,40 @@
         <v>305</v>
       </c>
       <c r="B86" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C86" t="n">
         <v>305</v>
       </c>
       <c r="D86" t="n">
-        <v>85.69196635613324</v>
+        <v>85.53276250155793</v>
       </c>
       <c r="E86" t="n">
-        <v>446.115</v>
+        <v>444.64</v>
       </c>
       <c r="F86" t="n">
-        <v>165.0955295686916</v>
+        <v>165.6431993827295</v>
       </c>
       <c r="G86" t="n">
-        <v>36257.7097875395</v>
+        <v>36725.2777434966</v>
       </c>
       <c r="H86" t="n">
-        <v>-8762.056793761083</v>
+        <v>-8778.845410104459</v>
       </c>
       <c r="I86" t="n">
-        <v>4.985</v>
+        <v>4.815</v>
       </c>
       <c r="J86" t="n">
-        <v>10.515</v>
+        <v>10.25</v>
       </c>
       <c r="K86" t="n">
-        <v>1.77</v>
+        <v>1.685</v>
       </c>
       <c r="L86" t="n">
-        <v>2.625</v>
+        <v>2.47</v>
       </c>
       <c r="M86" t="n">
-        <v>208.1450480610657</v>
+        <v>300.0734621616424</v>
       </c>
       <c r="N86" t="n">
         <v>7.242643590519569</v>
@@ -4245,43 +4245,43 @@
         <v>305</v>
       </c>
       <c r="B87" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C87" t="n">
         <v>305</v>
       </c>
       <c r="D87" t="n">
-        <v>85.29523023885534</v>
+        <v>85.69196635613324</v>
       </c>
       <c r="E87" t="n">
-        <v>441.75</v>
+        <v>446.115</v>
       </c>
       <c r="F87" t="n">
-        <v>166.7268640034791</v>
+        <v>165.0955295686916</v>
       </c>
       <c r="G87" t="n">
-        <v>37685.60944579857</v>
+        <v>36257.7097875395</v>
       </c>
       <c r="H87" t="n">
-        <v>-9141.146218132371</v>
+        <v>-8762.056793761083</v>
       </c>
       <c r="I87" t="n">
-        <v>4.72</v>
+        <v>4.985</v>
       </c>
       <c r="J87" t="n">
-        <v>10.05</v>
+        <v>10.515</v>
       </c>
       <c r="K87" t="n">
-        <v>1.595</v>
+        <v>1.77</v>
       </c>
       <c r="L87" t="n">
-        <v>2.37</v>
+        <v>2.625</v>
       </c>
       <c r="M87" t="n">
-        <v>300.0734627988316</v>
+        <v>208.1450480610657</v>
       </c>
       <c r="N87" t="n">
-        <v>7.24266892208129</v>
+        <v>7.242643590519569</v>
       </c>
     </row>
     <row r="88">
@@ -4289,40 +4289,40 @@
         <v>305</v>
       </c>
       <c r="B88" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C88" t="n">
         <v>305</v>
       </c>
       <c r="D88" t="n">
-        <v>84.97502641234331</v>
+        <v>85.29523023885534</v>
       </c>
       <c r="E88" t="n">
-        <v>443.23</v>
+        <v>441.75</v>
       </c>
       <c r="F88" t="n">
-        <v>166.1701423043044</v>
+        <v>166.7268640034791</v>
       </c>
       <c r="G88" t="n">
-        <v>38509.76874060684</v>
+        <v>37685.60944579857</v>
       </c>
       <c r="H88" t="n">
-        <v>-9024.780589164946</v>
+        <v>-9141.146218132371</v>
       </c>
       <c r="I88" t="n">
-        <v>4.83</v>
+        <v>4.72</v>
       </c>
       <c r="J88" t="n">
-        <v>10.255</v>
+        <v>10.05</v>
       </c>
       <c r="K88" t="n">
-        <v>1.68</v>
+        <v>1.595</v>
       </c>
       <c r="L88" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="M88" t="n">
-        <v>300.0734632642283</v>
+        <v>300.0734627988316</v>
       </c>
       <c r="N88" t="n">
         <v>7.24266892208129</v>
@@ -4333,40 +4333,40 @@
         <v>305</v>
       </c>
       <c r="B89" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C89" t="n">
         <v>305</v>
       </c>
       <c r="D89" t="n">
-        <v>85.17020859058194</v>
+        <v>84.97502641234331</v>
       </c>
       <c r="E89" t="n">
-        <v>444.31</v>
+        <v>443.23</v>
       </c>
       <c r="F89" t="n">
-        <v>165.7662266740269</v>
+        <v>166.1701423043044</v>
       </c>
       <c r="G89" t="n">
-        <v>38031.88441025994</v>
+        <v>38509.76874060684</v>
       </c>
       <c r="H89" t="n">
-        <v>-9109.297236292861</v>
+        <v>-9024.780589164946</v>
       </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="J89" t="n">
-        <v>10.52</v>
+        <v>10.255</v>
       </c>
       <c r="K89" t="n">
-        <v>1.775</v>
+        <v>1.68</v>
       </c>
       <c r="L89" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="M89" t="n">
-        <v>208.1627949573518</v>
+        <v>300.0734632642283</v>
       </c>
       <c r="N89" t="n">
         <v>7.24266892208129</v>
@@ -4374,46 +4374,46 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B90" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C90" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D90" t="n">
-        <v>93.51406360085934</v>
+        <v>85.17020859058194</v>
       </c>
       <c r="E90" t="n">
-        <v>478.61</v>
+        <v>444.31</v>
       </c>
       <c r="F90" t="n">
-        <v>153.8864465296105</v>
+        <v>165.7662266740269</v>
       </c>
       <c r="G90" t="n">
-        <v>6153.111703682009</v>
+        <v>38031.88441025994</v>
       </c>
       <c r="H90" t="n">
-        <v>-1492.863309931552</v>
+        <v>-9109.297236292861</v>
       </c>
       <c r="I90" t="n">
-        <v>5.72</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
-        <v>16.6</v>
+        <v>10.52</v>
       </c>
       <c r="K90" t="n">
-        <v>2.550000000000001</v>
+        <v>1.775</v>
       </c>
       <c r="L90" t="n">
-        <v>3.620000000000001</v>
+        <v>2.63</v>
       </c>
       <c r="M90" t="n">
-        <v>276.6878172939188</v>
+        <v>208.1627949573518</v>
       </c>
       <c r="N90" t="n">
-        <v>5.259746042528284</v>
+        <v>7.24266892208129</v>
       </c>
     </row>
     <row r="91">
@@ -4421,40 +4421,40 @@
         <v>307</v>
       </c>
       <c r="B91" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C91" t="n">
         <v>307</v>
       </c>
       <c r="D91" t="n">
-        <v>93.46072563038759</v>
+        <v>93.51406360085934</v>
       </c>
       <c r="E91" t="n">
-        <v>482.945</v>
+        <v>478.61</v>
       </c>
       <c r="F91" t="n">
-        <v>152.5051344843344</v>
+        <v>153.8864465296105</v>
       </c>
       <c r="G91" t="n">
-        <v>6272.605052490439</v>
+        <v>6153.111703682009</v>
       </c>
       <c r="H91" t="n">
-        <v>-1444.424203516434</v>
+        <v>-1492.863309931552</v>
       </c>
       <c r="I91" t="n">
-        <v>5.955</v>
+        <v>5.72</v>
       </c>
       <c r="J91" t="n">
-        <v>17.06</v>
+        <v>16.6</v>
       </c>
       <c r="K91" t="n">
-        <v>2.654999999999999</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="L91" t="n">
-        <v>3.835</v>
+        <v>3.620000000000001</v>
       </c>
       <c r="M91" t="n">
-        <v>252.5095289898121</v>
+        <v>276.6878172939188</v>
       </c>
       <c r="N91" t="n">
         <v>5.259746042528284</v>
@@ -4465,40 +4465,40 @@
         <v>307</v>
       </c>
       <c r="B92" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C92" t="n">
         <v>307</v>
       </c>
       <c r="D92" t="n">
-        <v>93.42556059685845</v>
+        <v>93.46072563038759</v>
       </c>
       <c r="E92" t="n">
-        <v>486.395</v>
+        <v>482.945</v>
       </c>
       <c r="F92" t="n">
-        <v>151.4234154823484</v>
+        <v>152.5051344843344</v>
       </c>
       <c r="G92" t="n">
-        <v>6355.202896443663</v>
+        <v>6272.605052490439</v>
       </c>
       <c r="H92" t="n">
-        <v>-1416.35211739665</v>
+        <v>-1444.424203516434</v>
       </c>
       <c r="I92" t="n">
-        <v>6.21</v>
+        <v>5.955</v>
       </c>
       <c r="J92" t="n">
-        <v>17.53</v>
+        <v>17.06</v>
       </c>
       <c r="K92" t="n">
-        <v>2.75</v>
+        <v>2.654999999999999</v>
       </c>
       <c r="L92" t="n">
-        <v>4.02</v>
+        <v>3.835</v>
       </c>
       <c r="M92" t="n">
-        <v>217.611783644889</v>
+        <v>252.5095289898121</v>
       </c>
       <c r="N92" t="n">
         <v>5.259746042528284</v>
@@ -4509,43 +4509,43 @@
         <v>307</v>
       </c>
       <c r="B93" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C93" t="n">
         <v>307</v>
       </c>
       <c r="D93" t="n">
-        <v>93.43566194116374</v>
+        <v>93.42556059685845</v>
       </c>
       <c r="E93" t="n">
-        <v>472.575</v>
+        <v>486.395</v>
       </c>
       <c r="F93" t="n">
-        <v>155.8516471957612</v>
+        <v>151.4234154823484</v>
       </c>
       <c r="G93" t="n">
-        <v>6621.745409759462</v>
+        <v>6355.202896443663</v>
       </c>
       <c r="H93" t="n">
-        <v>-1721.777563608836</v>
+        <v>-1416.35211739665</v>
       </c>
       <c r="I93" t="n">
-        <v>5.73</v>
+        <v>6.21</v>
       </c>
       <c r="J93" t="n">
-        <v>15.35</v>
+        <v>17.53</v>
       </c>
       <c r="K93" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="L93" t="n">
-        <v>3.485</v>
+        <v>4.02</v>
       </c>
       <c r="M93" t="n">
-        <v>286.5115313664276</v>
+        <v>217.611783644889</v>
       </c>
       <c r="N93" t="n">
-        <v>5.259798202048205</v>
+        <v>5.259746042528284</v>
       </c>
     </row>
     <row r="94">
@@ -4553,43 +4553,43 @@
         <v>307</v>
       </c>
       <c r="B94" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C94" t="n">
         <v>307</v>
       </c>
       <c r="D94" t="n">
-        <v>93.37423222341569</v>
+        <v>93.46843332897606</v>
       </c>
       <c r="E94" t="n">
-        <v>476.835</v>
+        <v>476.365</v>
       </c>
       <c r="F94" t="n">
-        <v>154.4592829249884</v>
+        <v>154.6116783842996</v>
       </c>
       <c r="G94" t="n">
-        <v>6757.198730392972</v>
+        <v>6405.248870609407</v>
       </c>
       <c r="H94" t="n">
-        <v>-1663.892522353884</v>
+        <v>-1604.841963370349</v>
       </c>
       <c r="I94" t="n">
-        <v>5.92</v>
+        <v>5.725000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>15.76</v>
+        <v>15.92</v>
       </c>
       <c r="K94" t="n">
-        <v>2.505</v>
+        <v>2.47</v>
       </c>
       <c r="L94" t="n">
-        <v>3.649999999999999</v>
+        <v>3.54</v>
       </c>
       <c r="M94" t="n">
-        <v>252.6008943792451</v>
+        <v>281.683010309403</v>
       </c>
       <c r="N94" t="n">
-        <v>5.259798202048205</v>
+        <v>5.259773801395505</v>
       </c>
     </row>
     <row r="95">
@@ -4597,219 +4597,219 @@
         <v>307</v>
       </c>
       <c r="B95" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C95" t="n">
         <v>307</v>
       </c>
       <c r="D95" t="n">
-        <v>93.34673725956608</v>
+        <v>93.41632642975102</v>
       </c>
       <c r="E95" t="n">
-        <v>479.95</v>
+        <v>480.225</v>
       </c>
       <c r="F95" t="n">
-        <v>153.4568021117551</v>
+        <v>153.3689253444466</v>
       </c>
       <c r="G95" t="n">
-        <v>6826.573749712831</v>
+        <v>6520.856114310886</v>
       </c>
       <c r="H95" t="n">
-        <v>-1646.831322890376</v>
+        <v>-1556.424692098753</v>
       </c>
       <c r="I95" t="n">
-        <v>6.175</v>
+        <v>5.93</v>
       </c>
       <c r="J95" t="n">
-        <v>16.235</v>
+        <v>16.355</v>
       </c>
       <c r="K95" t="n">
-        <v>2.600000000000001</v>
+        <v>2.565</v>
       </c>
       <c r="L95" t="n">
-        <v>3.84</v>
+        <v>3.73</v>
       </c>
       <c r="M95" t="n">
-        <v>217.7683663567076</v>
+        <v>252.5506025773835</v>
       </c>
       <c r="N95" t="n">
-        <v>5.259798202048205</v>
+        <v>5.259773801395505</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B96" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C96" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D96" t="n">
-        <v>93.45250265423572</v>
+        <v>93.38470158508471</v>
       </c>
       <c r="E96" t="n">
-        <v>484.9</v>
+        <v>483.175</v>
       </c>
       <c r="F96" t="n">
-        <v>151.8902705166774</v>
+        <v>152.4325392943279</v>
       </c>
       <c r="G96" t="n">
-        <v>6301.06977057217</v>
+        <v>6594.837628184146</v>
       </c>
       <c r="H96" t="n">
-        <v>-1447.120354272668</v>
+        <v>-1530.901072374127</v>
       </c>
       <c r="I96" t="n">
-        <v>5.77</v>
+        <v>6.19</v>
       </c>
       <c r="J96" t="n">
-        <v>17.625</v>
+        <v>16.835</v>
       </c>
       <c r="K96" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="L96" t="n">
-        <v>3.785</v>
+        <v>3.915</v>
       </c>
       <c r="M96" t="n">
-        <v>269.762677643332</v>
+        <v>217.6849423681168</v>
       </c>
       <c r="N96" t="n">
-        <v>5.259119322955875</v>
+        <v>5.259773801395505</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B97" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C97" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D97" t="n">
-        <v>93.42677108523303</v>
+        <v>93.43566194116374</v>
       </c>
       <c r="E97" t="n">
-        <v>486.465</v>
+        <v>472.575</v>
       </c>
       <c r="F97" t="n">
-        <v>151.4016263729906</v>
+        <v>155.8516471957612</v>
       </c>
       <c r="G97" t="n">
-        <v>6353.676339944446</v>
+        <v>6621.745409759462</v>
       </c>
       <c r="H97" t="n">
-        <v>-1418.653381854311</v>
+        <v>-1721.777563608836</v>
       </c>
       <c r="I97" t="n">
-        <v>5.92</v>
+        <v>5.73</v>
       </c>
       <c r="J97" t="n">
-        <v>17.985</v>
+        <v>15.35</v>
       </c>
       <c r="K97" t="n">
-        <v>2.875</v>
+        <v>2.41</v>
       </c>
       <c r="L97" t="n">
-        <v>3.96</v>
+        <v>3.485</v>
       </c>
       <c r="M97" t="n">
-        <v>227.387166189546</v>
+        <v>286.5115313664276</v>
       </c>
       <c r="N97" t="n">
-        <v>5.259119322955875</v>
+        <v>5.259798202048205</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B98" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C98" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D98" t="n">
-        <v>93.38624724840726</v>
+        <v>93.37423222341569</v>
       </c>
       <c r="E98" t="n">
-        <v>490.03</v>
+        <v>476.835</v>
       </c>
       <c r="F98" t="n">
-        <v>150.3001697315202</v>
+        <v>154.4592829249884</v>
       </c>
       <c r="G98" t="n">
-        <v>6445.731747995634</v>
+        <v>6757.198730392972</v>
       </c>
       <c r="H98" t="n">
-        <v>-1383.163908665368</v>
+        <v>-1663.892522353884</v>
       </c>
       <c r="I98" t="n">
-        <v>6.11</v>
+        <v>5.92</v>
       </c>
       <c r="J98" t="n">
-        <v>18.39</v>
+        <v>15.76</v>
       </c>
       <c r="K98" t="n">
-        <v>3.055</v>
+        <v>2.505</v>
       </c>
       <c r="L98" t="n">
-        <v>4.140000000000001</v>
+        <v>3.649999999999999</v>
       </c>
       <c r="M98" t="n">
-        <v>227.3868800057831</v>
+        <v>252.6008943792451</v>
       </c>
       <c r="N98" t="n">
-        <v>5.259119322955875</v>
+        <v>5.259798202048205</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B99" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C99" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D99" t="n">
-        <v>93.41591029275426</v>
+        <v>93.34673725956608</v>
       </c>
       <c r="E99" t="n">
-        <v>481.545</v>
+        <v>479.95</v>
       </c>
       <c r="F99" t="n">
-        <v>152.9485139987683</v>
+        <v>153.4568021117551</v>
       </c>
       <c r="G99" t="n">
-        <v>6530.938266738748</v>
+        <v>6826.573749712831</v>
       </c>
       <c r="H99" t="n">
-        <v>-1565.303400950452</v>
+        <v>-1646.831322890376</v>
       </c>
       <c r="I99" t="n">
-        <v>5.765</v>
+        <v>6.175</v>
       </c>
       <c r="J99" t="n">
-        <v>16.845</v>
+        <v>16.235</v>
       </c>
       <c r="K99" t="n">
-        <v>2.605</v>
+        <v>2.600000000000001</v>
       </c>
       <c r="L99" t="n">
-        <v>3.685</v>
+        <v>3.84</v>
       </c>
       <c r="M99" t="n">
-        <v>274.6352173903875</v>
+        <v>217.7683663567076</v>
       </c>
       <c r="N99" t="n">
-        <v>5.259145247383652</v>
+        <v>5.259798202048205</v>
       </c>
     </row>
     <row r="100">
@@ -4817,43 +4817,43 @@
         <v>312</v>
       </c>
       <c r="B100" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C100" t="n">
         <v>312</v>
       </c>
       <c r="D100" t="n">
-        <v>93.39001183292956</v>
+        <v>93.45250265423572</v>
       </c>
       <c r="E100" t="n">
-        <v>482.945</v>
+        <v>484.9</v>
       </c>
       <c r="F100" t="n">
-        <v>152.5051344843344</v>
+        <v>151.8902705166774</v>
       </c>
       <c r="G100" t="n">
-        <v>6583.057698376676</v>
+        <v>6301.06977057217</v>
       </c>
       <c r="H100" t="n">
-        <v>-1535.832889914837</v>
+        <v>-1447.120354272668</v>
       </c>
       <c r="I100" t="n">
-        <v>5.905</v>
+        <v>5.77</v>
       </c>
       <c r="J100" t="n">
-        <v>17.195</v>
+        <v>17.625</v>
       </c>
       <c r="K100" t="n">
-        <v>2.775</v>
+        <v>2.7</v>
       </c>
       <c r="L100" t="n">
-        <v>3.86</v>
+        <v>3.785</v>
       </c>
       <c r="M100" t="n">
-        <v>227.4493457435706</v>
+        <v>269.762677643332</v>
       </c>
       <c r="N100" t="n">
-        <v>5.259145247383652</v>
+        <v>5.259119322955875</v>
       </c>
     </row>
     <row r="101">
@@ -4861,43 +4861,43 @@
         <v>312</v>
       </c>
       <c r="B101" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C101" t="n">
         <v>312</v>
       </c>
       <c r="D101" t="n">
-        <v>93.33698224806081</v>
+        <v>93.42677108523303</v>
       </c>
       <c r="E101" t="n">
-        <v>486</v>
+        <v>486.465</v>
       </c>
       <c r="F101" t="n">
-        <v>151.5464859537796</v>
+        <v>151.4016263729906</v>
       </c>
       <c r="G101" t="n">
-        <v>6692.840471458085</v>
+        <v>6353.676339944446</v>
       </c>
       <c r="H101" t="n">
-        <v>-1478.632015084863</v>
+        <v>-1418.653381854311</v>
       </c>
       <c r="I101" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="J101" t="n">
-        <v>17.595</v>
+        <v>17.985</v>
       </c>
       <c r="K101" t="n">
-        <v>2.955</v>
+        <v>2.875</v>
       </c>
       <c r="L101" t="n">
-        <v>4.035</v>
+        <v>3.96</v>
       </c>
       <c r="M101" t="n">
-        <v>227.4474126794829</v>
+        <v>227.387166189546</v>
       </c>
       <c r="N101" t="n">
-        <v>5.259145247383652</v>
+        <v>5.259119322955875</v>
       </c>
     </row>
     <row r="102">
@@ -4905,43 +4905,43 @@
         <v>312</v>
       </c>
       <c r="B102" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C102" t="n">
         <v>312</v>
       </c>
       <c r="D102" t="n">
-        <v>93.38487797562313</v>
+        <v>93.38624724840726</v>
       </c>
       <c r="E102" t="n">
-        <v>477.69</v>
+        <v>490.03</v>
       </c>
       <c r="F102" t="n">
-        <v>154.1828218583954</v>
+        <v>150.3001697315202</v>
       </c>
       <c r="G102" t="n">
-        <v>6745.057849636835</v>
+        <v>6445.731747995634</v>
       </c>
       <c r="H102" t="n">
-        <v>-1685.38552511403</v>
+        <v>-1383.163908665368</v>
       </c>
       <c r="I102" t="n">
-        <v>5.76</v>
+        <v>6.11</v>
       </c>
       <c r="J102" t="n">
-        <v>16.175</v>
+        <v>18.39</v>
       </c>
       <c r="K102" t="n">
-        <v>2.524999999999999</v>
+        <v>3.055</v>
       </c>
       <c r="L102" t="n">
-        <v>3.605</v>
+        <v>4.140000000000001</v>
       </c>
       <c r="M102" t="n">
-        <v>279.345096598119</v>
+        <v>227.3868800057831</v>
       </c>
       <c r="N102" t="n">
-        <v>5.259169007902681</v>
+        <v>5.259119322955875</v>
       </c>
     </row>
     <row r="103">
@@ -4949,43 +4949,43 @@
         <v>312</v>
       </c>
       <c r="B103" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C103" t="n">
         <v>312</v>
       </c>
       <c r="D103" t="n">
-        <v>93.34182304590459</v>
+        <v>93.41591029275426</v>
       </c>
       <c r="E103" t="n">
-        <v>480.265</v>
+        <v>481.545</v>
       </c>
       <c r="F103" t="n">
-        <v>153.3561516528102</v>
+        <v>152.9485139987683</v>
       </c>
       <c r="G103" t="n">
-        <v>6836.346687415179</v>
+        <v>6530.938266738748</v>
       </c>
       <c r="H103" t="n">
-        <v>-1641.131631885564</v>
+        <v>-1565.303400950452</v>
       </c>
       <c r="I103" t="n">
-        <v>5.89</v>
+        <v>5.765</v>
       </c>
       <c r="J103" t="n">
-        <v>16.525</v>
+        <v>16.845</v>
       </c>
       <c r="K103" t="n">
-        <v>2.694999999999999</v>
+        <v>2.605</v>
       </c>
       <c r="L103" t="n">
-        <v>3.775</v>
+        <v>3.685</v>
       </c>
       <c r="M103" t="n">
-        <v>227.5122438338848</v>
+        <v>274.6352173903875</v>
       </c>
       <c r="N103" t="n">
-        <v>5.259169007902681</v>
+        <v>5.259145247383652</v>
       </c>
     </row>
     <row r="104">
@@ -4993,219 +4993,219 @@
         <v>312</v>
       </c>
       <c r="B104" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C104" t="n">
         <v>312</v>
       </c>
       <c r="D104" t="n">
-        <v>93.29647038871212</v>
+        <v>93.39001183292956</v>
       </c>
       <c r="E104" t="n">
-        <v>482.67</v>
+        <v>482.945</v>
       </c>
       <c r="F104" t="n">
-        <v>152.5920238952843</v>
+        <v>152.5051344843344</v>
       </c>
       <c r="G104" t="n">
-        <v>6928.78597366593</v>
+        <v>6583.057698376676</v>
       </c>
       <c r="H104" t="n">
-        <v>-1590.767787306452</v>
+        <v>-1535.832889914837</v>
       </c>
       <c r="I104" t="n">
-        <v>6.07</v>
+        <v>5.905</v>
       </c>
       <c r="J104" t="n">
-        <v>16.91</v>
+        <v>17.195</v>
       </c>
       <c r="K104" t="n">
-        <v>2.87</v>
+        <v>2.775</v>
       </c>
       <c r="L104" t="n">
-        <v>3.950000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="M104" t="n">
-        <v>227.5233010492316</v>
+        <v>227.4493457435706</v>
       </c>
       <c r="N104" t="n">
-        <v>5.259169007902681</v>
+        <v>5.259145247383652</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B105" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C105" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D105" t="n">
-        <v>93.52344188381194</v>
+        <v>93.33698224806081</v>
       </c>
       <c r="E105" t="n">
-        <v>486.865</v>
+        <v>486</v>
       </c>
       <c r="F105" t="n">
-        <v>151.2772373728587</v>
+        <v>151.5464859537796</v>
       </c>
       <c r="G105" t="n">
-        <v>5978.49564190572</v>
+        <v>6692.840471458085</v>
       </c>
       <c r="H105" t="n">
-        <v>-1344.201364050864</v>
+        <v>-1478.632015084863</v>
       </c>
       <c r="I105" t="n">
-        <v>5.845</v>
+        <v>6.09</v>
       </c>
       <c r="J105" t="n">
-        <v>17.97</v>
+        <v>17.595</v>
       </c>
       <c r="K105" t="n">
-        <v>2.675</v>
+        <v>2.955</v>
       </c>
       <c r="L105" t="n">
-        <v>3.76</v>
+        <v>4.035</v>
       </c>
       <c r="M105" t="n">
-        <v>261.2478496081201</v>
+        <v>227.4474126794829</v>
       </c>
       <c r="N105" t="n">
-        <v>5.252678710798757</v>
+        <v>5.259145247383652</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B106" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C106" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D106" t="n">
-        <v>93.510352875904</v>
+        <v>93.38487797562313</v>
       </c>
       <c r="E106" t="n">
-        <v>487.765</v>
+        <v>477.69</v>
       </c>
       <c r="F106" t="n">
-        <v>150.9981080510838</v>
+        <v>154.1828218583954</v>
       </c>
       <c r="G106" t="n">
-        <v>6004.499379622453</v>
+        <v>6745.057849636835</v>
       </c>
       <c r="H106" t="n">
-        <v>-1328.94116491731</v>
+        <v>-1685.38552511403</v>
       </c>
       <c r="I106" t="n">
-        <v>5.985</v>
+        <v>5.76</v>
       </c>
       <c r="J106" t="n">
-        <v>18.325</v>
+        <v>16.175</v>
       </c>
       <c r="K106" t="n">
-        <v>2.850000000000001</v>
+        <v>2.524999999999999</v>
       </c>
       <c r="L106" t="n">
-        <v>3.935</v>
+        <v>3.605</v>
       </c>
       <c r="M106" t="n">
-        <v>227.3276642712568</v>
+        <v>279.345096598119</v>
       </c>
       <c r="N106" t="n">
-        <v>5.252678710798757</v>
+        <v>5.259169007902681</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B107" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C107" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D107" t="n">
-        <v>93.46947467146789</v>
+        <v>93.34182304590459</v>
       </c>
       <c r="E107" t="n">
-        <v>491.76</v>
+        <v>480.265</v>
       </c>
       <c r="F107" t="n">
-        <v>149.7714173042477</v>
+        <v>153.3561516528102</v>
       </c>
       <c r="G107" t="n">
-        <v>6098.474812084224</v>
+        <v>6836.346687415179</v>
       </c>
       <c r="H107" t="n">
-        <v>-1294.215376117578</v>
+        <v>-1641.131631885564</v>
       </c>
       <c r="I107" t="n">
-        <v>6.17</v>
+        <v>5.89</v>
       </c>
       <c r="J107" t="n">
-        <v>18.73</v>
+        <v>16.525</v>
       </c>
       <c r="K107" t="n">
-        <v>3.025</v>
+        <v>2.694999999999999</v>
       </c>
       <c r="L107" t="n">
-        <v>4.11</v>
+        <v>3.775</v>
       </c>
       <c r="M107" t="n">
-        <v>227.3237025252131</v>
+        <v>227.5122438338848</v>
       </c>
       <c r="N107" t="n">
-        <v>5.252678710798757</v>
+        <v>5.259169007902681</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B108" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C108" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D108" t="n">
-        <v>93.49552562765908</v>
+        <v>93.29647038871212</v>
       </c>
       <c r="E108" t="n">
-        <v>482.51</v>
+        <v>482.67</v>
       </c>
       <c r="F108" t="n">
-        <v>152.6426233104741</v>
+        <v>152.5920238952843</v>
       </c>
       <c r="G108" t="n">
-        <v>6177.560557045344</v>
+        <v>6928.78597366593</v>
       </c>
       <c r="H108" t="n">
-        <v>-1458.447798458095</v>
+        <v>-1590.767787306452</v>
       </c>
       <c r="I108" t="n">
-        <v>5.83</v>
+        <v>6.07</v>
       </c>
       <c r="J108" t="n">
-        <v>17.14</v>
+        <v>16.91</v>
       </c>
       <c r="K108" t="n">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="L108" t="n">
-        <v>3.67</v>
+        <v>3.950000000000001</v>
       </c>
       <c r="M108" t="n">
-        <v>265.9538786030489</v>
+        <v>227.5233010492316</v>
       </c>
       <c r="N108" t="n">
-        <v>5.25270413490255</v>
+        <v>5.259169007902681</v>
       </c>
     </row>
     <row r="109">
@@ -5213,43 +5213,43 @@
         <v>318</v>
       </c>
       <c r="B109" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C109" t="n">
         <v>318</v>
       </c>
       <c r="D109" t="n">
-        <v>93.46407091502158</v>
+        <v>93.52344188381194</v>
       </c>
       <c r="E109" t="n">
-        <v>484.135</v>
+        <v>486.865</v>
       </c>
       <c r="F109" t="n">
-        <v>152.1302780702425</v>
+        <v>151.2772373728587</v>
       </c>
       <c r="G109" t="n">
-        <v>6239.26552564235</v>
+        <v>5978.49564190572</v>
       </c>
       <c r="H109" t="n">
-        <v>-1421.012016389429</v>
+        <v>-1344.201364050864</v>
       </c>
       <c r="I109" t="n">
-        <v>5.965</v>
+        <v>5.845</v>
       </c>
       <c r="J109" t="n">
-        <v>17.485</v>
+        <v>17.97</v>
       </c>
       <c r="K109" t="n">
-        <v>2.755</v>
+        <v>2.675</v>
       </c>
       <c r="L109" t="n">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="M109" t="n">
-        <v>227.3787156649078</v>
+        <v>261.2478496081201</v>
       </c>
       <c r="N109" t="n">
-        <v>5.25270413490255</v>
+        <v>5.252678710798757</v>
       </c>
     </row>
     <row r="110">
@@ -5257,43 +5257,43 @@
         <v>318</v>
       </c>
       <c r="B110" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C110" t="n">
         <v>318</v>
       </c>
       <c r="D110" t="n">
-        <v>93.42020557120924</v>
+        <v>93.510352875904</v>
       </c>
       <c r="E110" t="n">
-        <v>487.125</v>
+        <v>487.765</v>
       </c>
       <c r="F110" t="n">
-        <v>151.1964940693597</v>
+        <v>150.9981080510838</v>
       </c>
       <c r="G110" t="n">
-        <v>6331.624498374702</v>
+        <v>6004.499379622453</v>
       </c>
       <c r="H110" t="n">
-        <v>-1375.228079086551</v>
+        <v>-1328.94116491731</v>
       </c>
       <c r="I110" t="n">
-        <v>6.140000000000001</v>
+        <v>5.985</v>
       </c>
       <c r="J110" t="n">
-        <v>17.88</v>
+        <v>18.325</v>
       </c>
       <c r="K110" t="n">
-        <v>2.935</v>
+        <v>2.850000000000001</v>
       </c>
       <c r="L110" t="n">
-        <v>4.015000000000001</v>
+        <v>3.935</v>
       </c>
       <c r="M110" t="n">
-        <v>227.3868420862642</v>
+        <v>227.3276642712568</v>
       </c>
       <c r="N110" t="n">
-        <v>5.25270413490255</v>
+        <v>5.252678710798757</v>
       </c>
     </row>
     <row r="111">
@@ -5301,43 +5301,43 @@
         <v>318</v>
       </c>
       <c r="B111" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C111" t="n">
         <v>318</v>
       </c>
       <c r="D111" t="n">
-        <v>93.46203382968781</v>
+        <v>93.46947467146789</v>
       </c>
       <c r="E111" t="n">
-        <v>478.79</v>
+        <v>491.76</v>
       </c>
       <c r="F111" t="n">
-        <v>153.828593273746</v>
+        <v>149.7714173042477</v>
       </c>
       <c r="G111" t="n">
-        <v>6387.147371594431</v>
+        <v>6098.474812084224</v>
       </c>
       <c r="H111" t="n">
-        <v>-1565.790686198157</v>
+        <v>-1294.215376117578</v>
       </c>
       <c r="I111" t="n">
-        <v>5.825</v>
+        <v>6.17</v>
       </c>
       <c r="J111" t="n">
-        <v>16.43</v>
+        <v>18.73</v>
       </c>
       <c r="K111" t="n">
-        <v>2.52</v>
+        <v>3.025</v>
       </c>
       <c r="L111" t="n">
-        <v>3.600000000000001</v>
+        <v>4.11</v>
       </c>
       <c r="M111" t="n">
-        <v>270.5029847093602</v>
+        <v>227.3237025252131</v>
       </c>
       <c r="N111" t="n">
-        <v>5.252726696375484</v>
+        <v>5.252678710798757</v>
       </c>
     </row>
     <row r="112">
@@ -5345,43 +5345,43 @@
         <v>318</v>
       </c>
       <c r="B112" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C112" t="n">
         <v>318</v>
       </c>
       <c r="D112" t="n">
-        <v>93.42602857046694</v>
+        <v>93.49552562765908</v>
       </c>
       <c r="E112" t="n">
-        <v>481.3</v>
+        <v>482.51</v>
       </c>
       <c r="F112" t="n">
-        <v>153.0263706078057</v>
+        <v>152.6426233104741</v>
       </c>
       <c r="G112" t="n">
-        <v>6464.619020264462</v>
+        <v>6177.560557045344</v>
       </c>
       <c r="H112" t="n">
-        <v>-1529.879517998228</v>
+        <v>-1458.447798458095</v>
       </c>
       <c r="I112" t="n">
-        <v>5.945</v>
+        <v>5.83</v>
       </c>
       <c r="J112" t="n">
-        <v>16.765</v>
+        <v>17.14</v>
       </c>
       <c r="K112" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="L112" t="n">
-        <v>3.76</v>
+        <v>3.67</v>
       </c>
       <c r="M112" t="n">
-        <v>227.4449342895346</v>
+        <v>265.9538786030489</v>
       </c>
       <c r="N112" t="n">
-        <v>5.252726696375484</v>
+        <v>5.25270413490255</v>
       </c>
     </row>
     <row r="113">
@@ -5389,219 +5389,219 @@
         <v>318</v>
       </c>
       <c r="B113" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C113" t="n">
         <v>318</v>
       </c>
       <c r="D113" t="n">
-        <v>93.38258710001347</v>
+        <v>93.46407091502158</v>
       </c>
       <c r="E113" t="n">
-        <v>483.63</v>
+        <v>484.135</v>
       </c>
       <c r="F113" t="n">
-        <v>152.2891304789547</v>
+        <v>152.1302780702425</v>
       </c>
       <c r="G113" t="n">
-        <v>6551.853031023486</v>
+        <v>6239.26552564235</v>
       </c>
       <c r="H113" t="n">
-        <v>-1480.279716189877</v>
+        <v>-1421.012016389429</v>
       </c>
       <c r="I113" t="n">
-        <v>6.12</v>
+        <v>5.965</v>
       </c>
       <c r="J113" t="n">
-        <v>17.16</v>
+        <v>17.485</v>
       </c>
       <c r="K113" t="n">
-        <v>2.86</v>
+        <v>2.755</v>
       </c>
       <c r="L113" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="M113" t="n">
-        <v>227.451941689032</v>
+        <v>227.3787156649078</v>
       </c>
       <c r="N113" t="n">
-        <v>5.252726696375484</v>
+        <v>5.25270413490255</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B114" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C114" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D114" t="n">
-        <v>93.49668303760703</v>
+        <v>93.42020557120924</v>
       </c>
       <c r="E114" t="n">
-        <v>490.235</v>
+        <v>487.125</v>
       </c>
       <c r="F114" t="n">
-        <v>150.2373191908715</v>
+        <v>151.1964940693597</v>
       </c>
       <c r="G114" t="n">
-        <v>6045.612332308569</v>
+        <v>6331.624498374702</v>
       </c>
       <c r="H114" t="n">
-        <v>-1327.114476265482</v>
+        <v>-1375.228079086551</v>
       </c>
       <c r="I114" t="n">
-        <v>5.885</v>
+        <v>6.140000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>18.635</v>
+        <v>17.88</v>
       </c>
       <c r="K114" t="n">
-        <v>2.760000000000001</v>
+        <v>2.935</v>
       </c>
       <c r="L114" t="n">
-        <v>3.850000000000001</v>
+        <v>4.015000000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>259.1072797243198</v>
+        <v>227.3868420862642</v>
       </c>
       <c r="N114" t="n">
-        <v>5.253775613092472</v>
+        <v>5.25270413490255</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B115" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C115" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D115" t="n">
-        <v>93.47820692696499</v>
+        <v>93.46203382968781</v>
       </c>
       <c r="E115" t="n">
-        <v>491.13</v>
+        <v>478.79</v>
       </c>
       <c r="F115" t="n">
-        <v>149.9635375023657</v>
+        <v>153.828593273746</v>
       </c>
       <c r="G115" t="n">
-        <v>6080.621469916417</v>
+        <v>6387.147371594431</v>
       </c>
       <c r="H115" t="n">
-        <v>-1303.877010159506</v>
+        <v>-1565.790686198157</v>
       </c>
       <c r="I115" t="n">
-        <v>6.035</v>
+        <v>5.825</v>
       </c>
       <c r="J115" t="n">
-        <v>19.005</v>
+        <v>16.43</v>
       </c>
       <c r="K115" t="n">
-        <v>2.935</v>
+        <v>2.52</v>
       </c>
       <c r="L115" t="n">
-        <v>4.025</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="M115" t="n">
-        <v>227.2887429361407</v>
+        <v>270.5029847093602</v>
       </c>
       <c r="N115" t="n">
-        <v>5.253775613092472</v>
+        <v>5.252726696375484</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B116" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C116" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D116" t="n">
-        <v>93.43841750829837</v>
+        <v>93.42602857046694</v>
       </c>
       <c r="E116" t="n">
-        <v>494.625</v>
+        <v>481.3</v>
       </c>
       <c r="F116" t="n">
-        <v>148.9039012858971</v>
+        <v>153.0263706078057</v>
       </c>
       <c r="G116" t="n">
-        <v>6169.331357784015</v>
+        <v>6464.619020264462</v>
       </c>
       <c r="H116" t="n">
-        <v>-1267.299226715</v>
+        <v>-1529.879517998228</v>
       </c>
       <c r="I116" t="n">
-        <v>6.225000000000001</v>
+        <v>5.945</v>
       </c>
       <c r="J116" t="n">
-        <v>19.415</v>
+        <v>16.765</v>
       </c>
       <c r="K116" t="n">
-        <v>3.115</v>
+        <v>2.68</v>
       </c>
       <c r="L116" t="n">
-        <v>4.205</v>
+        <v>3.76</v>
       </c>
       <c r="M116" t="n">
-        <v>227.2953521330323</v>
+        <v>227.4449342895346</v>
       </c>
       <c r="N116" t="n">
-        <v>5.253775613092472</v>
+        <v>5.252726696375484</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B117" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C117" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D117" t="n">
-        <v>93.4668841967427</v>
+        <v>93.38258710001347</v>
       </c>
       <c r="E117" t="n">
-        <v>485.125</v>
+        <v>483.63</v>
       </c>
       <c r="F117" t="n">
-        <v>151.8198241144795</v>
+        <v>152.2891304789547</v>
       </c>
       <c r="G117" t="n">
-        <v>6243.154855929256</v>
+        <v>6551.853031023486</v>
       </c>
       <c r="H117" t="n">
-        <v>-1433.859687118748</v>
+        <v>-1480.279716189877</v>
       </c>
       <c r="I117" t="n">
-        <v>5.865</v>
+        <v>6.12</v>
       </c>
       <c r="J117" t="n">
-        <v>17.735</v>
+        <v>17.16</v>
       </c>
       <c r="K117" t="n">
-        <v>2.655</v>
+        <v>2.86</v>
       </c>
       <c r="L117" t="n">
-        <v>3.740000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="M117" t="n">
-        <v>263.7794622573939</v>
+        <v>227.451941689032</v>
       </c>
       <c r="N117" t="n">
-        <v>5.253800030107287</v>
+        <v>5.252726696375484</v>
       </c>
     </row>
     <row r="118">
@@ -5609,43 +5609,43 @@
         <v>319</v>
       </c>
       <c r="B118" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C118" t="n">
         <v>319</v>
       </c>
       <c r="D118" t="n">
-        <v>93.43924305446829</v>
+        <v>93.49668303760703</v>
       </c>
       <c r="E118" t="n">
-        <v>486.945</v>
+        <v>490.235</v>
       </c>
       <c r="F118" t="n">
-        <v>151.2523840958155</v>
+        <v>150.2373191908715</v>
       </c>
       <c r="G118" t="n">
-        <v>6300.527779996564</v>
+        <v>6045.612332308569</v>
       </c>
       <c r="H118" t="n">
-        <v>-1404.168843255348</v>
+        <v>-1327.114476265482</v>
       </c>
       <c r="I118" t="n">
-        <v>6.01</v>
+        <v>5.885</v>
       </c>
       <c r="J118" t="n">
-        <v>18.09</v>
+        <v>18.635</v>
       </c>
       <c r="K118" t="n">
-        <v>2.825</v>
+        <v>2.760000000000001</v>
       </c>
       <c r="L118" t="n">
-        <v>3.915</v>
+        <v>3.850000000000001</v>
       </c>
       <c r="M118" t="n">
-        <v>227.352599736636</v>
+        <v>259.1072797243198</v>
       </c>
       <c r="N118" t="n">
-        <v>5.253800030107287</v>
+        <v>5.253775613092472</v>
       </c>
     </row>
     <row r="119">
@@ -5653,43 +5653,43 @@
         <v>319</v>
       </c>
       <c r="B119" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C119" t="n">
         <v>319</v>
       </c>
       <c r="D119" t="n">
-        <v>93.39637801442582</v>
+        <v>93.47820692696499</v>
       </c>
       <c r="E119" t="n">
-        <v>490.185</v>
+        <v>491.13</v>
       </c>
       <c r="F119" t="n">
-        <v>150.2526437437638</v>
+        <v>149.9635375023657</v>
       </c>
       <c r="G119" t="n">
-        <v>6393.388847486058</v>
+        <v>6080.621469916417</v>
       </c>
       <c r="H119" t="n">
-        <v>-1362.057631311027</v>
+        <v>-1303.877010159506</v>
       </c>
       <c r="I119" t="n">
-        <v>6.19</v>
+        <v>6.035</v>
       </c>
       <c r="J119" t="n">
-        <v>18.495</v>
+        <v>19.005</v>
       </c>
       <c r="K119" t="n">
-        <v>3</v>
+        <v>2.935</v>
       </c>
       <c r="L119" t="n">
-        <v>4.09</v>
+        <v>4.025</v>
       </c>
       <c r="M119" t="n">
-        <v>227.3420875786154</v>
+        <v>227.2887429361407</v>
       </c>
       <c r="N119" t="n">
-        <v>5.253800030107287</v>
+        <v>5.253775613092472</v>
       </c>
     </row>
     <row r="120">
@@ -5697,43 +5697,43 @@
         <v>319</v>
       </c>
       <c r="B120" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C120" t="n">
         <v>319</v>
       </c>
       <c r="D120" t="n">
-        <v>93.42137308458253</v>
+        <v>93.43841750829837</v>
       </c>
       <c r="E120" t="n">
-        <v>482.165</v>
+        <v>494.625</v>
       </c>
       <c r="F120" t="n">
-        <v>152.7518425716028</v>
+        <v>148.9039012858971</v>
       </c>
       <c r="G120" t="n">
-        <v>6479.047213315419</v>
+        <v>6169.331357784015</v>
       </c>
       <c r="H120" t="n">
-        <v>-1529.706420525139</v>
+        <v>-1267.299226715</v>
       </c>
       <c r="I120" t="n">
-        <v>5.850000000000001</v>
+        <v>6.225000000000001</v>
       </c>
       <c r="J120" t="n">
-        <v>16.965</v>
+        <v>19.415</v>
       </c>
       <c r="K120" t="n">
-        <v>2.575</v>
+        <v>3.115</v>
       </c>
       <c r="L120" t="n">
-        <v>3.655</v>
+        <v>4.205</v>
       </c>
       <c r="M120" t="n">
-        <v>268.295846627913</v>
+        <v>227.2953521330323</v>
       </c>
       <c r="N120" t="n">
-        <v>5.253821452617513</v>
+        <v>5.253775613092472</v>
       </c>
     </row>
     <row r="121">
@@ -5741,43 +5741,43 @@
         <v>319</v>
       </c>
       <c r="B121" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C121" t="n">
         <v>319</v>
       </c>
       <c r="D121" t="n">
-        <v>93.40234395983778</v>
+        <v>93.4668841967427</v>
       </c>
       <c r="E121" t="n">
-        <v>483.125</v>
+        <v>485.125</v>
       </c>
       <c r="F121" t="n">
-        <v>152.4483149775666</v>
+        <v>151.8198241144795</v>
       </c>
       <c r="G121" t="n">
-        <v>6516.620962005842</v>
+        <v>6243.154855929256</v>
       </c>
       <c r="H121" t="n">
-        <v>-1507.309488925367</v>
+        <v>-1433.859687118748</v>
       </c>
       <c r="I121" t="n">
-        <v>5.98</v>
+        <v>5.865</v>
       </c>
       <c r="J121" t="n">
-        <v>17.31</v>
+        <v>17.735</v>
       </c>
       <c r="K121" t="n">
-        <v>2.74</v>
+        <v>2.655</v>
       </c>
       <c r="L121" t="n">
-        <v>3.825</v>
+        <v>3.740000000000001</v>
       </c>
       <c r="M121" t="n">
-        <v>227.4084175622542</v>
+        <v>263.7794622573939</v>
       </c>
       <c r="N121" t="n">
-        <v>5.253821452617513</v>
+        <v>5.253800030107287</v>
       </c>
     </row>
     <row r="122">
@@ -5785,219 +5785,219 @@
         <v>319</v>
       </c>
       <c r="B122" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C122" t="n">
         <v>319</v>
       </c>
       <c r="D122" t="n">
-        <v>93.35359060253191</v>
+        <v>93.43924305446829</v>
       </c>
       <c r="E122" t="n">
-        <v>486.345</v>
+        <v>486.945</v>
       </c>
       <c r="F122" t="n">
-        <v>151.4389829720402</v>
+        <v>151.2523840958155</v>
       </c>
       <c r="G122" t="n">
-        <v>6620.170264683915</v>
+        <v>6300.527779996564</v>
       </c>
       <c r="H122" t="n">
-        <v>-1457.370108947124</v>
+        <v>-1404.168843255348</v>
       </c>
       <c r="I122" t="n">
-        <v>6.16</v>
+        <v>6.01</v>
       </c>
       <c r="J122" t="n">
-        <v>17.715</v>
+        <v>18.09</v>
       </c>
       <c r="K122" t="n">
-        <v>2.915</v>
+        <v>2.825</v>
       </c>
       <c r="L122" t="n">
-        <v>4</v>
+        <v>3.915</v>
       </c>
       <c r="M122" t="n">
-        <v>227.4019882001658</v>
+        <v>227.352599736636</v>
       </c>
       <c r="N122" t="n">
-        <v>5.253821452617513</v>
+        <v>5.253800030107287</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B123" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C123" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D123" t="n">
-        <v>93.44950313997633</v>
+        <v>93.39637801442582</v>
       </c>
       <c r="E123" t="n">
-        <v>484.67</v>
+        <v>490.185</v>
       </c>
       <c r="F123" t="n">
-        <v>151.9623499980128</v>
+        <v>150.2526437437638</v>
       </c>
       <c r="G123" t="n">
-        <v>6304.574082983689</v>
+        <v>6393.388847486058</v>
       </c>
       <c r="H123" t="n">
-        <v>-1441.120075954446</v>
+        <v>-1362.057631311027</v>
       </c>
       <c r="I123" t="n">
-        <v>6.525</v>
+        <v>6.19</v>
       </c>
       <c r="J123" t="n">
-        <v>18.865</v>
+        <v>18.495</v>
       </c>
       <c r="K123" t="n">
-        <v>2.965000000000001</v>
+        <v>3</v>
       </c>
       <c r="L123" t="n">
-        <v>4.290000000000001</v>
+        <v>4.09</v>
       </c>
       <c r="M123" t="n">
-        <v>279.4807482110015</v>
+        <v>227.3420875786154</v>
       </c>
       <c r="N123" t="n">
-        <v>4.258269327761364</v>
+        <v>5.253800030107287</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B124" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C124" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D124" t="n">
-        <v>93.39692195319739</v>
+        <v>93.42137308458253</v>
       </c>
       <c r="E124" t="n">
-        <v>489</v>
+        <v>482.165</v>
       </c>
       <c r="F124" t="n">
-        <v>150.6167529111183</v>
+        <v>152.7518425716028</v>
       </c>
       <c r="G124" t="n">
-        <v>6422.933588566668</v>
+        <v>6479.047213315419</v>
       </c>
       <c r="H124" t="n">
-        <v>-1393.964606287007</v>
+        <v>-1529.706420525139</v>
       </c>
       <c r="I124" t="n">
-        <v>6.685</v>
+        <v>5.850000000000001</v>
       </c>
       <c r="J124" t="n">
-        <v>19.22</v>
+        <v>16.965</v>
       </c>
       <c r="K124" t="n">
-        <v>3.06</v>
+        <v>2.575</v>
       </c>
       <c r="L124" t="n">
-        <v>4.445</v>
+        <v>3.655</v>
       </c>
       <c r="M124" t="n">
-        <v>240.9661966467338</v>
+        <v>268.295846627913</v>
       </c>
       <c r="N124" t="n">
-        <v>4.258269327761364</v>
+        <v>5.253821452617513</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B125" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C125" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D125" t="n">
-        <v>93.36183593718894</v>
+        <v>93.40234395983778</v>
       </c>
       <c r="E125" t="n">
-        <v>493.485</v>
+        <v>483.125</v>
       </c>
       <c r="F125" t="n">
-        <v>149.2478842792321</v>
+        <v>152.4483149775666</v>
       </c>
       <c r="G125" t="n">
-        <v>6513.942692845931</v>
+        <v>6516.620962005842</v>
       </c>
       <c r="H125" t="n">
-        <v>-1374.670840155953</v>
+        <v>-1507.309488925367</v>
       </c>
       <c r="I125" t="n">
-        <v>6.92</v>
+        <v>5.98</v>
       </c>
       <c r="J125" t="n">
-        <v>19.665</v>
+        <v>17.31</v>
       </c>
       <c r="K125" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="L125" t="n">
-        <v>4.62</v>
+        <v>3.825</v>
       </c>
       <c r="M125" t="n">
-        <v>240.9687783972187</v>
+        <v>227.4084175622542</v>
       </c>
       <c r="N125" t="n">
-        <v>4.258269327761364</v>
+        <v>5.253821452617513</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B126" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C126" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D126" t="n">
-        <v>93.39912788985697</v>
+        <v>93.35359060253191</v>
       </c>
       <c r="E126" t="n">
-        <v>481.995</v>
+        <v>486.345</v>
       </c>
       <c r="F126" t="n">
-        <v>152.8057182616767</v>
+        <v>151.4389829720402</v>
       </c>
       <c r="G126" t="n">
-        <v>6564.006518884683</v>
+        <v>6620.170264683915</v>
       </c>
       <c r="H126" t="n">
-        <v>-1545.47621310465</v>
+        <v>-1457.370108947124</v>
       </c>
       <c r="I126" t="n">
-        <v>5.795</v>
+        <v>6.16</v>
       </c>
       <c r="J126" t="n">
-        <v>17.305</v>
+        <v>17.715</v>
       </c>
       <c r="K126" t="n">
-        <v>2.685</v>
+        <v>2.915</v>
       </c>
       <c r="L126" t="n">
-        <v>3.755</v>
+        <v>4</v>
       </c>
       <c r="M126" t="n">
-        <v>284.5657489351358</v>
+        <v>227.4019882001658</v>
       </c>
       <c r="N126" t="n">
-        <v>5.273768929319832</v>
+        <v>5.253821452617513</v>
       </c>
     </row>
     <row r="127">
@@ -6005,43 +6005,43 @@
         <v>328</v>
       </c>
       <c r="B127" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C127" t="n">
         <v>328</v>
       </c>
       <c r="D127" t="n">
-        <v>93.35960181649196</v>
+        <v>93.44950313997633</v>
       </c>
       <c r="E127" t="n">
-        <v>484.585</v>
+        <v>484.67</v>
       </c>
       <c r="F127" t="n">
-        <v>151.9890053830326</v>
+        <v>151.9623499980128</v>
       </c>
       <c r="G127" t="n">
-        <v>6648.124310726644</v>
+        <v>6304.574082983689</v>
       </c>
       <c r="H127" t="n">
-        <v>-1505.149558068831</v>
+        <v>-1441.120075954446</v>
       </c>
       <c r="I127" t="n">
-        <v>6.05</v>
+        <v>6.525</v>
       </c>
       <c r="J127" t="n">
-        <v>17.755</v>
+        <v>18.865</v>
       </c>
       <c r="K127" t="n">
-        <v>2.78</v>
+        <v>2.965000000000001</v>
       </c>
       <c r="L127" t="n">
-        <v>3.97</v>
+        <v>4.290000000000001</v>
       </c>
       <c r="M127" t="n">
-        <v>241.0251260639002</v>
+        <v>279.4807482110015</v>
       </c>
       <c r="N127" t="n">
-        <v>5.273117970311087</v>
+        <v>4.258269327761364</v>
       </c>
     </row>
     <row r="128">
@@ -6049,43 +6049,43 @@
         <v>328</v>
       </c>
       <c r="B128" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C128" t="n">
         <v>328</v>
       </c>
       <c r="D128" t="n">
-        <v>93.31885274704013</v>
+        <v>93.39692195319739</v>
       </c>
       <c r="E128" t="n">
-        <v>489.14</v>
+        <v>489</v>
       </c>
       <c r="F128" t="n">
-        <v>150.573643892417</v>
+        <v>150.6167529111183</v>
       </c>
       <c r="G128" t="n">
-        <v>6751.070800792269</v>
+        <v>6422.933588566668</v>
       </c>
       <c r="H128" t="n">
-        <v>-1479.988052872564</v>
+        <v>-1393.964606287007</v>
       </c>
       <c r="I128" t="n">
-        <v>6.32</v>
+        <v>6.685</v>
       </c>
       <c r="J128" t="n">
-        <v>18.235</v>
+        <v>19.22</v>
       </c>
       <c r="K128" t="n">
-        <v>2.875</v>
+        <v>3.06</v>
       </c>
       <c r="L128" t="n">
-        <v>4.16</v>
+        <v>4.445</v>
       </c>
       <c r="M128" t="n">
-        <v>241.0234083406213</v>
+        <v>240.9661966467338</v>
       </c>
       <c r="N128" t="n">
-        <v>5.273117970311087</v>
+        <v>4.258269327761364</v>
       </c>
     </row>
     <row r="129">
@@ -6093,43 +6093,43 @@
         <v>328</v>
       </c>
       <c r="B129" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C129" t="n">
         <v>328</v>
       </c>
       <c r="D129" t="n">
-        <v>93.37124847310385</v>
+        <v>93.36183593718894</v>
       </c>
       <c r="E129" t="n">
-        <v>477.885</v>
+        <v>493.485</v>
       </c>
       <c r="F129" t="n">
-        <v>154.119907872264</v>
+        <v>149.2478842792321</v>
       </c>
       <c r="G129" t="n">
-        <v>6771.909738162929</v>
+        <v>6513.942692845931</v>
       </c>
       <c r="H129" t="n">
-        <v>-1669.285347663635</v>
+        <v>-1374.670840155953</v>
       </c>
       <c r="I129" t="n">
-        <v>5.78</v>
+        <v>6.92</v>
       </c>
       <c r="J129" t="n">
-        <v>16.6</v>
+        <v>19.665</v>
       </c>
       <c r="K129" t="n">
-        <v>2.57</v>
+        <v>3.15</v>
       </c>
       <c r="L129" t="n">
-        <v>3.635</v>
+        <v>4.62</v>
       </c>
       <c r="M129" t="n">
-        <v>287.5103530514276</v>
+        <v>240.9687783972187</v>
       </c>
       <c r="N129" t="n">
-        <v>5.273789602585431</v>
+        <v>4.258269327761364</v>
       </c>
     </row>
     <row r="130">
@@ -6137,43 +6137,43 @@
         <v>328</v>
       </c>
       <c r="B130" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C130" t="n">
         <v>328</v>
       </c>
       <c r="D130" t="n">
-        <v>93.30922444465473</v>
+        <v>93.39912788985697</v>
       </c>
       <c r="E130" t="n">
-        <v>482.335</v>
+        <v>481.995</v>
       </c>
       <c r="F130" t="n">
-        <v>152.6980048587328</v>
+        <v>152.8057182616767</v>
       </c>
       <c r="G130" t="n">
-        <v>6909.773348486074</v>
+        <v>6564.006518884683</v>
       </c>
       <c r="H130" t="n">
-        <v>-1611.972212672484</v>
+        <v>-1545.47621310465</v>
       </c>
       <c r="I130" t="n">
-        <v>6.005</v>
+        <v>5.795</v>
       </c>
       <c r="J130" t="n">
-        <v>17.025</v>
+        <v>17.305</v>
       </c>
       <c r="K130" t="n">
-        <v>2.665</v>
+        <v>2.685</v>
       </c>
       <c r="L130" t="n">
-        <v>3.835</v>
+        <v>3.755</v>
       </c>
       <c r="M130" t="n">
-        <v>287.510554443335</v>
+        <v>284.5657489351358</v>
       </c>
       <c r="N130" t="n">
-        <v>5.27327867551934</v>
+        <v>5.273768929319832</v>
       </c>
     </row>
     <row r="131">
@@ -6181,219 +6181,219 @@
         <v>328</v>
       </c>
       <c r="B131" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C131" t="n">
         <v>328</v>
       </c>
       <c r="D131" t="n">
-        <v>93.27663173036494</v>
+        <v>93.35960181649196</v>
       </c>
       <c r="E131" t="n">
-        <v>486.08</v>
+        <v>484.585</v>
       </c>
       <c r="F131" t="n">
-        <v>151.5215441358148</v>
+        <v>151.9890053830326</v>
       </c>
       <c r="G131" t="n">
-        <v>6993.642238947837</v>
+        <v>6648.124310726644</v>
       </c>
       <c r="H131" t="n">
-        <v>-1593.427607877492</v>
+        <v>-1505.149558068831</v>
       </c>
       <c r="I131" t="n">
-        <v>6.275</v>
+        <v>6.05</v>
       </c>
       <c r="J131" t="n">
-        <v>17.5</v>
+        <v>17.755</v>
       </c>
       <c r="K131" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="L131" t="n">
-        <v>4.02</v>
+        <v>3.97</v>
       </c>
       <c r="M131" t="n">
-        <v>241.0754108106297</v>
+        <v>241.0251260639002</v>
       </c>
       <c r="N131" t="n">
-        <v>5.27327867551934</v>
+        <v>5.273117970311087</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B132" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C132" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D132" t="n">
-        <v>93.7375789427103</v>
+        <v>93.31885274704013</v>
       </c>
       <c r="E132" t="n">
-        <v>474.85</v>
+        <v>489.14</v>
       </c>
       <c r="F132" t="n">
-        <v>155.1049640381949</v>
+        <v>150.573643892417</v>
       </c>
       <c r="G132" t="n">
-        <v>5329.081592347652</v>
+        <v>6751.070800792269</v>
       </c>
       <c r="H132" t="n">
-        <v>-1365.873460059604</v>
+        <v>-1479.988052872564</v>
       </c>
       <c r="I132" t="n">
-        <v>5.755</v>
+        <v>6.32</v>
       </c>
       <c r="J132" t="n">
-        <v>16.005</v>
+        <v>18.235</v>
       </c>
       <c r="K132" t="n">
-        <v>2.55</v>
+        <v>2.875</v>
       </c>
       <c r="L132" t="n">
-        <v>3.615</v>
+        <v>4.16</v>
       </c>
       <c r="M132" t="n">
-        <v>300.0451389434209</v>
+        <v>241.0234083406213</v>
       </c>
       <c r="N132" t="n">
-        <v>5.276837814785707</v>
+        <v>5.273117970311087</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B133" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C133" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D133" t="n">
-        <v>93.70705125367142</v>
+        <v>93.37124847310385</v>
       </c>
       <c r="E133" t="n">
-        <v>477.415</v>
+        <v>477.885</v>
       </c>
       <c r="F133" t="n">
-        <v>154.2716340574487</v>
+        <v>154.119907872264</v>
       </c>
       <c r="G133" t="n">
-        <v>5395.828628533539</v>
+        <v>6771.909738162929</v>
       </c>
       <c r="H133" t="n">
-        <v>-1336.413461609626</v>
+        <v>-1669.285347663635</v>
       </c>
       <c r="I133" t="n">
-        <v>5.915</v>
+        <v>5.78</v>
       </c>
       <c r="J133" t="n">
-        <v>16.465</v>
+        <v>16.6</v>
       </c>
       <c r="K133" t="n">
-        <v>2.649999999999999</v>
+        <v>2.57</v>
       </c>
       <c r="L133" t="n">
-        <v>3.835</v>
+        <v>3.635</v>
       </c>
       <c r="M133" t="n">
-        <v>274.8280685050329</v>
+        <v>287.5103530514276</v>
       </c>
       <c r="N133" t="n">
-        <v>5.276795302796649</v>
+        <v>5.273789602585431</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B134" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C134" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D134" t="n">
-        <v>93.66736972948365</v>
+        <v>93.30922444465473</v>
       </c>
       <c r="E134" t="n">
-        <v>481.67</v>
+        <v>482.335</v>
       </c>
       <c r="F134" t="n">
-        <v>152.9088217525212</v>
+        <v>152.6980048587328</v>
       </c>
       <c r="G134" t="n">
-        <v>5487.845062078589</v>
+        <v>6909.773348486074</v>
       </c>
       <c r="H134" t="n">
-        <v>-1303.427722412256</v>
+        <v>-1611.972212672484</v>
       </c>
       <c r="I134" t="n">
-        <v>6.105</v>
+        <v>6.005</v>
       </c>
       <c r="J134" t="n">
-        <v>16.965</v>
+        <v>17.025</v>
       </c>
       <c r="K134" t="n">
-        <v>2.75</v>
+        <v>2.665</v>
       </c>
       <c r="L134" t="n">
-        <v>4.029999999999999</v>
+        <v>3.835</v>
       </c>
       <c r="M134" t="n">
-        <v>237.9234559192009</v>
+        <v>287.510554443335</v>
       </c>
       <c r="N134" t="n">
-        <v>5.276795302796649</v>
+        <v>5.27327867551934</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B135" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C135" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D135" t="n">
-        <v>93.70509773020183</v>
+        <v>93.27663173036494</v>
       </c>
       <c r="E135" t="n">
-        <v>472.055</v>
+        <v>486.08</v>
       </c>
       <c r="F135" t="n">
-        <v>156.0233281578139</v>
+        <v>151.5215441358148</v>
       </c>
       <c r="G135" t="n">
-        <v>5529.88772868665</v>
+        <v>6993.642238947837</v>
       </c>
       <c r="H135" t="n">
-        <v>-1466.999094859334</v>
+        <v>-1593.427607877492</v>
       </c>
       <c r="I135" t="n">
-        <v>5.75</v>
+        <v>6.275</v>
       </c>
       <c r="J135" t="n">
-        <v>15.4</v>
+        <v>17.5</v>
       </c>
       <c r="K135" t="n">
-        <v>2.455</v>
+        <v>2.76</v>
       </c>
       <c r="L135" t="n">
-        <v>3.52</v>
+        <v>4.02</v>
       </c>
       <c r="M135" t="n">
-        <v>300.057823899897</v>
+        <v>241.0754108106297</v>
       </c>
       <c r="N135" t="n">
-        <v>5.276849632707642</v>
+        <v>5.27327867551934</v>
       </c>
     </row>
     <row r="136">
@@ -6401,43 +6401,43 @@
         <v>332</v>
       </c>
       <c r="B136" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C136" t="n">
         <v>332</v>
       </c>
       <c r="D136" t="n">
-        <v>93.67181804630056</v>
+        <v>93.7375789427103</v>
       </c>
       <c r="E136" t="n">
-        <v>474.585</v>
+        <v>474.85</v>
       </c>
       <c r="F136" t="n">
-        <v>155.1915719492544</v>
+        <v>155.1049640381949</v>
       </c>
       <c r="G136" t="n">
-        <v>5602.478434254266</v>
+        <v>5329.081592347652</v>
       </c>
       <c r="H136" t="n">
-        <v>-1434.724518811227</v>
+        <v>-1365.873460059604</v>
       </c>
       <c r="I136" t="n">
-        <v>5.895</v>
+        <v>5.755</v>
       </c>
       <c r="J136" t="n">
-        <v>15.85</v>
+        <v>16.005</v>
       </c>
       <c r="K136" t="n">
         <v>2.55</v>
       </c>
       <c r="L136" t="n">
-        <v>3.715</v>
+        <v>3.615</v>
       </c>
       <c r="M136" t="n">
-        <v>274.866698194862</v>
+        <v>300.0451389434209</v>
       </c>
       <c r="N136" t="n">
-        <v>5.276816974753548</v>
+        <v>5.276837814785707</v>
       </c>
     </row>
     <row r="137">
@@ -6445,43 +6445,43 @@
         <v>332</v>
       </c>
       <c r="B137" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C137" t="n">
         <v>332</v>
       </c>
       <c r="D137" t="n">
-        <v>93.64238349983798</v>
+        <v>93.70705125367142</v>
       </c>
       <c r="E137" t="n">
-        <v>477.355</v>
+        <v>477.415</v>
       </c>
       <c r="F137" t="n">
-        <v>154.2910248631246</v>
+        <v>154.2716340574487</v>
       </c>
       <c r="G137" t="n">
-        <v>5669.039064292543</v>
+        <v>5395.828628533539</v>
       </c>
       <c r="H137" t="n">
-        <v>-1408.571100816436</v>
+        <v>-1336.413461609626</v>
       </c>
       <c r="I137" t="n">
-        <v>6.08</v>
+        <v>5.915</v>
       </c>
       <c r="J137" t="n">
-        <v>16.34</v>
+        <v>16.465</v>
       </c>
       <c r="K137" t="n">
-        <v>2.65</v>
+        <v>2.649999999999999</v>
       </c>
       <c r="L137" t="n">
-        <v>3.91</v>
+        <v>3.835</v>
       </c>
       <c r="M137" t="n">
-        <v>237.9996639240671</v>
+        <v>274.8280685050329</v>
       </c>
       <c r="N137" t="n">
-        <v>5.276816974753548</v>
+        <v>5.276795302796649</v>
       </c>
     </row>
     <row r="138">
@@ -6489,43 +6489,43 @@
         <v>332</v>
       </c>
       <c r="B138" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C138" t="n">
         <v>332</v>
       </c>
       <c r="D138" t="n">
-        <v>93.66794361387699</v>
+        <v>93.66736972948365</v>
       </c>
       <c r="E138" t="n">
-        <v>469.655</v>
+        <v>481.67</v>
       </c>
       <c r="F138" t="n">
-        <v>156.8206282772181</v>
+        <v>152.9088217525212</v>
       </c>
       <c r="G138" t="n">
-        <v>5741.700304435783</v>
+        <v>5487.845062078589</v>
       </c>
       <c r="H138" t="n">
-        <v>-1564.573877329694</v>
+        <v>-1303.427722412256</v>
       </c>
       <c r="I138" t="n">
-        <v>5.755</v>
+        <v>6.105</v>
       </c>
       <c r="J138" t="n">
-        <v>14.94</v>
+        <v>16.965</v>
       </c>
       <c r="K138" t="n">
-        <v>2.409999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="L138" t="n">
-        <v>3.47</v>
+        <v>4.029999999999999</v>
       </c>
       <c r="M138" t="n">
-        <v>300.0685310526121</v>
+        <v>237.9234559192009</v>
       </c>
       <c r="N138" t="n">
-        <v>5.27685976993095</v>
+        <v>5.276795302796649</v>
       </c>
     </row>
     <row r="139">
@@ -6533,43 +6533,43 @@
         <v>332</v>
       </c>
       <c r="B139" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C139" t="n">
         <v>332</v>
       </c>
       <c r="D139" t="n">
-        <v>93.63334590745175</v>
+        <v>93.70509773020183</v>
       </c>
       <c r="E139" t="n">
-        <v>471.635</v>
+        <v>472.055</v>
       </c>
       <c r="F139" t="n">
-        <v>156.1622699196134</v>
+        <v>156.0233281578139</v>
       </c>
       <c r="G139" t="n">
-        <v>5812.801875073716</v>
+        <v>5529.88772868665</v>
       </c>
       <c r="H139" t="n">
-        <v>-1526.631806797996</v>
+        <v>-1466.999094859334</v>
       </c>
       <c r="I139" t="n">
-        <v>5.895</v>
+        <v>5.75</v>
       </c>
       <c r="J139" t="n">
-        <v>15.385</v>
+        <v>15.4</v>
       </c>
       <c r="K139" t="n">
-        <v>2.505</v>
+        <v>2.455</v>
       </c>
       <c r="L139" t="n">
-        <v>3.655</v>
+        <v>3.52</v>
       </c>
       <c r="M139" t="n">
-        <v>274.9196996246158</v>
+        <v>300.057823899897</v>
       </c>
       <c r="N139" t="n">
-        <v>5.276826591510677</v>
+        <v>5.276849632707642</v>
       </c>
     </row>
     <row r="140">
@@ -6577,219 +6577,219 @@
         <v>332</v>
       </c>
       <c r="B140" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C140" t="n">
         <v>332</v>
       </c>
       <c r="D140" t="n">
-        <v>93.59397703509872</v>
+        <v>93.67181804630056</v>
       </c>
       <c r="E140" t="n">
-        <v>476.305</v>
+        <v>474.585</v>
       </c>
       <c r="F140" t="n">
-        <v>154.6311547717048</v>
+        <v>155.1915719492544</v>
       </c>
       <c r="G140" t="n">
-        <v>5910.743701685864</v>
+        <v>5602.478434254266</v>
       </c>
       <c r="H140" t="n">
-        <v>-1500.678319208266</v>
+        <v>-1434.724518811227</v>
       </c>
       <c r="I140" t="n">
-        <v>6.08</v>
+        <v>5.895</v>
       </c>
       <c r="J140" t="n">
-        <v>15.865</v>
+        <v>15.85</v>
       </c>
       <c r="K140" t="n">
-        <v>2.595000000000001</v>
+        <v>2.55</v>
       </c>
       <c r="L140" t="n">
-        <v>3.845000000000001</v>
+        <v>3.715</v>
       </c>
       <c r="M140" t="n">
-        <v>238.0733419319008</v>
+        <v>274.866698194862</v>
       </c>
       <c r="N140" t="n">
-        <v>5.276826591510677</v>
+        <v>5.276816974753548</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B141" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C141" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D141" t="n">
-        <v>94.06137263481666</v>
+        <v>93.64238349983798</v>
       </c>
       <c r="E141" t="n">
-        <v>488.545</v>
+        <v>477.355</v>
       </c>
       <c r="F141" t="n">
-        <v>150.7570278552372</v>
+        <v>154.2910248631246</v>
       </c>
       <c r="G141" t="n">
-        <v>3771.798401581734</v>
+        <v>5669.039064292543</v>
       </c>
       <c r="H141" t="n">
-        <v>-815.7019460284989</v>
+        <v>-1408.571100816436</v>
       </c>
       <c r="I141" t="n">
-        <v>5.435</v>
+        <v>6.08</v>
       </c>
       <c r="J141" t="n">
-        <v>18.015</v>
+        <v>16.34</v>
       </c>
       <c r="K141" t="n">
-        <v>2.915</v>
+        <v>2.65</v>
       </c>
       <c r="L141" t="n">
-        <v>4.095</v>
+        <v>3.91</v>
       </c>
       <c r="M141" t="n">
-        <v>274.630197781941</v>
+        <v>237.9996639240671</v>
       </c>
       <c r="N141" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276816974753548</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B142" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C142" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D142" t="n">
-        <v>94.03916891240675</v>
+        <v>93.66794361387699</v>
       </c>
       <c r="E142" t="n">
-        <v>491.925</v>
+        <v>469.655</v>
       </c>
       <c r="F142" t="n">
-        <v>149.7211814271218</v>
+        <v>156.8206282772181</v>
       </c>
       <c r="G142" t="n">
-        <v>3824.76185420302</v>
+        <v>5741.700304435783</v>
       </c>
       <c r="H142" t="n">
-        <v>-798.6284022285819</v>
+        <v>-1564.573877329694</v>
       </c>
       <c r="I142" t="n">
-        <v>5.465</v>
+        <v>5.755</v>
       </c>
       <c r="J142" t="n">
-        <v>18.35</v>
+        <v>14.94</v>
       </c>
       <c r="K142" t="n">
-        <v>3.01</v>
+        <v>2.409999999999999</v>
       </c>
       <c r="L142" t="n">
-        <v>4.255</v>
+        <v>3.47</v>
       </c>
       <c r="M142" t="n">
-        <v>237.648190391659</v>
+        <v>300.0685310526121</v>
       </c>
       <c r="N142" t="n">
-        <v>5.266216236948693</v>
+        <v>5.27685976993095</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B143" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C143" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D143" t="n">
-        <v>93.99919860159301</v>
+        <v>93.63334590745175</v>
       </c>
       <c r="E143" t="n">
-        <v>499.49</v>
+        <v>471.635</v>
       </c>
       <c r="F143" t="n">
-        <v>147.4535870058197</v>
+        <v>156.1622699196134</v>
       </c>
       <c r="G143" t="n">
-        <v>3927.851428236562</v>
+        <v>5812.801875073716</v>
       </c>
       <c r="H143" t="n">
-        <v>-775.692473444671</v>
+        <v>-1526.631806797996</v>
       </c>
       <c r="I143" t="n">
-        <v>5.625</v>
+        <v>5.895</v>
       </c>
       <c r="J143" t="n">
-        <v>18.82</v>
+        <v>15.385</v>
       </c>
       <c r="K143" t="n">
-        <v>3.105</v>
+        <v>2.505</v>
       </c>
       <c r="L143" t="n">
-        <v>4.44</v>
+        <v>3.655</v>
       </c>
       <c r="M143" t="n">
-        <v>237.6507318640143</v>
+        <v>274.9196996246158</v>
       </c>
       <c r="N143" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276826591510677</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B144" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C144" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D144" t="n">
-        <v>94.04086327642995</v>
+        <v>93.59397703509872</v>
       </c>
       <c r="E144" t="n">
-        <v>484.745</v>
+        <v>476.305</v>
       </c>
       <c r="F144" t="n">
-        <v>151.9388383037202</v>
+        <v>154.6311547717048</v>
       </c>
       <c r="G144" t="n">
-        <v>3905.628293202783</v>
+        <v>5910.743701685864</v>
       </c>
       <c r="H144" t="n">
-        <v>-886.0263704950112</v>
+        <v>-1500.678319208266</v>
       </c>
       <c r="I144" t="n">
-        <v>5.36</v>
+        <v>6.08</v>
       </c>
       <c r="J144" t="n">
-        <v>17.13</v>
+        <v>15.865</v>
       </c>
       <c r="K144" t="n">
-        <v>2.79</v>
+        <v>2.595000000000001</v>
       </c>
       <c r="L144" t="n">
-        <v>3.945</v>
+        <v>3.845000000000001</v>
       </c>
       <c r="M144" t="n">
-        <v>274.6602063166179</v>
+        <v>238.0733419319008</v>
       </c>
       <c r="N144" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276826591510677</v>
       </c>
     </row>
     <row r="145">
@@ -6797,40 +6797,40 @@
         <v>337</v>
       </c>
       <c r="B145" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C145" t="n">
         <v>337</v>
       </c>
       <c r="D145" t="n">
-        <v>94.00996552492347</v>
+        <v>94.06137263481666</v>
       </c>
       <c r="E145" t="n">
-        <v>488.54</v>
+        <v>488.545</v>
       </c>
       <c r="F145" t="n">
-        <v>150.7585707895707</v>
+        <v>150.7570278552372</v>
       </c>
       <c r="G145" t="n">
-        <v>3973.459816008984</v>
+        <v>3771.798401581734</v>
       </c>
       <c r="H145" t="n">
-        <v>-856.3651792493083</v>
+        <v>-815.7019460284989</v>
       </c>
       <c r="I145" t="n">
-        <v>5.405</v>
+        <v>5.435</v>
       </c>
       <c r="J145" t="n">
-        <v>17.48</v>
+        <v>18.015</v>
       </c>
       <c r="K145" t="n">
-        <v>2.89</v>
+        <v>2.915</v>
       </c>
       <c r="L145" t="n">
-        <v>4.105</v>
+        <v>4.095</v>
       </c>
       <c r="M145" t="n">
-        <v>274.6610046422483</v>
+        <v>274.630197781941</v>
       </c>
       <c r="N145" t="n">
         <v>5.266216236948693</v>
@@ -6841,40 +6841,40 @@
         <v>337</v>
       </c>
       <c r="B146" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C146" t="n">
         <v>337</v>
       </c>
       <c r="D146" t="n">
-        <v>93.97787731468296</v>
+        <v>94.03916891240675</v>
       </c>
       <c r="E146" t="n">
-        <v>493.715</v>
+        <v>491.925</v>
       </c>
       <c r="F146" t="n">
-        <v>149.1783562855835</v>
+        <v>149.7211814271218</v>
       </c>
       <c r="G146" t="n">
-        <v>4055.480768439214</v>
+        <v>3824.76185420302</v>
       </c>
       <c r="H146" t="n">
-        <v>-837.237951471551</v>
+        <v>-798.6284022285819</v>
       </c>
       <c r="I146" t="n">
-        <v>5.56</v>
+        <v>5.465</v>
       </c>
       <c r="J146" t="n">
-        <v>17.95</v>
+        <v>18.35</v>
       </c>
       <c r="K146" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="L146" t="n">
-        <v>4.289999999999999</v>
+        <v>4.255</v>
       </c>
       <c r="M146" t="n">
-        <v>237.7059010028416</v>
+        <v>237.648190391659</v>
       </c>
       <c r="N146" t="n">
         <v>5.266216236948693</v>
@@ -6885,40 +6885,40 @@
         <v>337</v>
       </c>
       <c r="B147" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C147" t="n">
         <v>337</v>
       </c>
       <c r="D147" t="n">
-        <v>94.01779240111325</v>
+        <v>93.99919860159301</v>
       </c>
       <c r="E147" t="n">
-        <v>480.955</v>
+        <v>499.49</v>
       </c>
       <c r="F147" t="n">
-        <v>153.136139916493</v>
+        <v>147.4535870058197</v>
       </c>
       <c r="G147" t="n">
-        <v>4040.706191284653</v>
+        <v>3927.851428236562</v>
       </c>
       <c r="H147" t="n">
-        <v>-949.5494989248116</v>
+        <v>-775.692473444671</v>
       </c>
       <c r="I147" t="n">
-        <v>5.29</v>
+        <v>5.625</v>
       </c>
       <c r="J147" t="n">
-        <v>16.35</v>
+        <v>18.82</v>
       </c>
       <c r="K147" t="n">
-        <v>2.685</v>
+        <v>3.105</v>
       </c>
       <c r="L147" t="n">
-        <v>3.81</v>
+        <v>4.44</v>
       </c>
       <c r="M147" t="n">
-        <v>274.6900564190772</v>
+        <v>237.6507318640143</v>
       </c>
       <c r="N147" t="n">
         <v>5.266216236948693</v>
@@ -6929,40 +6929,40 @@
         <v>337</v>
       </c>
       <c r="B148" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C148" t="n">
         <v>337</v>
       </c>
       <c r="D148" t="n">
-        <v>93.98926218137629</v>
+        <v>94.04086327642995</v>
       </c>
       <c r="E148" t="n">
-        <v>484.55</v>
+        <v>484.745</v>
       </c>
       <c r="F148" t="n">
-        <v>151.9999838479762</v>
+        <v>151.9388383037202</v>
       </c>
       <c r="G148" t="n">
-        <v>4106.38312675214</v>
+        <v>3905.628293202783</v>
       </c>
       <c r="H148" t="n">
-        <v>-925.2453286608534</v>
+        <v>-886.0263704950112</v>
       </c>
       <c r="I148" t="n">
-        <v>5.350000000000001</v>
+        <v>5.36</v>
       </c>
       <c r="J148" t="n">
-        <v>16.715</v>
+        <v>17.13</v>
       </c>
       <c r="K148" t="n">
-        <v>2.774999999999999</v>
+        <v>2.79</v>
       </c>
       <c r="L148" t="n">
-        <v>3.97</v>
+        <v>3.945</v>
       </c>
       <c r="M148" t="n">
-        <v>274.6937313449783</v>
+        <v>274.6602063166179</v>
       </c>
       <c r="N148" t="n">
         <v>5.266216236948693</v>
@@ -6973,40 +6973,40 @@
         <v>337</v>
       </c>
       <c r="B149" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C149" t="n">
         <v>337</v>
       </c>
       <c r="D149" t="n">
-        <v>93.95005843954007</v>
+        <v>94.00996552492347</v>
       </c>
       <c r="E149" t="n">
-        <v>490.355</v>
+        <v>488.54</v>
       </c>
       <c r="F149" t="n">
-        <v>150.2005530147278</v>
+        <v>150.7585707895707</v>
       </c>
       <c r="G149" t="n">
-        <v>4202.475191423594</v>
+        <v>3973.459816008984</v>
       </c>
       <c r="H149" t="n">
-        <v>-897.7375467634768</v>
+        <v>-856.3651792493083</v>
       </c>
       <c r="I149" t="n">
-        <v>5.51</v>
+        <v>5.405</v>
       </c>
       <c r="J149" t="n">
-        <v>17.185</v>
+        <v>17.48</v>
       </c>
       <c r="K149" t="n">
-        <v>2.875</v>
+        <v>2.89</v>
       </c>
       <c r="L149" t="n">
-        <v>4.164999999999999</v>
+        <v>4.105</v>
       </c>
       <c r="M149" t="n">
-        <v>237.7804262443778</v>
+        <v>274.6610046422483</v>
       </c>
       <c r="N149" t="n">
         <v>5.266216236948693</v>
@@ -7014,178 +7014,178 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B150" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C150" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D150" t="n">
-        <v>93.39160536374426</v>
+        <v>93.97787731468296</v>
       </c>
       <c r="E150" t="n">
-        <v>566.975</v>
+        <v>493.715</v>
       </c>
       <c r="F150" t="n">
-        <v>129.9027155933451</v>
+        <v>149.1783562855835</v>
       </c>
       <c r="G150" t="n">
-        <v>5881.019688831716</v>
+        <v>4055.480768439214</v>
       </c>
       <c r="H150" t="n">
-        <v>-824.2581740182918</v>
+        <v>-837.237951471551</v>
       </c>
       <c r="I150" t="n">
-        <v>5.25</v>
+        <v>5.56</v>
       </c>
       <c r="J150" t="n">
-        <v>15.98</v>
+        <v>17.95</v>
       </c>
       <c r="K150" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="L150" t="n">
-        <v>3.7</v>
+        <v>4.289999999999999</v>
       </c>
       <c r="M150" t="n">
-        <v>297.6108788591611</v>
+        <v>237.7059010028416</v>
       </c>
       <c r="N150" t="n">
-        <v>5.307415007540252</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B151" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C151" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D151" t="n">
-        <v>93.00520274446839</v>
+        <v>94.01779240111325</v>
       </c>
       <c r="E151" t="n">
-        <v>600</v>
+        <v>480.955</v>
       </c>
       <c r="F151" t="n">
-        <v>122.7526536225614</v>
+        <v>153.136139916493</v>
       </c>
       <c r="G151" t="n">
-        <v>6705.467309209334</v>
+        <v>4040.706191284653</v>
       </c>
       <c r="H151" t="n">
-        <v>-430.9480564697961</v>
+        <v>-949.5494989248116</v>
       </c>
       <c r="I151" t="n">
-        <v>5.445</v>
+        <v>5.29</v>
       </c>
       <c r="J151" t="n">
-        <v>16.495</v>
+        <v>16.35</v>
       </c>
       <c r="K151" t="n">
-        <v>2.82</v>
+        <v>2.685</v>
       </c>
       <c r="L151" t="n">
-        <v>3.96</v>
+        <v>3.81</v>
       </c>
       <c r="M151" t="n">
-        <v>224.2093764810274</v>
+        <v>274.6900564190772</v>
       </c>
       <c r="N151" t="n">
-        <v>5.302146700941705</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B152" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C152" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D152" t="n">
-        <v>93.20323324197504</v>
+        <v>93.98926218137629</v>
       </c>
       <c r="E152" t="n">
-        <v>600</v>
+        <v>484.55</v>
       </c>
       <c r="F152" t="n">
-        <v>122.7526536225614</v>
+        <v>151.9999838479762</v>
       </c>
       <c r="G152" t="n">
-        <v>6184.948622227217</v>
+        <v>4106.38312675214</v>
       </c>
       <c r="H152" t="n">
-        <v>-532.8396788580467</v>
+        <v>-925.2453286608534</v>
       </c>
       <c r="I152" t="n">
-        <v>5.705</v>
+        <v>5.350000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>17.07</v>
+        <v>16.715</v>
       </c>
       <c r="K152" t="n">
-        <v>3</v>
+        <v>2.774999999999999</v>
       </c>
       <c r="L152" t="n">
-        <v>4.234999999999999</v>
+        <v>3.97</v>
       </c>
       <c r="M152" t="n">
-        <v>224.1785042995384</v>
+        <v>274.6937313449783</v>
       </c>
       <c r="N152" t="n">
-        <v>5.299827897755545</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B153" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C153" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D153" t="n">
-        <v>93.37405640168669</v>
+        <v>93.95005843954007</v>
       </c>
       <c r="E153" t="n">
-        <v>553</v>
+        <v>490.355</v>
       </c>
       <c r="F153" t="n">
-        <v>133.1855193011517</v>
+        <v>150.2005530147278</v>
       </c>
       <c r="G153" t="n">
-        <v>6043.812569803414</v>
+        <v>4202.475191423594</v>
       </c>
       <c r="H153" t="n">
-        <v>-934.7605154360626</v>
+        <v>-897.7375467634768</v>
       </c>
       <c r="I153" t="n">
-        <v>5.215</v>
+        <v>5.51</v>
       </c>
       <c r="J153" t="n">
-        <v>15.32</v>
+        <v>17.185</v>
       </c>
       <c r="K153" t="n">
-        <v>2.545</v>
+        <v>2.875</v>
       </c>
       <c r="L153" t="n">
-        <v>3.605</v>
+        <v>4.164999999999999</v>
       </c>
       <c r="M153" t="n">
-        <v>300.0100695797773</v>
+        <v>237.7804262443778</v>
       </c>
       <c r="N153" t="n">
-        <v>5.307415007540252</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="154">
@@ -7193,43 +7193,43 @@
         <v>348</v>
       </c>
       <c r="B154" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C154" t="n">
         <v>348</v>
       </c>
       <c r="D154" t="n">
-        <v>92.9160562125255</v>
+        <v>93.39160536374426</v>
       </c>
       <c r="E154" t="n">
-        <v>600</v>
+        <v>566.975</v>
       </c>
       <c r="F154" t="n">
-        <v>122.7526536225614</v>
+        <v>129.9027155933451</v>
       </c>
       <c r="G154" t="n">
-        <v>6996.972720723452</v>
+        <v>5881.019688831716</v>
       </c>
       <c r="H154" t="n">
-        <v>-444.1735990791756</v>
+        <v>-824.2581740182918</v>
       </c>
       <c r="I154" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="J154" t="n">
-        <v>15.82</v>
+        <v>15.98</v>
       </c>
       <c r="K154" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="L154" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="M154" t="n">
-        <v>224.2907156932552</v>
+        <v>297.6108788591611</v>
       </c>
       <c r="N154" t="n">
-        <v>5.301625897179865</v>
+        <v>5.307415007540252</v>
       </c>
     </row>
     <row r="155">
@@ -7237,13 +7237,13 @@
         <v>348</v>
       </c>
       <c r="B155" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C155" t="n">
         <v>348</v>
       </c>
       <c r="D155" t="n">
-        <v>93.1227778417684</v>
+        <v>93.00520274446839</v>
       </c>
       <c r="E155" t="n">
         <v>600</v>
@@ -7252,28 +7252,28 @@
         <v>122.7526536225614</v>
       </c>
       <c r="G155" t="n">
-        <v>6472.578424628873</v>
+        <v>6705.467309209334</v>
       </c>
       <c r="H155" t="n">
-        <v>-569.462016244643</v>
+        <v>-430.9480564697961</v>
       </c>
       <c r="I155" t="n">
-        <v>5.655</v>
+        <v>5.445</v>
       </c>
       <c r="J155" t="n">
-        <v>16.39</v>
+        <v>16.495</v>
       </c>
       <c r="K155" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="L155" t="n">
-        <v>4.125</v>
+        <v>3.96</v>
       </c>
       <c r="M155" t="n">
-        <v>224.2387539633841</v>
+        <v>224.2093764810274</v>
       </c>
       <c r="N155" t="n">
-        <v>5.299141949620611</v>
+        <v>5.302146700941705</v>
       </c>
     </row>
     <row r="156">
@@ -7281,43 +7281,43 @@
         <v>348</v>
       </c>
       <c r="B156" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C156" t="n">
         <v>348</v>
       </c>
       <c r="D156" t="n">
-        <v>93.31618410638438</v>
+        <v>93.20323324197504</v>
       </c>
       <c r="E156" t="n">
-        <v>546.885</v>
+        <v>600</v>
       </c>
       <c r="F156" t="n">
-        <v>134.6747344936081</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G156" t="n">
-        <v>6255.292482077637</v>
+        <v>6184.948622227217</v>
       </c>
       <c r="H156" t="n">
-        <v>-965.6574981168902</v>
+        <v>-532.8396788580467</v>
       </c>
       <c r="I156" t="n">
-        <v>5.19</v>
+        <v>5.705</v>
       </c>
       <c r="J156" t="n">
-        <v>14.74</v>
+        <v>17.07</v>
       </c>
       <c r="K156" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="L156" t="n">
-        <v>3.53</v>
+        <v>4.234999999999999</v>
       </c>
       <c r="M156" t="n">
-        <v>300.0262041365498</v>
+        <v>224.1785042995384</v>
       </c>
       <c r="N156" t="n">
-        <v>5.307415007540252</v>
+        <v>5.299827897755545</v>
       </c>
     </row>
     <row r="157">
@@ -7325,43 +7325,43 @@
         <v>348</v>
       </c>
       <c r="B157" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C157" t="n">
         <v>348</v>
       </c>
       <c r="D157" t="n">
-        <v>92.82946804348842</v>
+        <v>93.37405640168669</v>
       </c>
       <c r="E157" t="n">
-        <v>600</v>
+        <v>553</v>
       </c>
       <c r="F157" t="n">
-        <v>122.7526536225614</v>
+        <v>133.1855193011517</v>
       </c>
       <c r="G157" t="n">
-        <v>7290.003077374275</v>
+        <v>6043.812569803414</v>
       </c>
       <c r="H157" t="n">
-        <v>-467.1081029056169</v>
+        <v>-934.7605154360626</v>
       </c>
       <c r="I157" t="n">
-        <v>5.37</v>
+        <v>5.215</v>
       </c>
       <c r="J157" t="n">
-        <v>15.24</v>
+        <v>15.32</v>
       </c>
       <c r="K157" t="n">
-        <v>2.655</v>
+        <v>2.545</v>
       </c>
       <c r="L157" t="n">
-        <v>3.775</v>
+        <v>3.605</v>
       </c>
       <c r="M157" t="n">
-        <v>224.3690081541812</v>
+        <v>300.0100695797773</v>
       </c>
       <c r="N157" t="n">
-        <v>5.300553327759205</v>
+        <v>5.307415007540252</v>
       </c>
     </row>
     <row r="158">
@@ -7369,13 +7369,13 @@
         <v>348</v>
       </c>
       <c r="B158" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C158" t="n">
         <v>348</v>
       </c>
       <c r="D158" t="n">
-        <v>93.04712082832047</v>
+        <v>92.9160562125255</v>
       </c>
       <c r="E158" t="n">
         <v>600</v>
@@ -7384,204 +7384,204 @@
         <v>122.7526536225614</v>
       </c>
       <c r="G158" t="n">
-        <v>6776.654490686403</v>
+        <v>6996.972720723452</v>
       </c>
       <c r="H158" t="n">
-        <v>-638.1252760577953</v>
+        <v>-444.1735990791756</v>
       </c>
       <c r="I158" t="n">
-        <v>5.63</v>
+        <v>5.4</v>
       </c>
       <c r="J158" t="n">
-        <v>15.81</v>
+        <v>15.82</v>
       </c>
       <c r="K158" t="n">
-        <v>2.835</v>
+        <v>2.73</v>
       </c>
       <c r="L158" t="n">
-        <v>4.045</v>
+        <v>3.86</v>
       </c>
       <c r="M158" t="n">
-        <v>224.3388964030367</v>
+        <v>224.2907156932552</v>
       </c>
       <c r="N158" t="n">
-        <v>5.297623858839702</v>
+        <v>5.301625897179865</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B159" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C159" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D159" t="n">
-        <v>93.60780736497125</v>
+        <v>93.1227778417684</v>
       </c>
       <c r="E159" t="n">
-        <v>478.64</v>
+        <v>600</v>
       </c>
       <c r="F159" t="n">
-        <v>153.8768012985477</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G159" t="n">
-        <v>5782.171879982329</v>
+        <v>6472.578424628873</v>
       </c>
       <c r="H159" t="n">
-        <v>-1413.492709881508</v>
+        <v>-569.462016244643</v>
       </c>
       <c r="I159" t="n">
-        <v>5.815</v>
+        <v>5.655</v>
       </c>
       <c r="J159" t="n">
-        <v>16.535</v>
+        <v>16.39</v>
       </c>
       <c r="K159" t="n">
-        <v>2.58</v>
+        <v>2.91</v>
       </c>
       <c r="L159" t="n">
-        <v>3.65</v>
+        <v>4.125</v>
       </c>
       <c r="M159" t="n">
-        <v>287.5255286332636</v>
+        <v>224.2387539633841</v>
       </c>
       <c r="N159" t="n">
-        <v>5.272856452064412</v>
+        <v>5.299141949620611</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B160" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C160" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D160" t="n">
-        <v>93.55536518664927</v>
+        <v>93.31618410638438</v>
       </c>
       <c r="E160" t="n">
-        <v>483.25</v>
+        <v>546.885</v>
       </c>
       <c r="F160" t="n">
-        <v>152.4088818904022</v>
+        <v>134.6747344936081</v>
       </c>
       <c r="G160" t="n">
-        <v>5900.50579425959</v>
+        <v>6255.292482077637</v>
       </c>
       <c r="H160" t="n">
-        <v>-1366.665182830038</v>
+        <v>-965.6574981168902</v>
       </c>
       <c r="I160" t="n">
-        <v>6.045</v>
+        <v>5.19</v>
       </c>
       <c r="J160" t="n">
-        <v>16.97</v>
+        <v>14.74</v>
       </c>
       <c r="K160" t="n">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="L160" t="n">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="M160" t="n">
-        <v>287.5256080259855</v>
+        <v>300.0262041365498</v>
       </c>
       <c r="N160" t="n">
-        <v>5.272279725385319</v>
+        <v>5.307415007540252</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B161" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C161" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D161" t="n">
-        <v>93.49466695286711</v>
+        <v>92.82946804348842</v>
       </c>
       <c r="E161" t="n">
-        <v>490.4</v>
+        <v>600</v>
       </c>
       <c r="F161" t="n">
-        <v>150.1867703375548</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G161" t="n">
-        <v>6050.57464560456</v>
+        <v>7290.003077374275</v>
       </c>
       <c r="H161" t="n">
-        <v>-1325.721340913737</v>
+        <v>-467.1081029056169</v>
       </c>
       <c r="I161" t="n">
-        <v>6.315</v>
+        <v>5.37</v>
       </c>
       <c r="J161" t="n">
-        <v>17.44</v>
+        <v>15.24</v>
       </c>
       <c r="K161" t="n">
-        <v>2.775</v>
+        <v>2.655</v>
       </c>
       <c r="L161" t="n">
-        <v>4.04</v>
+        <v>3.775</v>
       </c>
       <c r="M161" t="n">
-        <v>241.1186174329819</v>
+        <v>224.3690081541812</v>
       </c>
       <c r="N161" t="n">
-        <v>5.272279725385319</v>
+        <v>5.300553327759205</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B162" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C162" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D162" t="n">
-        <v>93.56591019123778</v>
+        <v>93.04712082832047</v>
       </c>
       <c r="E162" t="n">
-        <v>475.78</v>
+        <v>600</v>
       </c>
       <c r="F162" t="n">
-        <v>154.8017827011158</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G162" t="n">
-        <v>6013.65684137698</v>
+        <v>6776.654490686403</v>
       </c>
       <c r="H162" t="n">
-        <v>-1516.084332000202</v>
+        <v>-638.1252760577953</v>
       </c>
       <c r="I162" t="n">
-        <v>5.795</v>
+        <v>5.63</v>
       </c>
       <c r="J162" t="n">
-        <v>15.87</v>
+        <v>15.81</v>
       </c>
       <c r="K162" t="n">
-        <v>2.48</v>
+        <v>2.835</v>
       </c>
       <c r="L162" t="n">
-        <v>3.545</v>
+        <v>4.045</v>
       </c>
       <c r="M162" t="n">
-        <v>287.5548554343529</v>
+        <v>224.3388964030367</v>
       </c>
       <c r="N162" t="n">
-        <v>5.272874316835532</v>
+        <v>5.297623858839702</v>
       </c>
     </row>
     <row r="163">
@@ -7589,43 +7589,43 @@
         <v>357</v>
       </c>
       <c r="B163" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C163" t="n">
         <v>357</v>
       </c>
       <c r="D163" t="n">
-        <v>93.52302999996925</v>
+        <v>93.60780736497125</v>
       </c>
       <c r="E163" t="n">
-        <v>479.245</v>
+        <v>478.64</v>
       </c>
       <c r="F163" t="n">
-        <v>153.6825468675455</v>
+        <v>153.8768012985477</v>
       </c>
       <c r="G163" t="n">
-        <v>6108.646282534939</v>
+        <v>5782.171879982329</v>
       </c>
       <c r="H163" t="n">
-        <v>-1476.036436451451</v>
+        <v>-1413.492709881508</v>
       </c>
       <c r="I163" t="n">
-        <v>6.01</v>
+        <v>5.815</v>
       </c>
       <c r="J163" t="n">
-        <v>16.285</v>
+        <v>16.535</v>
       </c>
       <c r="K163" t="n">
-        <v>2.575</v>
+        <v>2.58</v>
       </c>
       <c r="L163" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="M163" t="n">
-        <v>287.5530010097403</v>
+        <v>287.5255286332636</v>
       </c>
       <c r="N163" t="n">
-        <v>5.272301741770099</v>
+        <v>5.272856452064412</v>
       </c>
     </row>
     <row r="164">
@@ -7633,43 +7633,43 @@
         <v>357</v>
       </c>
       <c r="B164" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C164" t="n">
         <v>357</v>
       </c>
       <c r="D164" t="n">
-        <v>93.47838239701272</v>
+        <v>93.55536518664927</v>
       </c>
       <c r="E164" t="n">
-        <v>483.715</v>
+        <v>483.25</v>
       </c>
       <c r="F164" t="n">
-        <v>152.2623697291522</v>
+        <v>152.4088818904022</v>
       </c>
       <c r="G164" t="n">
-        <v>6214.272162782726</v>
+        <v>5900.50579425959</v>
       </c>
       <c r="H164" t="n">
-        <v>-1441.141490868092</v>
+        <v>-1366.665182830038</v>
       </c>
       <c r="I164" t="n">
-        <v>6.27</v>
+        <v>6.045</v>
       </c>
       <c r="J164" t="n">
-        <v>16.745</v>
+        <v>16.97</v>
       </c>
       <c r="K164" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="L164" t="n">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="M164" t="n">
-        <v>241.1753300195797</v>
+        <v>287.5256080259855</v>
       </c>
       <c r="N164" t="n">
-        <v>5.272301741770099</v>
+        <v>5.272279725385319</v>
       </c>
     </row>
     <row r="165">
@@ -7677,43 +7677,43 @@
         <v>357</v>
       </c>
       <c r="B165" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C165" t="n">
         <v>357</v>
       </c>
       <c r="D165" t="n">
-        <v>93.53083417295163</v>
+        <v>93.49466695286711</v>
       </c>
       <c r="E165" t="n">
-        <v>472.795</v>
+        <v>490.4</v>
       </c>
       <c r="F165" t="n">
-        <v>155.7791266268401</v>
+        <v>150.1867703375548</v>
       </c>
       <c r="G165" t="n">
-        <v>6230.480796751935</v>
+        <v>6050.57464560456</v>
       </c>
       <c r="H165" t="n">
-        <v>-1625.672614200203</v>
+        <v>-1325.721340913737</v>
       </c>
       <c r="I165" t="n">
-        <v>5.79</v>
+        <v>6.315</v>
       </c>
       <c r="J165" t="n">
-        <v>15.31</v>
+        <v>17.44</v>
       </c>
       <c r="K165" t="n">
-        <v>2.415</v>
+        <v>2.775</v>
       </c>
       <c r="L165" t="n">
-        <v>3.48</v>
+        <v>4.04</v>
       </c>
       <c r="M165" t="n">
-        <v>287.5847306530924</v>
+        <v>241.1186174329819</v>
       </c>
       <c r="N165" t="n">
-        <v>5.272891224655314</v>
+        <v>5.272279725385319</v>
       </c>
     </row>
     <row r="166">
@@ -7721,43 +7721,43 @@
         <v>357</v>
       </c>
       <c r="B166" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C166" t="n">
         <v>357</v>
       </c>
       <c r="D166" t="n">
-        <v>93.48377917695814</v>
+        <v>93.56591019123778</v>
       </c>
       <c r="E166" t="n">
-        <v>476.165</v>
+        <v>475.78</v>
       </c>
       <c r="F166" t="n">
-        <v>154.6766187635313</v>
+        <v>154.8017827011158</v>
       </c>
       <c r="G166" t="n">
-        <v>6332.532133712925</v>
+        <v>6013.65684137698</v>
       </c>
       <c r="H166" t="n">
-        <v>-1579.555608603629</v>
+        <v>-1516.084332000202</v>
       </c>
       <c r="I166" t="n">
-        <v>5.99</v>
+        <v>5.795</v>
       </c>
       <c r="J166" t="n">
-        <v>15.71</v>
+        <v>15.87</v>
       </c>
       <c r="K166" t="n">
-        <v>2.510000000000001</v>
+        <v>2.48</v>
       </c>
       <c r="L166" t="n">
-        <v>3.65</v>
+        <v>3.545</v>
       </c>
       <c r="M166" t="n">
-        <v>287.5869654449736</v>
+        <v>287.5548554343529</v>
       </c>
       <c r="N166" t="n">
-        <v>5.272277243669286</v>
+        <v>5.272874316835532</v>
       </c>
     </row>
     <row r="167">
@@ -7765,219 +7765,219 @@
         <v>357</v>
       </c>
       <c r="B167" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C167" t="n">
         <v>357</v>
       </c>
       <c r="D167" t="n">
-        <v>93.4130935470521</v>
+        <v>93.52302999996925</v>
       </c>
       <c r="E167" t="n">
-        <v>482.785</v>
+        <v>479.245</v>
       </c>
       <c r="F167" t="n">
-        <v>152.5556762814438</v>
+        <v>153.6825468675455</v>
       </c>
       <c r="G167" t="n">
-        <v>6499.879389135563</v>
+        <v>6108.646282534939</v>
       </c>
       <c r="H167" t="n">
-        <v>-1524.493679029795</v>
+        <v>-1476.036436451451</v>
       </c>
       <c r="I167" t="n">
-        <v>6.25</v>
+        <v>6.01</v>
       </c>
       <c r="J167" t="n">
-        <v>16.175</v>
+        <v>16.285</v>
       </c>
       <c r="K167" t="n">
-        <v>2.605</v>
+        <v>2.575</v>
       </c>
       <c r="L167" t="n">
-        <v>3.83</v>
+        <v>3.73</v>
       </c>
       <c r="M167" t="n">
-        <v>241.2524692211172</v>
+        <v>287.5530010097403</v>
       </c>
       <c r="N167" t="n">
-        <v>5.272277243669286</v>
+        <v>5.272301741770099</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B168" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C168" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D168" t="n">
-        <v>81.17447304756479</v>
+        <v>93.47838239701272</v>
       </c>
       <c r="E168" t="n">
-        <v>472.935</v>
+        <v>483.715</v>
       </c>
       <c r="F168" t="n">
-        <v>155.7330123030372</v>
+        <v>152.2623697291522</v>
       </c>
       <c r="G168" t="n">
-        <v>52513.7615386265</v>
+        <v>6214.272162782726</v>
       </c>
       <c r="H168" t="n">
-        <v>-8235.246021061805</v>
+        <v>-1441.141490868092</v>
       </c>
       <c r="I168" t="n">
-        <v>5.715</v>
+        <v>6.27</v>
       </c>
       <c r="J168" t="n">
-        <v>16.2</v>
+        <v>16.745</v>
       </c>
       <c r="K168" t="n">
-        <v>2.699999999999999</v>
+        <v>2.67</v>
       </c>
       <c r="L168" t="n">
-        <v>3.78</v>
+        <v>3.91</v>
       </c>
       <c r="M168" t="n">
-        <v>299.523947455675</v>
+        <v>241.1753300195797</v>
       </c>
       <c r="N168" t="n">
-        <v>5.319434242601793</v>
+        <v>5.272301741770099</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B169" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C169" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D169" t="n">
-        <v>81.07936296066114</v>
+        <v>93.53083417295163</v>
       </c>
       <c r="E169" t="n">
-        <v>474.66</v>
+        <v>472.795</v>
       </c>
       <c r="F169" t="n">
-        <v>155.1670504646207</v>
+        <v>155.7791266268401</v>
       </c>
       <c r="G169" t="n">
-        <v>52717.38553865819</v>
+        <v>6230.480796751935</v>
       </c>
       <c r="H169" t="n">
-        <v>-8189.63592603311</v>
+        <v>-1625.672614200203</v>
       </c>
       <c r="I169" t="n">
-        <v>5.850000000000001</v>
+        <v>5.79</v>
       </c>
       <c r="J169" t="n">
-        <v>16.53</v>
+        <v>15.31</v>
       </c>
       <c r="K169" t="n">
-        <v>2.76</v>
+        <v>2.415</v>
       </c>
       <c r="L169" t="n">
-        <v>3.96</v>
+        <v>3.48</v>
       </c>
       <c r="M169" t="n">
-        <v>299.522924401521</v>
+        <v>287.5847306530924</v>
       </c>
       <c r="N169" t="n">
-        <v>5.324752570945306</v>
+        <v>5.272891224655314</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B170" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C170" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D170" t="n">
-        <v>80.81584820022067</v>
+        <v>93.48377917695814</v>
       </c>
       <c r="E170" t="n">
-        <v>478.805</v>
+        <v>476.165</v>
       </c>
       <c r="F170" t="n">
-        <v>153.8237741325527</v>
+        <v>154.6766187635313</v>
       </c>
       <c r="G170" t="n">
-        <v>53272.7003570364</v>
+        <v>6332.532133712925</v>
       </c>
       <c r="H170" t="n">
-        <v>-8083.121202495097</v>
+        <v>-1579.555608603629</v>
       </c>
       <c r="I170" t="n">
-        <v>5.985</v>
+        <v>5.99</v>
       </c>
       <c r="J170" t="n">
-        <v>16.875</v>
+        <v>15.71</v>
       </c>
       <c r="K170" t="n">
-        <v>2.825</v>
+        <v>2.510000000000001</v>
       </c>
       <c r="L170" t="n">
-        <v>4.09</v>
+        <v>3.65</v>
       </c>
       <c r="M170" t="n">
-        <v>299.5218833934957</v>
+        <v>287.5869654449736</v>
       </c>
       <c r="N170" t="n">
-        <v>5.336686842591843</v>
+        <v>5.272277243669286</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B171" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C171" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D171" t="n">
-        <v>80.72172269299428</v>
+        <v>93.4130935470521</v>
       </c>
       <c r="E171" t="n">
-        <v>469.35</v>
+        <v>482.785</v>
       </c>
       <c r="F171" t="n">
-        <v>156.9225357910661</v>
+        <v>152.5556762814438</v>
       </c>
       <c r="G171" t="n">
-        <v>54466.95159486185</v>
+        <v>6499.879389135563</v>
       </c>
       <c r="H171" t="n">
-        <v>-8508.821596508054</v>
+        <v>-1524.493679029795</v>
       </c>
       <c r="I171" t="n">
-        <v>5.575</v>
+        <v>6.25</v>
       </c>
       <c r="J171" t="n">
-        <v>15.43</v>
+        <v>16.175</v>
       </c>
       <c r="K171" t="n">
-        <v>2.555</v>
+        <v>2.605</v>
       </c>
       <c r="L171" t="n">
-        <v>3.59</v>
+        <v>3.83</v>
       </c>
       <c r="M171" t="n">
-        <v>300.0160827483674</v>
+        <v>241.2524692211172</v>
       </c>
       <c r="N171" t="n">
-        <v>5.403059520493683</v>
+        <v>5.272277243669286</v>
       </c>
     </row>
     <row r="172">
@@ -7985,43 +7985,43 @@
         <v>413</v>
       </c>
       <c r="B172" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C172" t="n">
         <v>413</v>
       </c>
       <c r="D172" t="n">
-        <v>80.65170135905515</v>
+        <v>81.17447304756479</v>
       </c>
       <c r="E172" t="n">
-        <v>470.92</v>
+        <v>472.935</v>
       </c>
       <c r="F172" t="n">
-        <v>156.3993718116386</v>
+        <v>155.7330123030372</v>
       </c>
       <c r="G172" t="n">
-        <v>54646.47492184487</v>
+        <v>52513.7615386265</v>
       </c>
       <c r="H172" t="n">
-        <v>-8484.427867905555</v>
+        <v>-8235.246021061805</v>
       </c>
       <c r="I172" t="n">
-        <v>5.725000000000001</v>
+        <v>5.715</v>
       </c>
       <c r="J172" t="n">
-        <v>15.775</v>
+        <v>16.2</v>
       </c>
       <c r="K172" t="n">
-        <v>2.62</v>
+        <v>2.699999999999999</v>
       </c>
       <c r="L172" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="M172" t="n">
-        <v>300.016082197001</v>
+        <v>299.523947455675</v>
       </c>
       <c r="N172" t="n">
-        <v>5.403205709217267</v>
+        <v>5.319434242601793</v>
       </c>
     </row>
     <row r="173">
@@ -8029,43 +8029,43 @@
         <v>413</v>
       </c>
       <c r="B173" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C173" t="n">
         <v>413</v>
       </c>
       <c r="D173" t="n">
-        <v>80.38307485323961</v>
+        <v>81.07936296066114</v>
       </c>
       <c r="E173" t="n">
-        <v>475.005</v>
+        <v>474.66</v>
       </c>
       <c r="F173" t="n">
-        <v>155.0543513721684</v>
+        <v>155.1670504646207</v>
       </c>
       <c r="G173" t="n">
-        <v>55198.94423016463</v>
+        <v>52717.38553865819</v>
       </c>
       <c r="H173" t="n">
-        <v>-8367.536026770043</v>
+        <v>-8189.63592603311</v>
       </c>
       <c r="I173" t="n">
-        <v>5.86</v>
+        <v>5.850000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>16.115</v>
+        <v>16.53</v>
       </c>
       <c r="K173" t="n">
-        <v>2.680000000000001</v>
+        <v>2.76</v>
       </c>
       <c r="L173" t="n">
-        <v>3.905</v>
+        <v>3.96</v>
       </c>
       <c r="M173" t="n">
-        <v>300.0160823418269</v>
+        <v>299.522924401521</v>
       </c>
       <c r="N173" t="n">
-        <v>5.417753888744446</v>
+        <v>5.324752570945306</v>
       </c>
     </row>
     <row r="174">
@@ -8073,43 +8073,43 @@
         <v>413</v>
       </c>
       <c r="B174" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C174" t="n">
         <v>413</v>
       </c>
       <c r="D174" t="n">
-        <v>80.30660156667822</v>
+        <v>80.81584820022067</v>
       </c>
       <c r="E174" t="n">
-        <v>466.08</v>
+        <v>478.805</v>
       </c>
       <c r="F174" t="n">
-        <v>158.0234984842449</v>
+        <v>153.8237741325527</v>
       </c>
       <c r="G174" t="n">
-        <v>56344.28841909636</v>
+        <v>53272.7003570364</v>
       </c>
       <c r="H174" t="n">
-        <v>-8782.699860939843</v>
+        <v>-8083.121202495097</v>
       </c>
       <c r="I174" t="n">
-        <v>5.49</v>
+        <v>5.985</v>
       </c>
       <c r="J174" t="n">
-        <v>14.795</v>
+        <v>16.875</v>
       </c>
       <c r="K174" t="n">
-        <v>2.44</v>
+        <v>2.825</v>
       </c>
       <c r="L174" t="n">
-        <v>3.46</v>
+        <v>4.09</v>
       </c>
       <c r="M174" t="n">
-        <v>300.0319778485202</v>
+        <v>299.5218833934957</v>
       </c>
       <c r="N174" t="n">
-        <v>5.481264488374775</v>
+        <v>5.336686842591843</v>
       </c>
     </row>
     <row r="175">
@@ -8117,43 +8117,43 @@
         <v>413</v>
       </c>
       <c r="B175" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C175" t="n">
         <v>413</v>
       </c>
       <c r="D175" t="n">
-        <v>80.23709110490057</v>
+        <v>80.72172269299428</v>
       </c>
       <c r="E175" t="n">
-        <v>467.19</v>
+        <v>469.35</v>
       </c>
       <c r="F175" t="n">
-        <v>157.6480493450991</v>
+        <v>156.9225357910661</v>
       </c>
       <c r="G175" t="n">
-        <v>56498.47235689612</v>
+        <v>54466.95159486185</v>
       </c>
       <c r="H175" t="n">
-        <v>-8741.236739706075</v>
+        <v>-8508.821596508054</v>
       </c>
       <c r="I175" t="n">
-        <v>5.615</v>
+        <v>5.575</v>
       </c>
       <c r="J175" t="n">
-        <v>15.11</v>
+        <v>15.43</v>
       </c>
       <c r="K175" t="n">
-        <v>2.5</v>
+        <v>2.555</v>
       </c>
       <c r="L175" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="M175" t="n">
-        <v>300.0319778451221</v>
+        <v>300.0160827483674</v>
       </c>
       <c r="N175" t="n">
-        <v>5.481361532008621</v>
+        <v>5.403059520493683</v>
       </c>
     </row>
     <row r="176">
@@ -8161,42 +8161,218 @@
         <v>413</v>
       </c>
       <c r="B176" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C176" t="n">
         <v>413</v>
       </c>
       <c r="D176" t="n">
+        <v>80.65170135905515</v>
+      </c>
+      <c r="E176" t="n">
+        <v>470.92</v>
+      </c>
+      <c r="F176" t="n">
+        <v>156.3993718116386</v>
+      </c>
+      <c r="G176" t="n">
+        <v>54646.47492184487</v>
+      </c>
+      <c r="H176" t="n">
+        <v>-8484.427867905555</v>
+      </c>
+      <c r="I176" t="n">
+        <v>5.725000000000001</v>
+      </c>
+      <c r="J176" t="n">
+        <v>15.775</v>
+      </c>
+      <c r="K176" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L176" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M176" t="n">
+        <v>300.016082197001</v>
+      </c>
+      <c r="N176" t="n">
+        <v>5.403205709217267</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>413</v>
+      </c>
+      <c r="B177" t="n">
+        <v>186</v>
+      </c>
+      <c r="C177" t="n">
+        <v>413</v>
+      </c>
+      <c r="D177" t="n">
+        <v>80.38307485323961</v>
+      </c>
+      <c r="E177" t="n">
+        <v>475.005</v>
+      </c>
+      <c r="F177" t="n">
+        <v>155.0543513721684</v>
+      </c>
+      <c r="G177" t="n">
+        <v>55198.94423016463</v>
+      </c>
+      <c r="H177" t="n">
+        <v>-8367.536026770043</v>
+      </c>
+      <c r="I177" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="J177" t="n">
+        <v>16.115</v>
+      </c>
+      <c r="K177" t="n">
+        <v>2.680000000000001</v>
+      </c>
+      <c r="L177" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="M177" t="n">
+        <v>300.0160823418269</v>
+      </c>
+      <c r="N177" t="n">
+        <v>5.417753888744446</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>413</v>
+      </c>
+      <c r="B178" t="n">
+        <v>187</v>
+      </c>
+      <c r="C178" t="n">
+        <v>413</v>
+      </c>
+      <c r="D178" t="n">
+        <v>80.30660156667822</v>
+      </c>
+      <c r="E178" t="n">
+        <v>466.08</v>
+      </c>
+      <c r="F178" t="n">
+        <v>158.0234984842449</v>
+      </c>
+      <c r="G178" t="n">
+        <v>56344.28841909636</v>
+      </c>
+      <c r="H178" t="n">
+        <v>-8782.699860939843</v>
+      </c>
+      <c r="I178" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="J178" t="n">
+        <v>14.795</v>
+      </c>
+      <c r="K178" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L178" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="M178" t="n">
+        <v>300.0319778485202</v>
+      </c>
+      <c r="N178" t="n">
+        <v>5.481264488374775</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>413</v>
+      </c>
+      <c r="B179" t="n">
+        <v>188</v>
+      </c>
+      <c r="C179" t="n">
+        <v>413</v>
+      </c>
+      <c r="D179" t="n">
+        <v>80.23709110490057</v>
+      </c>
+      <c r="E179" t="n">
+        <v>467.19</v>
+      </c>
+      <c r="F179" t="n">
+        <v>157.6480493450991</v>
+      </c>
+      <c r="G179" t="n">
+        <v>56498.47235689612</v>
+      </c>
+      <c r="H179" t="n">
+        <v>-8741.236739706075</v>
+      </c>
+      <c r="I179" t="n">
+        <v>5.615</v>
+      </c>
+      <c r="J179" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="K179" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L179" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M179" t="n">
+        <v>300.0319778451221</v>
+      </c>
+      <c r="N179" t="n">
+        <v>5.481361532008621</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>413</v>
+      </c>
+      <c r="B180" t="n">
+        <v>189</v>
+      </c>
+      <c r="C180" t="n">
+        <v>413</v>
+      </c>
+      <c r="D180" t="n">
         <v>79.92327980471686</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E180" t="n">
         <v>471.5</v>
       </c>
-      <c r="F176" t="n">
+      <c r="F180" t="n">
         <v>156.2069823404812</v>
       </c>
-      <c r="G176" t="n">
+      <c r="G180" t="n">
         <v>57162.52314702258</v>
       </c>
-      <c r="H176" t="n">
+      <c r="H180" t="n">
         <v>-8623.240824451565</v>
       </c>
-      <c r="I176" t="n">
+      <c r="I180" t="n">
         <v>5.745</v>
       </c>
-      <c r="J176" t="n">
+      <c r="J180" t="n">
         <v>15.445</v>
       </c>
-      <c r="K176" t="n">
+      <c r="K180" t="n">
         <v>2.56</v>
       </c>
-      <c r="L176" t="n">
+      <c r="L180" t="n">
         <v>3.74</v>
       </c>
-      <c r="M176" t="n">
+      <c r="M180" t="n">
         <v>300.0319766099359</v>
       </c>
-      <c r="N176" t="n">
+      <c r="N180" t="n">
         <v>5.498287282739448</v>
       </c>
     </row>

--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N180"/>
+  <dimension ref="A1:N190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3142,134 +3142,134 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B62" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D62" t="n">
-        <v>93.08411470319172</v>
+        <v>94.07453794796341</v>
       </c>
       <c r="E62" t="n">
-        <v>478.395</v>
+        <v>473.895</v>
       </c>
       <c r="F62" t="n">
-        <v>153.9556060860521</v>
+        <v>155.417533786043</v>
       </c>
       <c r="G62" t="n">
-        <v>7946.335159729334</v>
+        <v>3918.311122471651</v>
       </c>
       <c r="H62" t="n">
-        <v>-1955.388343938965</v>
+        <v>-1006.265954632418</v>
       </c>
       <c r="I62" t="n">
-        <v>5.805</v>
+        <v>5.22</v>
       </c>
       <c r="J62" t="n">
-        <v>16.145</v>
+        <v>14.88</v>
       </c>
       <c r="K62" t="n">
-        <v>2.635</v>
+        <v>2.54</v>
       </c>
       <c r="L62" t="n">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="M62" t="n">
-        <v>300.0574500871471</v>
+        <v>300.0674923038478</v>
       </c>
       <c r="N62" t="n">
-        <v>5.287166981350714</v>
+        <v>5.279563321807951</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B63" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D63" t="n">
-        <v>93.06214226315809</v>
+        <v>94.05990747451519</v>
       </c>
       <c r="E63" t="n">
-        <v>480.24</v>
+        <v>476.105</v>
       </c>
       <c r="F63" t="n">
-        <v>153.3641349607215</v>
+        <v>154.6961115164446</v>
       </c>
       <c r="G63" t="n">
-        <v>7990.791875577724</v>
+        <v>3948.098891120675</v>
       </c>
       <c r="H63" t="n">
-        <v>-1930.721784113969</v>
+        <v>-989.8708594456205</v>
       </c>
       <c r="I63" t="n">
-        <v>6.04</v>
+        <v>5.43</v>
       </c>
       <c r="J63" t="n">
-        <v>16.69</v>
+        <v>15.395</v>
       </c>
       <c r="K63" t="n">
-        <v>2.825</v>
+        <v>2.73</v>
       </c>
       <c r="L63" t="n">
-        <v>3.93</v>
+        <v>3.825</v>
       </c>
       <c r="M63" t="n">
-        <v>300.057450436158</v>
+        <v>300.0674921352895</v>
       </c>
       <c r="N63" t="n">
-        <v>5.289184782171045</v>
+        <v>5.27585264596571</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B64" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D64" t="n">
-        <v>93.00498750755133</v>
+        <v>94.0351739722481</v>
       </c>
       <c r="E64" t="n">
-        <v>484.22</v>
+        <v>479.42</v>
       </c>
       <c r="F64" t="n">
-        <v>152.1035731145695</v>
+        <v>153.6264489873949</v>
       </c>
       <c r="G64" t="n">
-        <v>8121.648262909504</v>
+        <v>4005.299978214047</v>
       </c>
       <c r="H64" t="n">
-        <v>-1881.988881820783</v>
+        <v>-969.0569545970178</v>
       </c>
       <c r="I64" t="n">
-        <v>6.32</v>
+        <v>5.695</v>
       </c>
       <c r="J64" t="n">
-        <v>17.275</v>
+        <v>15.97</v>
       </c>
       <c r="K64" t="n">
-        <v>3.015000000000001</v>
+        <v>2.915</v>
       </c>
       <c r="L64" t="n">
-        <v>4.205</v>
+        <v>4.09</v>
       </c>
       <c r="M64" t="n">
-        <v>235.100423777257</v>
+        <v>235.151426851846</v>
       </c>
       <c r="N64" t="n">
-        <v>5.287157478647369</v>
+        <v>5.275329810320967</v>
       </c>
     </row>
     <row r="65">
@@ -3277,43 +3277,43 @@
         <v>235</v>
       </c>
       <c r="B65" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C65" t="n">
         <v>235</v>
       </c>
       <c r="D65" t="n">
-        <v>93.0364137099274</v>
+        <v>93.08411470319172</v>
       </c>
       <c r="E65" t="n">
-        <v>475.26</v>
+        <v>478.395</v>
       </c>
       <c r="F65" t="n">
-        <v>154.9711572056072</v>
+        <v>153.9556060860521</v>
       </c>
       <c r="G65" t="n">
-        <v>8242.501776817579</v>
+        <v>7946.335159729334</v>
       </c>
       <c r="H65" t="n">
-        <v>-2107.46165361461</v>
+        <v>-1955.388343938965</v>
       </c>
       <c r="I65" t="n">
         <v>5.805</v>
       </c>
       <c r="J65" t="n">
-        <v>15.66</v>
+        <v>16.145</v>
       </c>
       <c r="K65" t="n">
-        <v>2.575</v>
+        <v>2.635</v>
       </c>
       <c r="L65" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="M65" t="n">
-        <v>300.0697908216366</v>
+        <v>300.0574500871471</v>
       </c>
       <c r="N65" t="n">
-        <v>5.289420882602325</v>
+        <v>5.287166981350714</v>
       </c>
     </row>
     <row r="66">
@@ -3321,43 +3321,43 @@
         <v>235</v>
       </c>
       <c r="B66" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C66" t="n">
         <v>235</v>
       </c>
       <c r="D66" t="n">
-        <v>93.01026813941864</v>
+        <v>93.06214226315809</v>
       </c>
       <c r="E66" t="n">
-        <v>477.055</v>
+        <v>480.24</v>
       </c>
       <c r="F66" t="n">
-        <v>154.3880520559199</v>
+        <v>153.3641349607215</v>
       </c>
       <c r="G66" t="n">
-        <v>8293.320375289675</v>
+        <v>7990.791875577724</v>
       </c>
       <c r="H66" t="n">
-        <v>-2076.024117136874</v>
+        <v>-1930.721784113969</v>
       </c>
       <c r="I66" t="n">
-        <v>6.03</v>
+        <v>6.04</v>
       </c>
       <c r="J66" t="n">
-        <v>16.195</v>
+        <v>16.69</v>
       </c>
       <c r="K66" t="n">
-        <v>2.760000000000001</v>
+        <v>2.825</v>
       </c>
       <c r="L66" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="M66" t="n">
-        <v>300.0697896500876</v>
+        <v>300.057450436158</v>
       </c>
       <c r="N66" t="n">
-        <v>5.289361946205399</v>
+        <v>5.289184782171045</v>
       </c>
     </row>
     <row r="67">
@@ -3365,43 +3365,43 @@
         <v>235</v>
       </c>
       <c r="B67" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C67" t="n">
         <v>235</v>
       </c>
       <c r="D67" t="n">
-        <v>92.95198454038147</v>
+        <v>93.00498750755133</v>
       </c>
       <c r="E67" t="n">
-        <v>480.845</v>
+        <v>484.22</v>
       </c>
       <c r="F67" t="n">
-        <v>153.1711719442582</v>
+        <v>152.1035731145695</v>
       </c>
       <c r="G67" t="n">
-        <v>8426.369452735697</v>
+        <v>8121.648262909504</v>
       </c>
       <c r="H67" t="n">
-        <v>-2026.002172810836</v>
+        <v>-1881.988881820783</v>
       </c>
       <c r="I67" t="n">
-        <v>6.315</v>
+        <v>6.32</v>
       </c>
       <c r="J67" t="n">
-        <v>16.78</v>
+        <v>17.275</v>
       </c>
       <c r="K67" t="n">
-        <v>2.95</v>
+        <v>3.015000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>4.130000000000001</v>
+        <v>4.205</v>
       </c>
       <c r="M67" t="n">
-        <v>235.1744918269117</v>
+        <v>235.100423777257</v>
       </c>
       <c r="N67" t="n">
-        <v>5.287193186824704</v>
+        <v>5.287157478647369</v>
       </c>
     </row>
     <row r="68">
@@ -3409,43 +3409,43 @@
         <v>235</v>
       </c>
       <c r="B68" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C68" t="n">
         <v>235</v>
       </c>
       <c r="D68" t="n">
-        <v>92.97506604249594</v>
+        <v>93.0364137099274</v>
       </c>
       <c r="E68" t="n">
-        <v>472.585</v>
+        <v>475.26</v>
       </c>
       <c r="F68" t="n">
-        <v>155.8483493414663</v>
+        <v>154.9711572056072</v>
       </c>
       <c r="G68" t="n">
-        <v>8561.750830016865</v>
+        <v>8242.501776817579</v>
       </c>
       <c r="H68" t="n">
-        <v>-2239.978675435848</v>
+        <v>-2107.46165361461</v>
       </c>
       <c r="I68" t="n">
-        <v>5.815</v>
+        <v>5.805</v>
       </c>
       <c r="J68" t="n">
-        <v>15.455</v>
+        <v>15.66</v>
       </c>
       <c r="K68" t="n">
-        <v>2.534999999999999</v>
+        <v>2.575</v>
       </c>
       <c r="L68" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="M68" t="n">
-        <v>300.06978819568</v>
+        <v>300.0697908216366</v>
       </c>
       <c r="N68" t="n">
-        <v>5.290760606878296</v>
+        <v>5.289420882602325</v>
       </c>
     </row>
     <row r="69">
@@ -3453,43 +3453,43 @@
         <v>235</v>
       </c>
       <c r="B69" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C69" t="n">
         <v>235</v>
       </c>
       <c r="D69" t="n">
-        <v>92.94957247292707</v>
+        <v>93.01026813941864</v>
       </c>
       <c r="E69" t="n">
-        <v>474.8</v>
+        <v>477.055</v>
       </c>
       <c r="F69" t="n">
-        <v>155.1212977538687</v>
+        <v>154.3880520559199</v>
       </c>
       <c r="G69" t="n">
-        <v>8615.753533525256</v>
+        <v>8293.320375289675</v>
       </c>
       <c r="H69" t="n">
-        <v>-2213.83876900426</v>
+        <v>-2076.024117136874</v>
       </c>
       <c r="I69" t="n">
-        <v>6.035</v>
+        <v>6.03</v>
       </c>
       <c r="J69" t="n">
-        <v>15.985</v>
+        <v>16.195</v>
       </c>
       <c r="K69" t="n">
-        <v>2.725</v>
+        <v>2.760000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="M69" t="n">
-        <v>300.0697887405183</v>
+        <v>300.0697896500876</v>
       </c>
       <c r="N69" t="n">
-        <v>5.289443248086725</v>
+        <v>5.289361946205399</v>
       </c>
     </row>
     <row r="70">
@@ -3497,175 +3497,175 @@
         <v>235</v>
       </c>
       <c r="B70" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C70" t="n">
         <v>235</v>
       </c>
       <c r="D70" t="n">
-        <v>92.88132651844941</v>
+        <v>92.95198454038147</v>
       </c>
       <c r="E70" t="n">
-        <v>478.67</v>
+        <v>480.845</v>
       </c>
       <c r="F70" t="n">
-        <v>153.8671572764888</v>
+        <v>153.1711719442582</v>
       </c>
       <c r="G70" t="n">
-        <v>8768.069910799191</v>
+        <v>8426.369452735697</v>
       </c>
       <c r="H70" t="n">
-        <v>-2151.810747883992</v>
+        <v>-2026.002172810836</v>
       </c>
       <c r="I70" t="n">
-        <v>6.31</v>
+        <v>6.315</v>
       </c>
       <c r="J70" t="n">
-        <v>16.56</v>
+        <v>16.78</v>
       </c>
       <c r="K70" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="L70" t="n">
-        <v>4.085</v>
+        <v>4.130000000000001</v>
       </c>
       <c r="M70" t="n">
-        <v>235.1737897185261</v>
+        <v>235.1744918269117</v>
       </c>
       <c r="N70" t="n">
-        <v>5.287356048694752</v>
+        <v>5.287193186824704</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B71" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D71" t="n">
-        <v>93.07089740407457</v>
+        <v>92.97506604249594</v>
       </c>
       <c r="E71" t="n">
-        <v>479.075</v>
+        <v>472.585</v>
       </c>
       <c r="F71" t="n">
-        <v>153.7370811950882</v>
+        <v>155.8483493414663</v>
       </c>
       <c r="G71" t="n">
-        <v>7974.563432559217</v>
+        <v>8561.750830016865</v>
       </c>
       <c r="H71" t="n">
-        <v>-1942.057006645183</v>
+        <v>-2239.978675435848</v>
       </c>
       <c r="I71" t="n">
-        <v>5.850000000000001</v>
+        <v>5.815</v>
       </c>
       <c r="J71" t="n">
-        <v>16.87</v>
+        <v>15.455</v>
       </c>
       <c r="K71" t="n">
-        <v>2.755000000000001</v>
+        <v>2.534999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>3.815</v>
+        <v>3.59</v>
       </c>
       <c r="M71" t="n">
-        <v>300.0158371475002</v>
+        <v>300.06978819568</v>
       </c>
       <c r="N71" t="n">
-        <v>5.272243114095827</v>
+        <v>5.290760606878296</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B72" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D72" t="n">
-        <v>93.03912134971216</v>
+        <v>92.94957247292707</v>
       </c>
       <c r="E72" t="n">
-        <v>481.315</v>
+        <v>474.8</v>
       </c>
       <c r="F72" t="n">
-        <v>153.0216015988217</v>
+        <v>155.1212977538687</v>
       </c>
       <c r="G72" t="n">
-        <v>8044.064140090631</v>
+        <v>8615.753533525256</v>
       </c>
       <c r="H72" t="n">
-        <v>-1911.651931236464</v>
+        <v>-2213.83876900426</v>
       </c>
       <c r="I72" t="n">
-        <v>6.09</v>
+        <v>6.035</v>
       </c>
       <c r="J72" t="n">
-        <v>17.415</v>
+        <v>15.985</v>
       </c>
       <c r="K72" t="n">
-        <v>2.94</v>
+        <v>2.725</v>
       </c>
       <c r="L72" t="n">
-        <v>4.055</v>
+        <v>3.82</v>
       </c>
       <c r="M72" t="n">
-        <v>300.0158372842804</v>
+        <v>300.0697887405183</v>
       </c>
       <c r="N72" t="n">
-        <v>5.271683751951102</v>
+        <v>5.289443248086725</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B73" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D73" t="n">
-        <v>93.00152788144494</v>
+        <v>92.88132651844941</v>
       </c>
       <c r="E73" t="n">
-        <v>484.135</v>
+        <v>478.67</v>
       </c>
       <c r="F73" t="n">
-        <v>152.1302780702425</v>
+        <v>153.8671572764888</v>
       </c>
       <c r="G73" t="n">
-        <v>8132.344053767129</v>
+        <v>8768.069910799191</v>
       </c>
       <c r="H73" t="n">
-        <v>-1881.857598216936</v>
+        <v>-2151.810747883992</v>
       </c>
       <c r="I73" t="n">
-        <v>6.365</v>
+        <v>6.31</v>
       </c>
       <c r="J73" t="n">
-        <v>18</v>
+        <v>16.56</v>
       </c>
       <c r="K73" t="n">
-        <v>3.125000000000001</v>
+        <v>2.91</v>
       </c>
       <c r="L73" t="n">
-        <v>4.32</v>
+        <v>4.085</v>
       </c>
       <c r="M73" t="n">
-        <v>234.9589631825281</v>
+        <v>235.1737897185261</v>
       </c>
       <c r="N73" t="n">
-        <v>5.269234130732465</v>
+        <v>5.287356048694752</v>
       </c>
     </row>
     <row r="74">
@@ -3673,43 +3673,43 @@
         <v>243</v>
       </c>
       <c r="B74" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C74" t="n">
         <v>243</v>
       </c>
       <c r="D74" t="n">
-        <v>93.03344845830883</v>
+        <v>93.07089740407457</v>
       </c>
       <c r="E74" t="n">
-        <v>475.17</v>
+        <v>479.075</v>
       </c>
       <c r="F74" t="n">
-        <v>155.0005096566215</v>
+        <v>153.7370811950882</v>
       </c>
       <c r="G74" t="n">
-        <v>8247.417073373785</v>
+        <v>7974.563432559217</v>
       </c>
       <c r="H74" t="n">
-        <v>-2103.029668946147</v>
+        <v>-1942.057006645183</v>
       </c>
       <c r="I74" t="n">
-        <v>5.83</v>
+        <v>5.850000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>16.21</v>
+        <v>16.87</v>
       </c>
       <c r="K74" t="n">
-        <v>2.645</v>
+        <v>2.755000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>3.71</v>
+        <v>3.815</v>
       </c>
       <c r="M74" t="n">
-        <v>300.0323465174197</v>
+        <v>300.0158371475002</v>
       </c>
       <c r="N74" t="n">
-        <v>5.273654684421681</v>
+        <v>5.272243114095827</v>
       </c>
     </row>
     <row r="75">
@@ -3717,43 +3717,43 @@
         <v>243</v>
       </c>
       <c r="B75" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C75" t="n">
         <v>243</v>
       </c>
       <c r="D75" t="n">
-        <v>92.98698604252111</v>
+        <v>93.03912134971216</v>
       </c>
       <c r="E75" t="n">
-        <v>471.785</v>
+        <v>481.315</v>
       </c>
       <c r="F75" t="n">
-        <v>156.112619463393</v>
+        <v>153.0216015988217</v>
       </c>
       <c r="G75" t="n">
-        <v>8537.076040797645</v>
+        <v>8044.064140090631</v>
       </c>
       <c r="H75" t="n">
-        <v>-2252.765444771382</v>
+        <v>-1911.651931236464</v>
       </c>
       <c r="I75" t="n">
-        <v>5.825</v>
+        <v>6.09</v>
       </c>
       <c r="J75" t="n">
-        <v>15.635</v>
+        <v>17.415</v>
       </c>
       <c r="K75" t="n">
-        <v>2.565</v>
+        <v>2.94</v>
       </c>
       <c r="L75" t="n">
-        <v>3.63</v>
+        <v>4.055</v>
       </c>
       <c r="M75" t="n">
-        <v>300.047448554556</v>
+        <v>300.0158372842804</v>
       </c>
       <c r="N75" t="n">
-        <v>5.274677997196122</v>
+        <v>5.271683751951102</v>
       </c>
     </row>
     <row r="76">
@@ -3761,43 +3761,43 @@
         <v>243</v>
       </c>
       <c r="B76" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C76" t="n">
         <v>243</v>
       </c>
       <c r="D76" t="n">
-        <v>92.95220095109302</v>
+        <v>93.00152788144494</v>
       </c>
       <c r="E76" t="n">
-        <v>474.05</v>
+        <v>484.135</v>
       </c>
       <c r="F76" t="n">
-        <v>155.3667169571498</v>
+        <v>152.1302780702425</v>
       </c>
       <c r="G76" t="n">
-        <v>8610.898289806948</v>
+        <v>8132.344053767129</v>
       </c>
       <c r="H76" t="n">
-        <v>-2217.246307165785</v>
+        <v>-1881.857598216936</v>
       </c>
       <c r="I76" t="n">
-        <v>6.045</v>
+        <v>6.365</v>
       </c>
       <c r="J76" t="n">
-        <v>16.165</v>
+        <v>18</v>
       </c>
       <c r="K76" t="n">
-        <v>2.755</v>
+        <v>3.125000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>3.865</v>
+        <v>4.32</v>
       </c>
       <c r="M76" t="n">
-        <v>300.0474487569205</v>
+        <v>234.9589631825281</v>
       </c>
       <c r="N76" t="n">
-        <v>5.271849489975422</v>
+        <v>5.269234130732465</v>
       </c>
     </row>
     <row r="77">
@@ -3805,4574 +3805,5014 @@
         <v>243</v>
       </c>
       <c r="B77" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C77" t="n">
         <v>243</v>
       </c>
       <c r="D77" t="n">
-        <v>92.8917519819303</v>
+        <v>93.03344845830883</v>
       </c>
       <c r="E77" t="n">
-        <v>478.605</v>
+        <v>475.17</v>
       </c>
       <c r="F77" t="n">
-        <v>153.8880541856789</v>
+        <v>155.0005096566215</v>
       </c>
       <c r="G77" t="n">
-        <v>8758.821020037867</v>
+        <v>8247.417073373785</v>
       </c>
       <c r="H77" t="n">
-        <v>-2175.51998668201</v>
+        <v>-2103.029668946147</v>
       </c>
       <c r="I77" t="n">
-        <v>6.32</v>
+        <v>5.83</v>
       </c>
       <c r="J77" t="n">
-        <v>16.74</v>
+        <v>16.21</v>
       </c>
       <c r="K77" t="n">
-        <v>2.94</v>
+        <v>2.645</v>
       </c>
       <c r="L77" t="n">
-        <v>4.125</v>
+        <v>3.71</v>
       </c>
       <c r="M77" t="n">
-        <v>235.0853150102566</v>
+        <v>300.0323465174197</v>
       </c>
       <c r="N77" t="n">
-        <v>5.269412750144725</v>
+        <v>5.273654684421681</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="B78" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="D78" t="n">
-        <v>93.69674903048164</v>
+        <v>92.99213742164812</v>
       </c>
       <c r="E78" t="n">
-        <v>512.495</v>
+        <v>477.7</v>
       </c>
       <c r="F78" t="n">
-        <v>143.711825819836</v>
+        <v>154.1795942506529</v>
       </c>
       <c r="G78" t="n">
-        <v>4940.765032058101</v>
+        <v>8335.344865448611</v>
       </c>
       <c r="H78" t="n">
-        <v>-839.8178171649643</v>
+        <v>-2061.088674972483</v>
       </c>
       <c r="I78" t="n">
-        <v>7.23</v>
+        <v>6.06</v>
       </c>
       <c r="J78" t="n">
-        <v>27.5</v>
+        <v>16.735</v>
       </c>
       <c r="K78" t="n">
-        <v>4.145</v>
+        <v>2.83</v>
       </c>
       <c r="L78" t="n">
-        <v>5.425000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="M78" t="n">
-        <v>239.7404630157553</v>
+        <v>300.0323467495622</v>
       </c>
       <c r="N78" t="n">
-        <v>4.560017417083075</v>
+        <v>5.271763219074517</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="B79" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="D79" t="n">
-        <v>93.64999629600874</v>
+        <v>92.94267037589772</v>
       </c>
       <c r="E79" t="n">
-        <v>519.24</v>
+        <v>481.185</v>
       </c>
       <c r="F79" t="n">
-        <v>141.8449891640414</v>
+        <v>153.0629428879472</v>
       </c>
       <c r="G79" t="n">
-        <v>5052.777732801751</v>
+        <v>8451.397021997889</v>
       </c>
       <c r="H79" t="n">
-        <v>-804.5195338064688</v>
+        <v>-2021.811427764729</v>
       </c>
       <c r="I79" t="n">
-        <v>7.32</v>
+        <v>6.335</v>
       </c>
       <c r="J79" t="n">
-        <v>27.82</v>
+        <v>17.325</v>
       </c>
       <c r="K79" t="n">
-        <v>4.235</v>
+        <v>3.02</v>
       </c>
       <c r="L79" t="n">
-        <v>5.515000000000001</v>
+        <v>4.21</v>
       </c>
       <c r="M79" t="n">
-        <v>239.7407574655874</v>
+        <v>235.0310177175042</v>
       </c>
       <c r="N79" t="n">
-        <v>4.560017417083075</v>
+        <v>5.269312281270834</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="B80" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="D80" t="n">
-        <v>93.64638467813667</v>
+        <v>92.98698604252111</v>
       </c>
       <c r="E80" t="n">
-        <v>510.885</v>
+        <v>471.785</v>
       </c>
       <c r="F80" t="n">
-        <v>144.1647184269197</v>
+        <v>156.112619463393</v>
       </c>
       <c r="G80" t="n">
-        <v>5163.260041859553</v>
+        <v>8537.076040797645</v>
       </c>
       <c r="H80" t="n">
-        <v>-905.4173578638894</v>
+        <v>-2252.765444771382</v>
       </c>
       <c r="I80" t="n">
-        <v>6.890000000000001</v>
+        <v>5.825</v>
       </c>
       <c r="J80" t="n">
-        <v>25.32</v>
+        <v>15.635</v>
       </c>
       <c r="K80" t="n">
-        <v>3.825</v>
+        <v>2.565</v>
       </c>
       <c r="L80" t="n">
-        <v>5.04</v>
+        <v>3.63</v>
       </c>
       <c r="M80" t="n">
-        <v>239.7619618014928</v>
+        <v>300.047448554556</v>
       </c>
       <c r="N80" t="n">
-        <v>4.801091379183875</v>
+        <v>5.274677997196122</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="B81" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="D81" t="n">
-        <v>93.66404021981816</v>
+        <v>92.95220095109302</v>
       </c>
       <c r="E81" t="n">
-        <v>507.94</v>
+        <v>474.05</v>
       </c>
       <c r="F81" t="n">
-        <v>145.0005752126961</v>
+        <v>155.3667169571498</v>
       </c>
       <c r="G81" t="n">
-        <v>5116.597969114839</v>
+        <v>8610.898289806948</v>
       </c>
       <c r="H81" t="n">
-        <v>-914.3385786321323</v>
+        <v>-2217.246307165785</v>
       </c>
       <c r="I81" t="n">
-        <v>6.985</v>
+        <v>6.045</v>
       </c>
       <c r="J81" t="n">
-        <v>25.645</v>
+        <v>16.165</v>
       </c>
       <c r="K81" t="n">
-        <v>3.920000000000001</v>
+        <v>2.755</v>
       </c>
       <c r="L81" t="n">
-        <v>5.135000000000001</v>
+        <v>3.865</v>
       </c>
       <c r="M81" t="n">
-        <v>239.7620152375329</v>
+        <v>300.0474487569205</v>
       </c>
       <c r="N81" t="n">
-        <v>4.801091379183875</v>
+        <v>5.271849489975422</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="B82" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="D82" t="n">
-        <v>93.60353589882081</v>
+        <v>92.8917519819303</v>
       </c>
       <c r="E82" t="n">
-        <v>515.83</v>
+        <v>478.605</v>
       </c>
       <c r="F82" t="n">
-        <v>142.7826845540912</v>
+        <v>153.8880541856789</v>
       </c>
       <c r="G82" t="n">
-        <v>5259.395217040341</v>
+        <v>8758.821020037867</v>
       </c>
       <c r="H82" t="n">
-        <v>-866.5203743669672</v>
+        <v>-2175.51998668201</v>
       </c>
       <c r="I82" t="n">
-        <v>7.075</v>
+        <v>6.32</v>
       </c>
       <c r="J82" t="n">
-        <v>25.965</v>
+        <v>16.74</v>
       </c>
       <c r="K82" t="n">
-        <v>4.010000000000001</v>
+        <v>2.94</v>
       </c>
       <c r="L82" t="n">
-        <v>5.225000000000001</v>
+        <v>4.125</v>
       </c>
       <c r="M82" t="n">
-        <v>239.7613309624005</v>
+        <v>235.0853150102566</v>
       </c>
       <c r="N82" t="n">
-        <v>4.801091379183875</v>
+        <v>5.269412750144725</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B83" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D83" t="n">
-        <v>85.96689449914007</v>
+        <v>93.68742618713188</v>
       </c>
       <c r="E83" t="n">
-        <v>446.065</v>
+        <v>515.61</v>
       </c>
       <c r="F83" t="n">
-        <v>165.1140353391027</v>
+        <v>142.8436069384552</v>
       </c>
       <c r="G83" t="n">
-        <v>35182.595902612</v>
+        <v>4974.028446379185</v>
       </c>
       <c r="H83" t="n">
-        <v>-8422.060199215268</v>
+        <v>-843.784560550298</v>
       </c>
       <c r="I83" t="n">
-        <v>4.795</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>10.265</v>
+        <v>27.17</v>
       </c>
       <c r="K83" t="n">
-        <v>1.685</v>
+        <v>4.05</v>
       </c>
       <c r="L83" t="n">
-        <v>2.47</v>
+        <v>5.33</v>
       </c>
       <c r="M83" t="n">
-        <v>300.0734614592056</v>
+        <v>239.7402396249865</v>
       </c>
       <c r="N83" t="n">
-        <v>7.24261145101418</v>
+        <v>4.560017417083075</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B84" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D84" t="n">
-        <v>86.15287970112803</v>
+        <v>93.69674903048164</v>
       </c>
       <c r="E84" t="n">
-        <v>447.95</v>
+        <v>512.495</v>
       </c>
       <c r="F84" t="n">
-        <v>164.4192257473755</v>
+        <v>143.711825819836</v>
       </c>
       <c r="G84" t="n">
-        <v>34759.1428788493</v>
+        <v>4940.765032058101</v>
       </c>
       <c r="H84" t="n">
-        <v>-8540.368589083148</v>
+        <v>-839.8178171649643</v>
       </c>
       <c r="I84" t="n">
-        <v>4.965</v>
+        <v>7.23</v>
       </c>
       <c r="J84" t="n">
-        <v>10.525</v>
+        <v>27.5</v>
       </c>
       <c r="K84" t="n">
-        <v>1.77</v>
+        <v>4.145</v>
       </c>
       <c r="L84" t="n">
-        <v>2.625</v>
+        <v>5.425000000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>208.1278673001732</v>
+        <v>239.7404630157553</v>
       </c>
       <c r="N84" t="n">
-        <v>7.24261145101418</v>
+        <v>4.560017417083075</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B85" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D85" t="n">
-        <v>85.74857125932778</v>
+        <v>93.64999629600874</v>
       </c>
       <c r="E85" t="n">
-        <v>442.48</v>
+        <v>519.24</v>
       </c>
       <c r="F85" t="n">
-        <v>166.4517993435565</v>
+        <v>141.8449891640414</v>
       </c>
       <c r="G85" t="n">
-        <v>36168.03387750834</v>
+        <v>5052.777732801751</v>
       </c>
       <c r="H85" t="n">
-        <v>-8867.970665994213</v>
+        <v>-804.5195338064688</v>
       </c>
       <c r="I85" t="n">
-        <v>4.7</v>
+        <v>7.32</v>
       </c>
       <c r="J85" t="n">
-        <v>10.045</v>
+        <v>27.82</v>
       </c>
       <c r="K85" t="n">
-        <v>1.595</v>
+        <v>4.235</v>
       </c>
       <c r="L85" t="n">
-        <v>2.375</v>
+        <v>5.515000000000001</v>
       </c>
       <c r="M85" t="n">
-        <v>300.0734631925171</v>
+        <v>239.7407574655874</v>
       </c>
       <c r="N85" t="n">
-        <v>7.242643590519569</v>
+        <v>4.560017417083075</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B86" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D86" t="n">
-        <v>85.53276250155793</v>
+        <v>93.64638467813667</v>
       </c>
       <c r="E86" t="n">
-        <v>444.64</v>
+        <v>510.885</v>
       </c>
       <c r="F86" t="n">
-        <v>165.6431993827295</v>
+        <v>144.1647184269197</v>
       </c>
       <c r="G86" t="n">
-        <v>36725.2777434966</v>
+        <v>5163.260041859553</v>
       </c>
       <c r="H86" t="n">
-        <v>-8778.845410104459</v>
+        <v>-905.4173578638894</v>
       </c>
       <c r="I86" t="n">
-        <v>4.815</v>
+        <v>6.890000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>10.25</v>
+        <v>25.32</v>
       </c>
       <c r="K86" t="n">
-        <v>1.685</v>
+        <v>3.825</v>
       </c>
       <c r="L86" t="n">
-        <v>2.47</v>
+        <v>5.04</v>
       </c>
       <c r="M86" t="n">
-        <v>300.0734621616424</v>
+        <v>239.7619618014928</v>
       </c>
       <c r="N86" t="n">
-        <v>7.242643590519569</v>
+        <v>4.801091379183875</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B87" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D87" t="n">
-        <v>85.69196635613324</v>
+        <v>93.66404021981816</v>
       </c>
       <c r="E87" t="n">
-        <v>446.115</v>
+        <v>507.94</v>
       </c>
       <c r="F87" t="n">
-        <v>165.0955295686916</v>
+        <v>145.0005752126961</v>
       </c>
       <c r="G87" t="n">
-        <v>36257.7097875395</v>
+        <v>5116.597969114839</v>
       </c>
       <c r="H87" t="n">
-        <v>-8762.056793761083</v>
+        <v>-914.3385786321323</v>
       </c>
       <c r="I87" t="n">
-        <v>4.985</v>
+        <v>6.985</v>
       </c>
       <c r="J87" t="n">
-        <v>10.515</v>
+        <v>25.645</v>
       </c>
       <c r="K87" t="n">
-        <v>1.77</v>
+        <v>3.920000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>2.625</v>
+        <v>5.135000000000001</v>
       </c>
       <c r="M87" t="n">
-        <v>208.1450480610657</v>
+        <v>239.7620152375329</v>
       </c>
       <c r="N87" t="n">
-        <v>7.242643590519569</v>
+        <v>4.801091379183875</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B88" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D88" t="n">
-        <v>85.29523023885534</v>
+        <v>93.60353589882081</v>
       </c>
       <c r="E88" t="n">
-        <v>441.75</v>
+        <v>515.83</v>
       </c>
       <c r="F88" t="n">
-        <v>166.7268640034791</v>
+        <v>142.7826845540912</v>
       </c>
       <c r="G88" t="n">
-        <v>37685.60944579857</v>
+        <v>5259.395217040341</v>
       </c>
       <c r="H88" t="n">
-        <v>-9141.146218132371</v>
+        <v>-866.5203743669672</v>
       </c>
       <c r="I88" t="n">
-        <v>4.72</v>
+        <v>7.075</v>
       </c>
       <c r="J88" t="n">
-        <v>10.05</v>
+        <v>25.965</v>
       </c>
       <c r="K88" t="n">
-        <v>1.595</v>
+        <v>4.010000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>2.37</v>
+        <v>5.225000000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>300.0734627988316</v>
+        <v>239.7613309624005</v>
       </c>
       <c r="N88" t="n">
-        <v>7.24266892208129</v>
+        <v>4.801091379183875</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B89" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D89" t="n">
-        <v>84.97502641234331</v>
+        <v>93.61141755126326</v>
       </c>
       <c r="E89" t="n">
-        <v>443.23</v>
+        <v>506.445</v>
       </c>
       <c r="F89" t="n">
-        <v>166.1701423043044</v>
+        <v>145.42860956972</v>
       </c>
       <c r="G89" t="n">
-        <v>38509.76874060684</v>
+        <v>5341.511760433159</v>
       </c>
       <c r="H89" t="n">
-        <v>-9024.780589164946</v>
+        <v>-975.3338533411502</v>
       </c>
       <c r="I89" t="n">
-        <v>4.83</v>
+        <v>6.67</v>
       </c>
       <c r="J89" t="n">
-        <v>10.255</v>
+        <v>23.745</v>
       </c>
       <c r="K89" t="n">
-        <v>1.68</v>
+        <v>3.63</v>
       </c>
       <c r="L89" t="n">
-        <v>2.47</v>
+        <v>4.785</v>
       </c>
       <c r="M89" t="n">
-        <v>300.0734632642283</v>
+        <v>239.789270620851</v>
       </c>
       <c r="N89" t="n">
-        <v>7.24266892208129</v>
+        <v>5.041762263162907</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B90" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D90" t="n">
-        <v>85.17020859058194</v>
+        <v>93.63303040141308</v>
       </c>
       <c r="E90" t="n">
-        <v>444.31</v>
+        <v>503.16</v>
       </c>
       <c r="F90" t="n">
-        <v>165.7662266740269</v>
+        <v>146.3780749136197</v>
       </c>
       <c r="G90" t="n">
-        <v>38031.88441025994</v>
+        <v>5285.409640863534</v>
       </c>
       <c r="H90" t="n">
-        <v>-9109.297236292861</v>
+        <v>-987.2621921475086</v>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>6.765000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>10.52</v>
+        <v>24.065</v>
       </c>
       <c r="K90" t="n">
-        <v>1.775</v>
+        <v>3.72</v>
       </c>
       <c r="L90" t="n">
-        <v>2.63</v>
+        <v>4.875</v>
       </c>
       <c r="M90" t="n">
-        <v>208.1627949573518</v>
+        <v>239.787055573648</v>
       </c>
       <c r="N90" t="n">
-        <v>7.24266892208129</v>
+        <v>5.041762263162907</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="B91" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="D91" t="n">
-        <v>93.51406360085934</v>
+        <v>93.56356646144445</v>
       </c>
       <c r="E91" t="n">
-        <v>478.61</v>
+        <v>511.83</v>
       </c>
       <c r="F91" t="n">
-        <v>153.8864465296105</v>
+        <v>143.8985447776349</v>
       </c>
       <c r="G91" t="n">
-        <v>6153.111703682009</v>
+        <v>5449.837169933598</v>
       </c>
       <c r="H91" t="n">
-        <v>-1492.863309931552</v>
+        <v>-932.8978412596703</v>
       </c>
       <c r="I91" t="n">
-        <v>5.72</v>
+        <v>6.855</v>
       </c>
       <c r="J91" t="n">
-        <v>16.6</v>
+        <v>24.385</v>
       </c>
       <c r="K91" t="n">
-        <v>2.550000000000001</v>
+        <v>3.815</v>
       </c>
       <c r="L91" t="n">
-        <v>3.620000000000001</v>
+        <v>4.970000000000001</v>
       </c>
       <c r="M91" t="n">
-        <v>276.6878172939188</v>
+        <v>239.7878320759359</v>
       </c>
       <c r="N91" t="n">
-        <v>5.259746042528284</v>
+        <v>5.041762263162907</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B92" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C92" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D92" t="n">
-        <v>93.46072563038759</v>
+        <v>86.24922471942575</v>
       </c>
       <c r="E92" t="n">
-        <v>482.945</v>
+        <v>444.035</v>
       </c>
       <c r="F92" t="n">
-        <v>152.5051344843344</v>
+        <v>165.8688891045455</v>
       </c>
       <c r="G92" t="n">
-        <v>6272.605052490439</v>
+        <v>34441.33304201571</v>
       </c>
       <c r="H92" t="n">
-        <v>-1444.424203516434</v>
+        <v>-8519.505943814291</v>
       </c>
       <c r="I92" t="n">
-        <v>5.955</v>
+        <v>4.685</v>
       </c>
       <c r="J92" t="n">
-        <v>17.06</v>
+        <v>10.055</v>
       </c>
       <c r="K92" t="n">
-        <v>2.654999999999999</v>
+        <v>1.595</v>
       </c>
       <c r="L92" t="n">
-        <v>3.835</v>
+        <v>2.375</v>
       </c>
       <c r="M92" t="n">
-        <v>252.5095289898121</v>
+        <v>300.0734617663323</v>
       </c>
       <c r="N92" t="n">
-        <v>5.259746042528284</v>
+        <v>7.24261145101418</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B93" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C93" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D93" t="n">
-        <v>93.42556059685845</v>
+        <v>85.96689449914007</v>
       </c>
       <c r="E93" t="n">
-        <v>486.395</v>
+        <v>446.065</v>
       </c>
       <c r="F93" t="n">
-        <v>151.4234154823484</v>
+        <v>165.1140353391027</v>
       </c>
       <c r="G93" t="n">
-        <v>6355.202896443663</v>
+        <v>35182.595902612</v>
       </c>
       <c r="H93" t="n">
-        <v>-1416.35211739665</v>
+        <v>-8422.060199215268</v>
       </c>
       <c r="I93" t="n">
-        <v>6.21</v>
+        <v>4.795</v>
       </c>
       <c r="J93" t="n">
-        <v>17.53</v>
+        <v>10.265</v>
       </c>
       <c r="K93" t="n">
-        <v>2.75</v>
+        <v>1.685</v>
       </c>
       <c r="L93" t="n">
-        <v>4.02</v>
+        <v>2.47</v>
       </c>
       <c r="M93" t="n">
-        <v>217.611783644889</v>
+        <v>300.0734614592056</v>
       </c>
       <c r="N93" t="n">
-        <v>5.259746042528284</v>
+        <v>7.24261145101418</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B94" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D94" t="n">
-        <v>93.46843332897606</v>
+        <v>86.15287970112803</v>
       </c>
       <c r="E94" t="n">
-        <v>476.365</v>
+        <v>447.95</v>
       </c>
       <c r="F94" t="n">
-        <v>154.6116783842996</v>
+        <v>164.4192257473755</v>
       </c>
       <c r="G94" t="n">
-        <v>6405.248870609407</v>
+        <v>34759.1428788493</v>
       </c>
       <c r="H94" t="n">
-        <v>-1604.841963370349</v>
+        <v>-8540.368589083148</v>
       </c>
       <c r="I94" t="n">
-        <v>5.725000000000001</v>
+        <v>4.965</v>
       </c>
       <c r="J94" t="n">
-        <v>15.92</v>
+        <v>10.525</v>
       </c>
       <c r="K94" t="n">
-        <v>2.47</v>
+        <v>1.77</v>
       </c>
       <c r="L94" t="n">
-        <v>3.54</v>
+        <v>2.625</v>
       </c>
       <c r="M94" t="n">
-        <v>281.683010309403</v>
+        <v>208.1278673001732</v>
       </c>
       <c r="N94" t="n">
-        <v>5.259773801395505</v>
+        <v>7.24261145101418</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B95" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C95" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D95" t="n">
-        <v>93.41632642975102</v>
+        <v>85.74857125932778</v>
       </c>
       <c r="E95" t="n">
-        <v>480.225</v>
+        <v>442.48</v>
       </c>
       <c r="F95" t="n">
-        <v>153.3689253444466</v>
+        <v>166.4517993435565</v>
       </c>
       <c r="G95" t="n">
-        <v>6520.856114310886</v>
+        <v>36168.03387750834</v>
       </c>
       <c r="H95" t="n">
-        <v>-1556.424692098753</v>
+        <v>-8867.970665994213</v>
       </c>
       <c r="I95" t="n">
-        <v>5.93</v>
+        <v>4.7</v>
       </c>
       <c r="J95" t="n">
-        <v>16.355</v>
+        <v>10.045</v>
       </c>
       <c r="K95" t="n">
-        <v>2.565</v>
+        <v>1.595</v>
       </c>
       <c r="L95" t="n">
-        <v>3.73</v>
+        <v>2.375</v>
       </c>
       <c r="M95" t="n">
-        <v>252.5506025773835</v>
+        <v>300.0734631925171</v>
       </c>
       <c r="N95" t="n">
-        <v>5.259773801395505</v>
+        <v>7.242643590519569</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B96" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D96" t="n">
-        <v>93.38470158508471</v>
+        <v>85.53276250155793</v>
       </c>
       <c r="E96" t="n">
-        <v>483.175</v>
+        <v>444.64</v>
       </c>
       <c r="F96" t="n">
-        <v>152.4325392943279</v>
+        <v>165.6431993827295</v>
       </c>
       <c r="G96" t="n">
-        <v>6594.837628184146</v>
+        <v>36725.2777434966</v>
       </c>
       <c r="H96" t="n">
-        <v>-1530.901072374127</v>
+        <v>-8778.845410104459</v>
       </c>
       <c r="I96" t="n">
-        <v>6.19</v>
+        <v>4.815</v>
       </c>
       <c r="J96" t="n">
-        <v>16.835</v>
+        <v>10.25</v>
       </c>
       <c r="K96" t="n">
-        <v>2.66</v>
+        <v>1.685</v>
       </c>
       <c r="L96" t="n">
-        <v>3.915</v>
+        <v>2.47</v>
       </c>
       <c r="M96" t="n">
-        <v>217.6849423681168</v>
+        <v>300.0734621616424</v>
       </c>
       <c r="N96" t="n">
-        <v>5.259773801395505</v>
+        <v>7.242643590519569</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B97" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C97" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D97" t="n">
-        <v>93.43566194116374</v>
+        <v>85.69196635613324</v>
       </c>
       <c r="E97" t="n">
-        <v>472.575</v>
+        <v>446.115</v>
       </c>
       <c r="F97" t="n">
-        <v>155.8516471957612</v>
+        <v>165.0955295686916</v>
       </c>
       <c r="G97" t="n">
-        <v>6621.745409759462</v>
+        <v>36257.7097875395</v>
       </c>
       <c r="H97" t="n">
-        <v>-1721.777563608836</v>
+        <v>-8762.056793761083</v>
       </c>
       <c r="I97" t="n">
-        <v>5.73</v>
+        <v>4.985</v>
       </c>
       <c r="J97" t="n">
-        <v>15.35</v>
+        <v>10.515</v>
       </c>
       <c r="K97" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="L97" t="n">
-        <v>3.485</v>
+        <v>2.625</v>
       </c>
       <c r="M97" t="n">
-        <v>286.5115313664276</v>
+        <v>208.1450480610657</v>
       </c>
       <c r="N97" t="n">
-        <v>5.259798202048205</v>
+        <v>7.242643590519569</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B98" t="n">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C98" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D98" t="n">
-        <v>93.37423222341569</v>
+        <v>85.29523023885534</v>
       </c>
       <c r="E98" t="n">
-        <v>476.835</v>
+        <v>441.75</v>
       </c>
       <c r="F98" t="n">
-        <v>154.4592829249884</v>
+        <v>166.7268640034791</v>
       </c>
       <c r="G98" t="n">
-        <v>6757.198730392972</v>
+        <v>37685.60944579857</v>
       </c>
       <c r="H98" t="n">
-        <v>-1663.892522353884</v>
+        <v>-9141.146218132371</v>
       </c>
       <c r="I98" t="n">
-        <v>5.92</v>
+        <v>4.72</v>
       </c>
       <c r="J98" t="n">
-        <v>15.76</v>
+        <v>10.05</v>
       </c>
       <c r="K98" t="n">
-        <v>2.505</v>
+        <v>1.595</v>
       </c>
       <c r="L98" t="n">
-        <v>3.649999999999999</v>
+        <v>2.37</v>
       </c>
       <c r="M98" t="n">
-        <v>252.6008943792451</v>
+        <v>300.0734627988316</v>
       </c>
       <c r="N98" t="n">
-        <v>5.259798202048205</v>
+        <v>7.24266892208129</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B99" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C99" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D99" t="n">
-        <v>93.34673725956608</v>
+        <v>84.97502641234331</v>
       </c>
       <c r="E99" t="n">
-        <v>479.95</v>
+        <v>443.23</v>
       </c>
       <c r="F99" t="n">
-        <v>153.4568021117551</v>
+        <v>166.1701423043044</v>
       </c>
       <c r="G99" t="n">
-        <v>6826.573749712831</v>
+        <v>38509.76874060684</v>
       </c>
       <c r="H99" t="n">
-        <v>-1646.831322890376</v>
+        <v>-9024.780589164946</v>
       </c>
       <c r="I99" t="n">
-        <v>6.175</v>
+        <v>4.83</v>
       </c>
       <c r="J99" t="n">
-        <v>16.235</v>
+        <v>10.255</v>
       </c>
       <c r="K99" t="n">
-        <v>2.600000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="L99" t="n">
-        <v>3.84</v>
+        <v>2.47</v>
       </c>
       <c r="M99" t="n">
-        <v>217.7683663567076</v>
+        <v>300.0734632642283</v>
       </c>
       <c r="N99" t="n">
-        <v>5.259798202048205</v>
+        <v>7.24266892208129</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B100" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C100" t="n">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D100" t="n">
-        <v>93.45250265423572</v>
+        <v>85.17020859058194</v>
       </c>
       <c r="E100" t="n">
-        <v>484.9</v>
+        <v>444.31</v>
       </c>
       <c r="F100" t="n">
-        <v>151.8902705166774</v>
+        <v>165.7662266740269</v>
       </c>
       <c r="G100" t="n">
-        <v>6301.06977057217</v>
+        <v>38031.88441025994</v>
       </c>
       <c r="H100" t="n">
-        <v>-1447.120354272668</v>
+        <v>-9109.297236292861</v>
       </c>
       <c r="I100" t="n">
-        <v>5.77</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>17.625</v>
+        <v>10.52</v>
       </c>
       <c r="K100" t="n">
-        <v>2.7</v>
+        <v>1.775</v>
       </c>
       <c r="L100" t="n">
-        <v>3.785</v>
+        <v>2.63</v>
       </c>
       <c r="M100" t="n">
-        <v>269.762677643332</v>
+        <v>208.1627949573518</v>
       </c>
       <c r="N100" t="n">
-        <v>5.259119322955875</v>
+        <v>7.24266892208129</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B101" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C101" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D101" t="n">
-        <v>93.42677108523303</v>
+        <v>93.51406360085934</v>
       </c>
       <c r="E101" t="n">
-        <v>486.465</v>
+        <v>478.61</v>
       </c>
       <c r="F101" t="n">
-        <v>151.4016263729906</v>
+        <v>153.8864465296105</v>
       </c>
       <c r="G101" t="n">
-        <v>6353.676339944446</v>
+        <v>6153.111703682009</v>
       </c>
       <c r="H101" t="n">
-        <v>-1418.653381854311</v>
+        <v>-1492.863309931552</v>
       </c>
       <c r="I101" t="n">
-        <v>5.92</v>
+        <v>5.72</v>
       </c>
       <c r="J101" t="n">
-        <v>17.985</v>
+        <v>16.6</v>
       </c>
       <c r="K101" t="n">
-        <v>2.875</v>
+        <v>2.550000000000001</v>
       </c>
       <c r="L101" t="n">
-        <v>3.96</v>
+        <v>3.620000000000001</v>
       </c>
       <c r="M101" t="n">
-        <v>227.387166189546</v>
+        <v>276.6878172939188</v>
       </c>
       <c r="N101" t="n">
-        <v>5.259119322955875</v>
+        <v>5.259746042528284</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B102" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C102" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D102" t="n">
-        <v>93.38624724840726</v>
+        <v>93.46072563038759</v>
       </c>
       <c r="E102" t="n">
-        <v>490.03</v>
+        <v>482.945</v>
       </c>
       <c r="F102" t="n">
-        <v>150.3001697315202</v>
+        <v>152.5051344843344</v>
       </c>
       <c r="G102" t="n">
-        <v>6445.731747995634</v>
+        <v>6272.605052490439</v>
       </c>
       <c r="H102" t="n">
-        <v>-1383.163908665368</v>
+        <v>-1444.424203516434</v>
       </c>
       <c r="I102" t="n">
-        <v>6.11</v>
+        <v>5.955</v>
       </c>
       <c r="J102" t="n">
-        <v>18.39</v>
+        <v>17.06</v>
       </c>
       <c r="K102" t="n">
-        <v>3.055</v>
+        <v>2.654999999999999</v>
       </c>
       <c r="L102" t="n">
-        <v>4.140000000000001</v>
+        <v>3.835</v>
       </c>
       <c r="M102" t="n">
-        <v>227.3868800057831</v>
+        <v>252.5095289898121</v>
       </c>
       <c r="N102" t="n">
-        <v>5.259119322955875</v>
+        <v>5.259746042528284</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B103" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C103" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D103" t="n">
-        <v>93.41591029275426</v>
+        <v>93.42556059685845</v>
       </c>
       <c r="E103" t="n">
-        <v>481.545</v>
+        <v>486.395</v>
       </c>
       <c r="F103" t="n">
-        <v>152.9485139987683</v>
+        <v>151.4234154823484</v>
       </c>
       <c r="G103" t="n">
-        <v>6530.938266738748</v>
+        <v>6355.202896443663</v>
       </c>
       <c r="H103" t="n">
-        <v>-1565.303400950452</v>
+        <v>-1416.35211739665</v>
       </c>
       <c r="I103" t="n">
-        <v>5.765</v>
+        <v>6.21</v>
       </c>
       <c r="J103" t="n">
-        <v>16.845</v>
+        <v>17.53</v>
       </c>
       <c r="K103" t="n">
-        <v>2.605</v>
+        <v>2.75</v>
       </c>
       <c r="L103" t="n">
-        <v>3.685</v>
+        <v>4.02</v>
       </c>
       <c r="M103" t="n">
-        <v>274.6352173903875</v>
+        <v>217.611783644889</v>
       </c>
       <c r="N103" t="n">
-        <v>5.259145247383652</v>
+        <v>5.259746042528284</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B104" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C104" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D104" t="n">
-        <v>93.39001183292956</v>
+        <v>93.46843332897606</v>
       </c>
       <c r="E104" t="n">
-        <v>482.945</v>
+        <v>476.365</v>
       </c>
       <c r="F104" t="n">
-        <v>152.5051344843344</v>
+        <v>154.6116783842996</v>
       </c>
       <c r="G104" t="n">
-        <v>6583.057698376676</v>
+        <v>6405.248870609407</v>
       </c>
       <c r="H104" t="n">
-        <v>-1535.832889914837</v>
+        <v>-1604.841963370349</v>
       </c>
       <c r="I104" t="n">
-        <v>5.905</v>
+        <v>5.725000000000001</v>
       </c>
       <c r="J104" t="n">
-        <v>17.195</v>
+        <v>15.92</v>
       </c>
       <c r="K104" t="n">
-        <v>2.775</v>
+        <v>2.47</v>
       </c>
       <c r="L104" t="n">
-        <v>3.86</v>
+        <v>3.54</v>
       </c>
       <c r="M104" t="n">
-        <v>227.4493457435706</v>
+        <v>281.683010309403</v>
       </c>
       <c r="N104" t="n">
-        <v>5.259145247383652</v>
+        <v>5.259773801395505</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B105" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C105" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D105" t="n">
-        <v>93.33698224806081</v>
+        <v>93.41632642975102</v>
       </c>
       <c r="E105" t="n">
-        <v>486</v>
+        <v>480.225</v>
       </c>
       <c r="F105" t="n">
-        <v>151.5464859537796</v>
+        <v>153.3689253444466</v>
       </c>
       <c r="G105" t="n">
-        <v>6692.840471458085</v>
+        <v>6520.856114310886</v>
       </c>
       <c r="H105" t="n">
-        <v>-1478.632015084863</v>
+        <v>-1556.424692098753</v>
       </c>
       <c r="I105" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="J105" t="n">
-        <v>17.595</v>
+        <v>16.355</v>
       </c>
       <c r="K105" t="n">
-        <v>2.955</v>
+        <v>2.565</v>
       </c>
       <c r="L105" t="n">
-        <v>4.035</v>
+        <v>3.73</v>
       </c>
       <c r="M105" t="n">
-        <v>227.4474126794829</v>
+        <v>252.5506025773835</v>
       </c>
       <c r="N105" t="n">
-        <v>5.259145247383652</v>
+        <v>5.259773801395505</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B106" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C106" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D106" t="n">
-        <v>93.38487797562313</v>
+        <v>93.38470158508471</v>
       </c>
       <c r="E106" t="n">
-        <v>477.69</v>
+        <v>483.175</v>
       </c>
       <c r="F106" t="n">
-        <v>154.1828218583954</v>
+        <v>152.4325392943279</v>
       </c>
       <c r="G106" t="n">
-        <v>6745.057849636835</v>
+        <v>6594.837628184146</v>
       </c>
       <c r="H106" t="n">
-        <v>-1685.38552511403</v>
+        <v>-1530.901072374127</v>
       </c>
       <c r="I106" t="n">
-        <v>5.76</v>
+        <v>6.19</v>
       </c>
       <c r="J106" t="n">
-        <v>16.175</v>
+        <v>16.835</v>
       </c>
       <c r="K106" t="n">
-        <v>2.524999999999999</v>
+        <v>2.66</v>
       </c>
       <c r="L106" t="n">
-        <v>3.605</v>
+        <v>3.915</v>
       </c>
       <c r="M106" t="n">
-        <v>279.345096598119</v>
+        <v>217.6849423681168</v>
       </c>
       <c r="N106" t="n">
-        <v>5.259169007902681</v>
+        <v>5.259773801395505</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B107" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C107" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D107" t="n">
-        <v>93.34182304590459</v>
+        <v>93.43566194116374</v>
       </c>
       <c r="E107" t="n">
-        <v>480.265</v>
+        <v>472.575</v>
       </c>
       <c r="F107" t="n">
-        <v>153.3561516528102</v>
+        <v>155.8516471957612</v>
       </c>
       <c r="G107" t="n">
-        <v>6836.346687415179</v>
+        <v>6621.745409759462</v>
       </c>
       <c r="H107" t="n">
-        <v>-1641.131631885564</v>
+        <v>-1721.777563608836</v>
       </c>
       <c r="I107" t="n">
-        <v>5.89</v>
+        <v>5.73</v>
       </c>
       <c r="J107" t="n">
-        <v>16.525</v>
+        <v>15.35</v>
       </c>
       <c r="K107" t="n">
-        <v>2.694999999999999</v>
+        <v>2.41</v>
       </c>
       <c r="L107" t="n">
-        <v>3.775</v>
+        <v>3.485</v>
       </c>
       <c r="M107" t="n">
-        <v>227.5122438338848</v>
+        <v>286.5115313664276</v>
       </c>
       <c r="N107" t="n">
-        <v>5.259169007902681</v>
+        <v>5.259798202048205</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B108" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C108" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D108" t="n">
-        <v>93.29647038871212</v>
+        <v>93.37423222341569</v>
       </c>
       <c r="E108" t="n">
-        <v>482.67</v>
+        <v>476.835</v>
       </c>
       <c r="F108" t="n">
-        <v>152.5920238952843</v>
+        <v>154.4592829249884</v>
       </c>
       <c r="G108" t="n">
-        <v>6928.78597366593</v>
+        <v>6757.198730392972</v>
       </c>
       <c r="H108" t="n">
-        <v>-1590.767787306452</v>
+        <v>-1663.892522353884</v>
       </c>
       <c r="I108" t="n">
-        <v>6.07</v>
+        <v>5.92</v>
       </c>
       <c r="J108" t="n">
-        <v>16.91</v>
+        <v>15.76</v>
       </c>
       <c r="K108" t="n">
-        <v>2.87</v>
+        <v>2.505</v>
       </c>
       <c r="L108" t="n">
-        <v>3.950000000000001</v>
+        <v>3.649999999999999</v>
       </c>
       <c r="M108" t="n">
-        <v>227.5233010492316</v>
+        <v>252.6008943792451</v>
       </c>
       <c r="N108" t="n">
-        <v>5.259169007902681</v>
+        <v>5.259798202048205</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="B109" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C109" t="n">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D109" t="n">
-        <v>93.52344188381194</v>
+        <v>93.34673725956608</v>
       </c>
       <c r="E109" t="n">
-        <v>486.865</v>
+        <v>479.95</v>
       </c>
       <c r="F109" t="n">
-        <v>151.2772373728587</v>
+        <v>153.4568021117551</v>
       </c>
       <c r="G109" t="n">
-        <v>5978.49564190572</v>
+        <v>6826.573749712831</v>
       </c>
       <c r="H109" t="n">
-        <v>-1344.201364050864</v>
+        <v>-1646.831322890376</v>
       </c>
       <c r="I109" t="n">
-        <v>5.845</v>
+        <v>6.175</v>
       </c>
       <c r="J109" t="n">
-        <v>17.97</v>
+        <v>16.235</v>
       </c>
       <c r="K109" t="n">
-        <v>2.675</v>
+        <v>2.600000000000001</v>
       </c>
       <c r="L109" t="n">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="M109" t="n">
-        <v>261.2478496081201</v>
+        <v>217.7683663567076</v>
       </c>
       <c r="N109" t="n">
-        <v>5.252678710798757</v>
+        <v>5.259798202048205</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B110" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C110" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D110" t="n">
-        <v>93.510352875904</v>
+        <v>93.45250265423572</v>
       </c>
       <c r="E110" t="n">
-        <v>487.765</v>
+        <v>484.9</v>
       </c>
       <c r="F110" t="n">
-        <v>150.9981080510838</v>
+        <v>151.8902705166774</v>
       </c>
       <c r="G110" t="n">
-        <v>6004.499379622453</v>
+        <v>6301.06977057217</v>
       </c>
       <c r="H110" t="n">
-        <v>-1328.94116491731</v>
+        <v>-1447.120354272668</v>
       </c>
       <c r="I110" t="n">
-        <v>5.985</v>
+        <v>5.77</v>
       </c>
       <c r="J110" t="n">
-        <v>18.325</v>
+        <v>17.625</v>
       </c>
       <c r="K110" t="n">
-        <v>2.850000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="L110" t="n">
-        <v>3.935</v>
+        <v>3.785</v>
       </c>
       <c r="M110" t="n">
-        <v>227.3276642712568</v>
+        <v>269.762677643332</v>
       </c>
       <c r="N110" t="n">
-        <v>5.252678710798757</v>
+        <v>5.259119322955875</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B111" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C111" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D111" t="n">
-        <v>93.46947467146789</v>
+        <v>93.42677108523303</v>
       </c>
       <c r="E111" t="n">
-        <v>491.76</v>
+        <v>486.465</v>
       </c>
       <c r="F111" t="n">
-        <v>149.7714173042477</v>
+        <v>151.4016263729906</v>
       </c>
       <c r="G111" t="n">
-        <v>6098.474812084224</v>
+        <v>6353.676339944446</v>
       </c>
       <c r="H111" t="n">
-        <v>-1294.215376117578</v>
+        <v>-1418.653381854311</v>
       </c>
       <c r="I111" t="n">
-        <v>6.17</v>
+        <v>5.92</v>
       </c>
       <c r="J111" t="n">
-        <v>18.73</v>
+        <v>17.985</v>
       </c>
       <c r="K111" t="n">
-        <v>3.025</v>
+        <v>2.875</v>
       </c>
       <c r="L111" t="n">
-        <v>4.11</v>
+        <v>3.96</v>
       </c>
       <c r="M111" t="n">
-        <v>227.3237025252131</v>
+        <v>227.387166189546</v>
       </c>
       <c r="N111" t="n">
-        <v>5.252678710798757</v>
+        <v>5.259119322955875</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B112" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C112" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D112" t="n">
-        <v>93.49552562765908</v>
+        <v>93.38624724840726</v>
       </c>
       <c r="E112" t="n">
-        <v>482.51</v>
+        <v>490.03</v>
       </c>
       <c r="F112" t="n">
-        <v>152.6426233104741</v>
+        <v>150.3001697315202</v>
       </c>
       <c r="G112" t="n">
-        <v>6177.560557045344</v>
+        <v>6445.731747995634</v>
       </c>
       <c r="H112" t="n">
-        <v>-1458.447798458095</v>
+        <v>-1383.163908665368</v>
       </c>
       <c r="I112" t="n">
-        <v>5.83</v>
+        <v>6.11</v>
       </c>
       <c r="J112" t="n">
-        <v>17.14</v>
+        <v>18.39</v>
       </c>
       <c r="K112" t="n">
-        <v>2.59</v>
+        <v>3.055</v>
       </c>
       <c r="L112" t="n">
-        <v>3.67</v>
+        <v>4.140000000000001</v>
       </c>
       <c r="M112" t="n">
-        <v>265.9538786030489</v>
+        <v>227.3868800057831</v>
       </c>
       <c r="N112" t="n">
-        <v>5.25270413490255</v>
+        <v>5.259119322955875</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B113" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C113" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D113" t="n">
-        <v>93.46407091502158</v>
+        <v>93.41591029275426</v>
       </c>
       <c r="E113" t="n">
-        <v>484.135</v>
+        <v>481.545</v>
       </c>
       <c r="F113" t="n">
-        <v>152.1302780702425</v>
+        <v>152.9485139987683</v>
       </c>
       <c r="G113" t="n">
-        <v>6239.26552564235</v>
+        <v>6530.938266738748</v>
       </c>
       <c r="H113" t="n">
-        <v>-1421.012016389429</v>
+        <v>-1565.303400950452</v>
       </c>
       <c r="I113" t="n">
-        <v>5.965</v>
+        <v>5.765</v>
       </c>
       <c r="J113" t="n">
-        <v>17.485</v>
+        <v>16.845</v>
       </c>
       <c r="K113" t="n">
-        <v>2.755</v>
+        <v>2.605</v>
       </c>
       <c r="L113" t="n">
-        <v>3.84</v>
+        <v>3.685</v>
       </c>
       <c r="M113" t="n">
-        <v>227.3787156649078</v>
+        <v>274.6352173903875</v>
       </c>
       <c r="N113" t="n">
-        <v>5.25270413490255</v>
+        <v>5.259145247383652</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B114" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C114" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D114" t="n">
-        <v>93.42020557120924</v>
+        <v>93.39001183292956</v>
       </c>
       <c r="E114" t="n">
-        <v>487.125</v>
+        <v>482.945</v>
       </c>
       <c r="F114" t="n">
-        <v>151.1964940693597</v>
+        <v>152.5051344843344</v>
       </c>
       <c r="G114" t="n">
-        <v>6331.624498374702</v>
+        <v>6583.057698376676</v>
       </c>
       <c r="H114" t="n">
-        <v>-1375.228079086551</v>
+        <v>-1535.832889914837</v>
       </c>
       <c r="I114" t="n">
-        <v>6.140000000000001</v>
+        <v>5.905</v>
       </c>
       <c r="J114" t="n">
-        <v>17.88</v>
+        <v>17.195</v>
       </c>
       <c r="K114" t="n">
-        <v>2.935</v>
+        <v>2.775</v>
       </c>
       <c r="L114" t="n">
-        <v>4.015000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="M114" t="n">
-        <v>227.3868420862642</v>
+        <v>227.4493457435706</v>
       </c>
       <c r="N114" t="n">
-        <v>5.25270413490255</v>
+        <v>5.259145247383652</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B115" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C115" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D115" t="n">
-        <v>93.46203382968781</v>
+        <v>93.33698224806081</v>
       </c>
       <c r="E115" t="n">
-        <v>478.79</v>
+        <v>486</v>
       </c>
       <c r="F115" t="n">
-        <v>153.828593273746</v>
+        <v>151.5464859537796</v>
       </c>
       <c r="G115" t="n">
-        <v>6387.147371594431</v>
+        <v>6692.840471458085</v>
       </c>
       <c r="H115" t="n">
-        <v>-1565.790686198157</v>
+        <v>-1478.632015084863</v>
       </c>
       <c r="I115" t="n">
-        <v>5.825</v>
+        <v>6.09</v>
       </c>
       <c r="J115" t="n">
-        <v>16.43</v>
+        <v>17.595</v>
       </c>
       <c r="K115" t="n">
-        <v>2.52</v>
+        <v>2.955</v>
       </c>
       <c r="L115" t="n">
-        <v>3.600000000000001</v>
+        <v>4.035</v>
       </c>
       <c r="M115" t="n">
-        <v>270.5029847093602</v>
+        <v>227.4474126794829</v>
       </c>
       <c r="N115" t="n">
-        <v>5.252726696375484</v>
+        <v>5.259145247383652</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B116" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C116" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D116" t="n">
-        <v>93.42602857046694</v>
+        <v>93.38487797562313</v>
       </c>
       <c r="E116" t="n">
-        <v>481.3</v>
+        <v>477.69</v>
       </c>
       <c r="F116" t="n">
-        <v>153.0263706078057</v>
+        <v>154.1828218583954</v>
       </c>
       <c r="G116" t="n">
-        <v>6464.619020264462</v>
+        <v>6745.057849636835</v>
       </c>
       <c r="H116" t="n">
-        <v>-1529.879517998228</v>
+        <v>-1685.38552511403</v>
       </c>
       <c r="I116" t="n">
-        <v>5.945</v>
+        <v>5.76</v>
       </c>
       <c r="J116" t="n">
-        <v>16.765</v>
+        <v>16.175</v>
       </c>
       <c r="K116" t="n">
-        <v>2.68</v>
+        <v>2.524999999999999</v>
       </c>
       <c r="L116" t="n">
-        <v>3.76</v>
+        <v>3.605</v>
       </c>
       <c r="M116" t="n">
-        <v>227.4449342895346</v>
+        <v>279.345096598119</v>
       </c>
       <c r="N116" t="n">
-        <v>5.252726696375484</v>
+        <v>5.259169007902681</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B117" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C117" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D117" t="n">
-        <v>93.38258710001347</v>
+        <v>93.34182304590459</v>
       </c>
       <c r="E117" t="n">
-        <v>483.63</v>
+        <v>480.265</v>
       </c>
       <c r="F117" t="n">
-        <v>152.2891304789547</v>
+        <v>153.3561516528102</v>
       </c>
       <c r="G117" t="n">
-        <v>6551.853031023486</v>
+        <v>6836.346687415179</v>
       </c>
       <c r="H117" t="n">
-        <v>-1480.279716189877</v>
+        <v>-1641.131631885564</v>
       </c>
       <c r="I117" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="J117" t="n">
-        <v>17.16</v>
+        <v>16.525</v>
       </c>
       <c r="K117" t="n">
-        <v>2.86</v>
+        <v>2.694999999999999</v>
       </c>
       <c r="L117" t="n">
-        <v>3.94</v>
+        <v>3.775</v>
       </c>
       <c r="M117" t="n">
-        <v>227.451941689032</v>
+        <v>227.5122438338848</v>
       </c>
       <c r="N117" t="n">
-        <v>5.252726696375484</v>
+        <v>5.259169007902681</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B118" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C118" t="n">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D118" t="n">
-        <v>93.49668303760703</v>
+        <v>93.29647038871212</v>
       </c>
       <c r="E118" t="n">
-        <v>490.235</v>
+        <v>482.67</v>
       </c>
       <c r="F118" t="n">
-        <v>150.2373191908715</v>
+        <v>152.5920238952843</v>
       </c>
       <c r="G118" t="n">
-        <v>6045.612332308569</v>
+        <v>6928.78597366593</v>
       </c>
       <c r="H118" t="n">
-        <v>-1327.114476265482</v>
+        <v>-1590.767787306452</v>
       </c>
       <c r="I118" t="n">
-        <v>5.885</v>
+        <v>6.07</v>
       </c>
       <c r="J118" t="n">
-        <v>18.635</v>
+        <v>16.91</v>
       </c>
       <c r="K118" t="n">
-        <v>2.760000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="L118" t="n">
-        <v>3.850000000000001</v>
+        <v>3.950000000000001</v>
       </c>
       <c r="M118" t="n">
-        <v>259.1072797243198</v>
+        <v>227.5233010492316</v>
       </c>
       <c r="N118" t="n">
-        <v>5.253775613092472</v>
+        <v>5.259169007902681</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B119" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C119" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D119" t="n">
-        <v>93.47820692696499</v>
+        <v>93.52344188381194</v>
       </c>
       <c r="E119" t="n">
-        <v>491.13</v>
+        <v>486.865</v>
       </c>
       <c r="F119" t="n">
-        <v>149.9635375023657</v>
+        <v>151.2772373728587</v>
       </c>
       <c r="G119" t="n">
-        <v>6080.621469916417</v>
+        <v>5978.49564190572</v>
       </c>
       <c r="H119" t="n">
-        <v>-1303.877010159506</v>
+        <v>-1344.201364050864</v>
       </c>
       <c r="I119" t="n">
-        <v>6.035</v>
+        <v>5.845</v>
       </c>
       <c r="J119" t="n">
-        <v>19.005</v>
+        <v>17.97</v>
       </c>
       <c r="K119" t="n">
-        <v>2.935</v>
+        <v>2.675</v>
       </c>
       <c r="L119" t="n">
-        <v>4.025</v>
+        <v>3.76</v>
       </c>
       <c r="M119" t="n">
-        <v>227.2887429361407</v>
+        <v>261.2478496081201</v>
       </c>
       <c r="N119" t="n">
-        <v>5.253775613092472</v>
+        <v>5.252678710798757</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B120" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C120" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D120" t="n">
-        <v>93.43841750829837</v>
+        <v>93.510352875904</v>
       </c>
       <c r="E120" t="n">
-        <v>494.625</v>
+        <v>487.765</v>
       </c>
       <c r="F120" t="n">
-        <v>148.9039012858971</v>
+        <v>150.9981080510838</v>
       </c>
       <c r="G120" t="n">
-        <v>6169.331357784015</v>
+        <v>6004.499379622453</v>
       </c>
       <c r="H120" t="n">
-        <v>-1267.299226715</v>
+        <v>-1328.94116491731</v>
       </c>
       <c r="I120" t="n">
-        <v>6.225000000000001</v>
+        <v>5.985</v>
       </c>
       <c r="J120" t="n">
-        <v>19.415</v>
+        <v>18.325</v>
       </c>
       <c r="K120" t="n">
-        <v>3.115</v>
+        <v>2.850000000000001</v>
       </c>
       <c r="L120" t="n">
-        <v>4.205</v>
+        <v>3.935</v>
       </c>
       <c r="M120" t="n">
-        <v>227.2953521330323</v>
+        <v>227.3276642712568</v>
       </c>
       <c r="N120" t="n">
-        <v>5.253775613092472</v>
+        <v>5.252678710798757</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B121" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C121" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D121" t="n">
-        <v>93.4668841967427</v>
+        <v>93.46947467146789</v>
       </c>
       <c r="E121" t="n">
-        <v>485.125</v>
+        <v>491.76</v>
       </c>
       <c r="F121" t="n">
-        <v>151.8198241144795</v>
+        <v>149.7714173042477</v>
       </c>
       <c r="G121" t="n">
-        <v>6243.154855929256</v>
+        <v>6098.474812084224</v>
       </c>
       <c r="H121" t="n">
-        <v>-1433.859687118748</v>
+        <v>-1294.215376117578</v>
       </c>
       <c r="I121" t="n">
-        <v>5.865</v>
+        <v>6.17</v>
       </c>
       <c r="J121" t="n">
-        <v>17.735</v>
+        <v>18.73</v>
       </c>
       <c r="K121" t="n">
-        <v>2.655</v>
+        <v>3.025</v>
       </c>
       <c r="L121" t="n">
-        <v>3.740000000000001</v>
+        <v>4.11</v>
       </c>
       <c r="M121" t="n">
-        <v>263.7794622573939</v>
+        <v>227.3237025252131</v>
       </c>
       <c r="N121" t="n">
-        <v>5.253800030107287</v>
+        <v>5.252678710798757</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B122" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C122" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D122" t="n">
-        <v>93.43924305446829</v>
+        <v>93.49552562765908</v>
       </c>
       <c r="E122" t="n">
-        <v>486.945</v>
+        <v>482.51</v>
       </c>
       <c r="F122" t="n">
-        <v>151.2523840958155</v>
+        <v>152.6426233104741</v>
       </c>
       <c r="G122" t="n">
-        <v>6300.527779996564</v>
+        <v>6177.560557045344</v>
       </c>
       <c r="H122" t="n">
-        <v>-1404.168843255348</v>
+        <v>-1458.447798458095</v>
       </c>
       <c r="I122" t="n">
-        <v>6.01</v>
+        <v>5.83</v>
       </c>
       <c r="J122" t="n">
-        <v>18.09</v>
+        <v>17.14</v>
       </c>
       <c r="K122" t="n">
-        <v>2.825</v>
+        <v>2.59</v>
       </c>
       <c r="L122" t="n">
-        <v>3.915</v>
+        <v>3.67</v>
       </c>
       <c r="M122" t="n">
-        <v>227.352599736636</v>
+        <v>265.9538786030489</v>
       </c>
       <c r="N122" t="n">
-        <v>5.253800030107287</v>
+        <v>5.25270413490255</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B123" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C123" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D123" t="n">
-        <v>93.39637801442582</v>
+        <v>93.46407091502158</v>
       </c>
       <c r="E123" t="n">
-        <v>490.185</v>
+        <v>484.135</v>
       </c>
       <c r="F123" t="n">
-        <v>150.2526437437638</v>
+        <v>152.1302780702425</v>
       </c>
       <c r="G123" t="n">
-        <v>6393.388847486058</v>
+        <v>6239.26552564235</v>
       </c>
       <c r="H123" t="n">
-        <v>-1362.057631311027</v>
+        <v>-1421.012016389429</v>
       </c>
       <c r="I123" t="n">
-        <v>6.19</v>
+        <v>5.965</v>
       </c>
       <c r="J123" t="n">
-        <v>18.495</v>
+        <v>17.485</v>
       </c>
       <c r="K123" t="n">
-        <v>3</v>
+        <v>2.755</v>
       </c>
       <c r="L123" t="n">
-        <v>4.09</v>
+        <v>3.84</v>
       </c>
       <c r="M123" t="n">
-        <v>227.3420875786154</v>
+        <v>227.3787156649078</v>
       </c>
       <c r="N123" t="n">
-        <v>5.253800030107287</v>
+        <v>5.25270413490255</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B124" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C124" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D124" t="n">
-        <v>93.42137308458253</v>
+        <v>93.42020557120924</v>
       </c>
       <c r="E124" t="n">
-        <v>482.165</v>
+        <v>487.125</v>
       </c>
       <c r="F124" t="n">
-        <v>152.7518425716028</v>
+        <v>151.1964940693597</v>
       </c>
       <c r="G124" t="n">
-        <v>6479.047213315419</v>
+        <v>6331.624498374702</v>
       </c>
       <c r="H124" t="n">
-        <v>-1529.706420525139</v>
+        <v>-1375.228079086551</v>
       </c>
       <c r="I124" t="n">
-        <v>5.850000000000001</v>
+        <v>6.140000000000001</v>
       </c>
       <c r="J124" t="n">
-        <v>16.965</v>
+        <v>17.88</v>
       </c>
       <c r="K124" t="n">
-        <v>2.575</v>
+        <v>2.935</v>
       </c>
       <c r="L124" t="n">
-        <v>3.655</v>
+        <v>4.015000000000001</v>
       </c>
       <c r="M124" t="n">
-        <v>268.295846627913</v>
+        <v>227.3868420862642</v>
       </c>
       <c r="N124" t="n">
-        <v>5.253821452617513</v>
+        <v>5.25270413490255</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B125" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C125" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D125" t="n">
-        <v>93.40234395983778</v>
+        <v>93.46203382968781</v>
       </c>
       <c r="E125" t="n">
-        <v>483.125</v>
+        <v>478.79</v>
       </c>
       <c r="F125" t="n">
-        <v>152.4483149775666</v>
+        <v>153.828593273746</v>
       </c>
       <c r="G125" t="n">
-        <v>6516.620962005842</v>
+        <v>6387.147371594431</v>
       </c>
       <c r="H125" t="n">
-        <v>-1507.309488925367</v>
+        <v>-1565.790686198157</v>
       </c>
       <c r="I125" t="n">
-        <v>5.98</v>
+        <v>5.825</v>
       </c>
       <c r="J125" t="n">
-        <v>17.31</v>
+        <v>16.43</v>
       </c>
       <c r="K125" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="L125" t="n">
-        <v>3.825</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="M125" t="n">
-        <v>227.4084175622542</v>
+        <v>270.5029847093602</v>
       </c>
       <c r="N125" t="n">
-        <v>5.253821452617513</v>
+        <v>5.252726696375484</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B126" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C126" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D126" t="n">
-        <v>93.35359060253191</v>
+        <v>93.42602857046694</v>
       </c>
       <c r="E126" t="n">
-        <v>486.345</v>
+        <v>481.3</v>
       </c>
       <c r="F126" t="n">
-        <v>151.4389829720402</v>
+        <v>153.0263706078057</v>
       </c>
       <c r="G126" t="n">
-        <v>6620.170264683915</v>
+        <v>6464.619020264462</v>
       </c>
       <c r="H126" t="n">
-        <v>-1457.370108947124</v>
+        <v>-1529.879517998228</v>
       </c>
       <c r="I126" t="n">
-        <v>6.16</v>
+        <v>5.945</v>
       </c>
       <c r="J126" t="n">
-        <v>17.715</v>
+        <v>16.765</v>
       </c>
       <c r="K126" t="n">
-        <v>2.915</v>
+        <v>2.68</v>
       </c>
       <c r="L126" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="M126" t="n">
-        <v>227.4019882001658</v>
+        <v>227.4449342895346</v>
       </c>
       <c r="N126" t="n">
-        <v>5.253821452617513</v>
+        <v>5.252726696375484</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B127" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C127" t="n">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D127" t="n">
-        <v>93.44950313997633</v>
+        <v>93.38258710001347</v>
       </c>
       <c r="E127" t="n">
-        <v>484.67</v>
+        <v>483.63</v>
       </c>
       <c r="F127" t="n">
-        <v>151.9623499980128</v>
+        <v>152.2891304789547</v>
       </c>
       <c r="G127" t="n">
-        <v>6304.574082983689</v>
+        <v>6551.853031023486</v>
       </c>
       <c r="H127" t="n">
-        <v>-1441.120075954446</v>
+        <v>-1480.279716189877</v>
       </c>
       <c r="I127" t="n">
-        <v>6.525</v>
+        <v>6.12</v>
       </c>
       <c r="J127" t="n">
-        <v>18.865</v>
+        <v>17.16</v>
       </c>
       <c r="K127" t="n">
-        <v>2.965000000000001</v>
+        <v>2.86</v>
       </c>
       <c r="L127" t="n">
-        <v>4.290000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="M127" t="n">
-        <v>279.4807482110015</v>
+        <v>227.451941689032</v>
       </c>
       <c r="N127" t="n">
-        <v>4.258269327761364</v>
+        <v>5.252726696375484</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B128" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C128" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D128" t="n">
-        <v>93.39692195319739</v>
+        <v>93.49668303760703</v>
       </c>
       <c r="E128" t="n">
-        <v>489</v>
+        <v>490.235</v>
       </c>
       <c r="F128" t="n">
-        <v>150.6167529111183</v>
+        <v>150.2373191908715</v>
       </c>
       <c r="G128" t="n">
-        <v>6422.933588566668</v>
+        <v>6045.612332308569</v>
       </c>
       <c r="H128" t="n">
-        <v>-1393.964606287007</v>
+        <v>-1327.114476265482</v>
       </c>
       <c r="I128" t="n">
-        <v>6.685</v>
+        <v>5.885</v>
       </c>
       <c r="J128" t="n">
-        <v>19.22</v>
+        <v>18.635</v>
       </c>
       <c r="K128" t="n">
-        <v>3.06</v>
+        <v>2.760000000000001</v>
       </c>
       <c r="L128" t="n">
-        <v>4.445</v>
+        <v>3.850000000000001</v>
       </c>
       <c r="M128" t="n">
-        <v>240.9661966467338</v>
+        <v>259.1072797243198</v>
       </c>
       <c r="N128" t="n">
-        <v>4.258269327761364</v>
+        <v>5.253775613092472</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B129" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C129" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D129" t="n">
-        <v>93.36183593718894</v>
+        <v>93.47820692696499</v>
       </c>
       <c r="E129" t="n">
-        <v>493.485</v>
+        <v>491.13</v>
       </c>
       <c r="F129" t="n">
-        <v>149.2478842792321</v>
+        <v>149.9635375023657</v>
       </c>
       <c r="G129" t="n">
-        <v>6513.942692845931</v>
+        <v>6080.621469916417</v>
       </c>
       <c r="H129" t="n">
-        <v>-1374.670840155953</v>
+        <v>-1303.877010159506</v>
       </c>
       <c r="I129" t="n">
-        <v>6.92</v>
+        <v>6.035</v>
       </c>
       <c r="J129" t="n">
-        <v>19.665</v>
+        <v>19.005</v>
       </c>
       <c r="K129" t="n">
-        <v>3.15</v>
+        <v>2.935</v>
       </c>
       <c r="L129" t="n">
-        <v>4.62</v>
+        <v>4.025</v>
       </c>
       <c r="M129" t="n">
-        <v>240.9687783972187</v>
+        <v>227.2887429361407</v>
       </c>
       <c r="N129" t="n">
-        <v>4.258269327761364</v>
+        <v>5.253775613092472</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C130" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D130" t="n">
-        <v>93.39912788985697</v>
+        <v>93.43841750829837</v>
       </c>
       <c r="E130" t="n">
-        <v>481.995</v>
+        <v>494.625</v>
       </c>
       <c r="F130" t="n">
-        <v>152.8057182616767</v>
+        <v>148.9039012858971</v>
       </c>
       <c r="G130" t="n">
-        <v>6564.006518884683</v>
+        <v>6169.331357784015</v>
       </c>
       <c r="H130" t="n">
-        <v>-1545.47621310465</v>
+        <v>-1267.299226715</v>
       </c>
       <c r="I130" t="n">
-        <v>5.795</v>
+        <v>6.225000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>17.305</v>
+        <v>19.415</v>
       </c>
       <c r="K130" t="n">
-        <v>2.685</v>
+        <v>3.115</v>
       </c>
       <c r="L130" t="n">
-        <v>3.755</v>
+        <v>4.205</v>
       </c>
       <c r="M130" t="n">
-        <v>284.5657489351358</v>
+        <v>227.2953521330323</v>
       </c>
       <c r="N130" t="n">
-        <v>5.273768929319832</v>
+        <v>5.253775613092472</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B131" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C131" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D131" t="n">
-        <v>93.35960181649196</v>
+        <v>93.4668841967427</v>
       </c>
       <c r="E131" t="n">
-        <v>484.585</v>
+        <v>485.125</v>
       </c>
       <c r="F131" t="n">
-        <v>151.9890053830326</v>
+        <v>151.8198241144795</v>
       </c>
       <c r="G131" t="n">
-        <v>6648.124310726644</v>
+        <v>6243.154855929256</v>
       </c>
       <c r="H131" t="n">
-        <v>-1505.149558068831</v>
+        <v>-1433.859687118748</v>
       </c>
       <c r="I131" t="n">
-        <v>6.05</v>
+        <v>5.865</v>
       </c>
       <c r="J131" t="n">
-        <v>17.755</v>
+        <v>17.735</v>
       </c>
       <c r="K131" t="n">
-        <v>2.78</v>
+        <v>2.655</v>
       </c>
       <c r="L131" t="n">
-        <v>3.97</v>
+        <v>3.740000000000001</v>
       </c>
       <c r="M131" t="n">
-        <v>241.0251260639002</v>
+        <v>263.7794622573939</v>
       </c>
       <c r="N131" t="n">
-        <v>5.273117970311087</v>
+        <v>5.253800030107287</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B132" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C132" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D132" t="n">
-        <v>93.31885274704013</v>
+        <v>93.43924305446829</v>
       </c>
       <c r="E132" t="n">
-        <v>489.14</v>
+        <v>486.945</v>
       </c>
       <c r="F132" t="n">
-        <v>150.573643892417</v>
+        <v>151.2523840958155</v>
       </c>
       <c r="G132" t="n">
-        <v>6751.070800792269</v>
+        <v>6300.527779996564</v>
       </c>
       <c r="H132" t="n">
-        <v>-1479.988052872564</v>
+        <v>-1404.168843255348</v>
       </c>
       <c r="I132" t="n">
-        <v>6.32</v>
+        <v>6.01</v>
       </c>
       <c r="J132" t="n">
-        <v>18.235</v>
+        <v>18.09</v>
       </c>
       <c r="K132" t="n">
-        <v>2.875</v>
+        <v>2.825</v>
       </c>
       <c r="L132" t="n">
-        <v>4.16</v>
+        <v>3.915</v>
       </c>
       <c r="M132" t="n">
-        <v>241.0234083406213</v>
+        <v>227.352599736636</v>
       </c>
       <c r="N132" t="n">
-        <v>5.273117970311087</v>
+        <v>5.253800030107287</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B133" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C133" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D133" t="n">
-        <v>93.37124847310385</v>
+        <v>93.39637801442582</v>
       </c>
       <c r="E133" t="n">
-        <v>477.885</v>
+        <v>490.185</v>
       </c>
       <c r="F133" t="n">
-        <v>154.119907872264</v>
+        <v>150.2526437437638</v>
       </c>
       <c r="G133" t="n">
-        <v>6771.909738162929</v>
+        <v>6393.388847486058</v>
       </c>
       <c r="H133" t="n">
-        <v>-1669.285347663635</v>
+        <v>-1362.057631311027</v>
       </c>
       <c r="I133" t="n">
-        <v>5.78</v>
+        <v>6.19</v>
       </c>
       <c r="J133" t="n">
-        <v>16.6</v>
+        <v>18.495</v>
       </c>
       <c r="K133" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="L133" t="n">
-        <v>3.635</v>
+        <v>4.09</v>
       </c>
       <c r="M133" t="n">
-        <v>287.5103530514276</v>
+        <v>227.3420875786154</v>
       </c>
       <c r="N133" t="n">
-        <v>5.273789602585431</v>
+        <v>5.253800030107287</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B134" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C134" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D134" t="n">
-        <v>93.30922444465473</v>
+        <v>93.42137308458253</v>
       </c>
       <c r="E134" t="n">
-        <v>482.335</v>
+        <v>482.165</v>
       </c>
       <c r="F134" t="n">
-        <v>152.6980048587328</v>
+        <v>152.7518425716028</v>
       </c>
       <c r="G134" t="n">
-        <v>6909.773348486074</v>
+        <v>6479.047213315419</v>
       </c>
       <c r="H134" t="n">
-        <v>-1611.972212672484</v>
+        <v>-1529.706420525139</v>
       </c>
       <c r="I134" t="n">
-        <v>6.005</v>
+        <v>5.850000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>17.025</v>
+        <v>16.965</v>
       </c>
       <c r="K134" t="n">
-        <v>2.665</v>
+        <v>2.575</v>
       </c>
       <c r="L134" t="n">
-        <v>3.835</v>
+        <v>3.655</v>
       </c>
       <c r="M134" t="n">
-        <v>287.510554443335</v>
+        <v>268.295846627913</v>
       </c>
       <c r="N134" t="n">
-        <v>5.27327867551934</v>
+        <v>5.253821452617513</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B135" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C135" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D135" t="n">
-        <v>93.27663173036494</v>
+        <v>93.40234395983778</v>
       </c>
       <c r="E135" t="n">
-        <v>486.08</v>
+        <v>483.125</v>
       </c>
       <c r="F135" t="n">
-        <v>151.5215441358148</v>
+        <v>152.4483149775666</v>
       </c>
       <c r="G135" t="n">
-        <v>6993.642238947837</v>
+        <v>6516.620962005842</v>
       </c>
       <c r="H135" t="n">
-        <v>-1593.427607877492</v>
+        <v>-1507.309488925367</v>
       </c>
       <c r="I135" t="n">
-        <v>6.275</v>
+        <v>5.98</v>
       </c>
       <c r="J135" t="n">
-        <v>17.5</v>
+        <v>17.31</v>
       </c>
       <c r="K135" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="L135" t="n">
-        <v>4.02</v>
+        <v>3.825</v>
       </c>
       <c r="M135" t="n">
-        <v>241.0754108106297</v>
+        <v>227.4084175622542</v>
       </c>
       <c r="N135" t="n">
-        <v>5.27327867551934</v>
+        <v>5.253821452617513</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="B136" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C136" t="n">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="D136" t="n">
-        <v>93.7375789427103</v>
+        <v>93.35359060253191</v>
       </c>
       <c r="E136" t="n">
-        <v>474.85</v>
+        <v>486.345</v>
       </c>
       <c r="F136" t="n">
-        <v>155.1049640381949</v>
+        <v>151.4389829720402</v>
       </c>
       <c r="G136" t="n">
-        <v>5329.081592347652</v>
+        <v>6620.170264683915</v>
       </c>
       <c r="H136" t="n">
-        <v>-1365.873460059604</v>
+        <v>-1457.370108947124</v>
       </c>
       <c r="I136" t="n">
-        <v>5.755</v>
+        <v>6.16</v>
       </c>
       <c r="J136" t="n">
-        <v>16.005</v>
+        <v>17.715</v>
       </c>
       <c r="K136" t="n">
-        <v>2.55</v>
+        <v>2.915</v>
       </c>
       <c r="L136" t="n">
-        <v>3.615</v>
+        <v>4</v>
       </c>
       <c r="M136" t="n">
-        <v>300.0451389434209</v>
+        <v>227.4019882001658</v>
       </c>
       <c r="N136" t="n">
-        <v>5.276837814785707</v>
+        <v>5.253821452617513</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B137" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C137" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D137" t="n">
-        <v>93.70705125367142</v>
+        <v>93.44950313997633</v>
       </c>
       <c r="E137" t="n">
-        <v>477.415</v>
+        <v>484.67</v>
       </c>
       <c r="F137" t="n">
-        <v>154.2716340574487</v>
+        <v>151.9623499980128</v>
       </c>
       <c r="G137" t="n">
-        <v>5395.828628533539</v>
+        <v>6304.574082983689</v>
       </c>
       <c r="H137" t="n">
-        <v>-1336.413461609626</v>
+        <v>-1441.120075954446</v>
       </c>
       <c r="I137" t="n">
-        <v>5.915</v>
+        <v>6.525</v>
       </c>
       <c r="J137" t="n">
-        <v>16.465</v>
+        <v>18.865</v>
       </c>
       <c r="K137" t="n">
-        <v>2.649999999999999</v>
+        <v>2.965000000000001</v>
       </c>
       <c r="L137" t="n">
-        <v>3.835</v>
+        <v>4.290000000000001</v>
       </c>
       <c r="M137" t="n">
-        <v>274.8280685050329</v>
+        <v>279.4807482110015</v>
       </c>
       <c r="N137" t="n">
-        <v>5.276795302796649</v>
+        <v>4.258269327761364</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B138" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C138" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D138" t="n">
-        <v>93.66736972948365</v>
+        <v>93.39692195319739</v>
       </c>
       <c r="E138" t="n">
-        <v>481.67</v>
+        <v>489</v>
       </c>
       <c r="F138" t="n">
-        <v>152.9088217525212</v>
+        <v>150.6167529111183</v>
       </c>
       <c r="G138" t="n">
-        <v>5487.845062078589</v>
+        <v>6422.933588566668</v>
       </c>
       <c r="H138" t="n">
-        <v>-1303.427722412256</v>
+        <v>-1393.964606287007</v>
       </c>
       <c r="I138" t="n">
-        <v>6.105</v>
+        <v>6.685</v>
       </c>
       <c r="J138" t="n">
-        <v>16.965</v>
+        <v>19.22</v>
       </c>
       <c r="K138" t="n">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="L138" t="n">
-        <v>4.029999999999999</v>
+        <v>4.445</v>
       </c>
       <c r="M138" t="n">
-        <v>237.9234559192009</v>
+        <v>240.9661966467338</v>
       </c>
       <c r="N138" t="n">
-        <v>5.276795302796649</v>
+        <v>4.258269327761364</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B139" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C139" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D139" t="n">
-        <v>93.70509773020183</v>
+        <v>93.36183593718894</v>
       </c>
       <c r="E139" t="n">
-        <v>472.055</v>
+        <v>493.485</v>
       </c>
       <c r="F139" t="n">
-        <v>156.0233281578139</v>
+        <v>149.2478842792321</v>
       </c>
       <c r="G139" t="n">
-        <v>5529.88772868665</v>
+        <v>6513.942692845931</v>
       </c>
       <c r="H139" t="n">
-        <v>-1466.999094859334</v>
+        <v>-1374.670840155953</v>
       </c>
       <c r="I139" t="n">
-        <v>5.75</v>
+        <v>6.92</v>
       </c>
       <c r="J139" t="n">
-        <v>15.4</v>
+        <v>19.665</v>
       </c>
       <c r="K139" t="n">
-        <v>2.455</v>
+        <v>3.15</v>
       </c>
       <c r="L139" t="n">
-        <v>3.52</v>
+        <v>4.62</v>
       </c>
       <c r="M139" t="n">
-        <v>300.057823899897</v>
+        <v>240.9687783972187</v>
       </c>
       <c r="N139" t="n">
-        <v>5.276849632707642</v>
+        <v>4.258269327761364</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B140" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C140" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D140" t="n">
-        <v>93.67181804630056</v>
+        <v>93.39912788985697</v>
       </c>
       <c r="E140" t="n">
-        <v>474.585</v>
+        <v>481.995</v>
       </c>
       <c r="F140" t="n">
-        <v>155.1915719492544</v>
+        <v>152.8057182616767</v>
       </c>
       <c r="G140" t="n">
-        <v>5602.478434254266</v>
+        <v>6564.006518884683</v>
       </c>
       <c r="H140" t="n">
-        <v>-1434.724518811227</v>
+        <v>-1545.47621310465</v>
       </c>
       <c r="I140" t="n">
-        <v>5.895</v>
+        <v>5.795</v>
       </c>
       <c r="J140" t="n">
-        <v>15.85</v>
+        <v>17.305</v>
       </c>
       <c r="K140" t="n">
-        <v>2.55</v>
+        <v>2.685</v>
       </c>
       <c r="L140" t="n">
-        <v>3.715</v>
+        <v>3.755</v>
       </c>
       <c r="M140" t="n">
-        <v>274.866698194862</v>
+        <v>284.5657489351358</v>
       </c>
       <c r="N140" t="n">
-        <v>5.276816974753548</v>
+        <v>5.273768929319832</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B141" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C141" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D141" t="n">
-        <v>93.64238349983798</v>
+        <v>93.35960181649196</v>
       </c>
       <c r="E141" t="n">
-        <v>477.355</v>
+        <v>484.585</v>
       </c>
       <c r="F141" t="n">
-        <v>154.2910248631246</v>
+        <v>151.9890053830326</v>
       </c>
       <c r="G141" t="n">
-        <v>5669.039064292543</v>
+        <v>6648.124310726644</v>
       </c>
       <c r="H141" t="n">
-        <v>-1408.571100816436</v>
+        <v>-1505.149558068831</v>
       </c>
       <c r="I141" t="n">
-        <v>6.08</v>
+        <v>6.05</v>
       </c>
       <c r="J141" t="n">
-        <v>16.34</v>
+        <v>17.755</v>
       </c>
       <c r="K141" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="L141" t="n">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="M141" t="n">
-        <v>237.9996639240671</v>
+        <v>241.0251260639002</v>
       </c>
       <c r="N141" t="n">
-        <v>5.276816974753548</v>
+        <v>5.273117970311087</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B142" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C142" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D142" t="n">
-        <v>93.66794361387699</v>
+        <v>93.31885274704013</v>
       </c>
       <c r="E142" t="n">
-        <v>469.655</v>
+        <v>489.14</v>
       </c>
       <c r="F142" t="n">
-        <v>156.8206282772181</v>
+        <v>150.573643892417</v>
       </c>
       <c r="G142" t="n">
-        <v>5741.700304435783</v>
+        <v>6751.070800792269</v>
       </c>
       <c r="H142" t="n">
-        <v>-1564.573877329694</v>
+        <v>-1479.988052872564</v>
       </c>
       <c r="I142" t="n">
-        <v>5.755</v>
+        <v>6.32</v>
       </c>
       <c r="J142" t="n">
-        <v>14.94</v>
+        <v>18.235</v>
       </c>
       <c r="K142" t="n">
-        <v>2.409999999999999</v>
+        <v>2.875</v>
       </c>
       <c r="L142" t="n">
-        <v>3.47</v>
+        <v>4.16</v>
       </c>
       <c r="M142" t="n">
-        <v>300.0685310526121</v>
+        <v>241.0234083406213</v>
       </c>
       <c r="N142" t="n">
-        <v>5.27685976993095</v>
+        <v>5.273117970311087</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B143" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C143" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D143" t="n">
-        <v>93.63334590745175</v>
+        <v>93.37124847310385</v>
       </c>
       <c r="E143" t="n">
-        <v>471.635</v>
+        <v>477.885</v>
       </c>
       <c r="F143" t="n">
-        <v>156.1622699196134</v>
+        <v>154.119907872264</v>
       </c>
       <c r="G143" t="n">
-        <v>5812.801875073716</v>
+        <v>6771.909738162929</v>
       </c>
       <c r="H143" t="n">
-        <v>-1526.631806797996</v>
+        <v>-1669.285347663635</v>
       </c>
       <c r="I143" t="n">
-        <v>5.895</v>
+        <v>5.78</v>
       </c>
       <c r="J143" t="n">
-        <v>15.385</v>
+        <v>16.6</v>
       </c>
       <c r="K143" t="n">
-        <v>2.505</v>
+        <v>2.57</v>
       </c>
       <c r="L143" t="n">
-        <v>3.655</v>
+        <v>3.635</v>
       </c>
       <c r="M143" t="n">
-        <v>274.9196996246158</v>
+        <v>287.5103530514276</v>
       </c>
       <c r="N143" t="n">
-        <v>5.276826591510677</v>
+        <v>5.273789602585431</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B144" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C144" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D144" t="n">
-        <v>93.59397703509872</v>
+        <v>93.30922444465473</v>
       </c>
       <c r="E144" t="n">
-        <v>476.305</v>
+        <v>482.335</v>
       </c>
       <c r="F144" t="n">
-        <v>154.6311547717048</v>
+        <v>152.6980048587328</v>
       </c>
       <c r="G144" t="n">
-        <v>5910.743701685864</v>
+        <v>6909.773348486074</v>
       </c>
       <c r="H144" t="n">
-        <v>-1500.678319208266</v>
+        <v>-1611.972212672484</v>
       </c>
       <c r="I144" t="n">
-        <v>6.08</v>
+        <v>6.005</v>
       </c>
       <c r="J144" t="n">
-        <v>15.865</v>
+        <v>17.025</v>
       </c>
       <c r="K144" t="n">
-        <v>2.595000000000001</v>
+        <v>2.665</v>
       </c>
       <c r="L144" t="n">
-        <v>3.845000000000001</v>
+        <v>3.835</v>
       </c>
       <c r="M144" t="n">
-        <v>238.0733419319008</v>
+        <v>287.510554443335</v>
       </c>
       <c r="N144" t="n">
-        <v>5.276826591510677</v>
+        <v>5.27327867551934</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B145" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C145" t="n">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D145" t="n">
-        <v>94.06137263481666</v>
+        <v>93.27663173036494</v>
       </c>
       <c r="E145" t="n">
-        <v>488.545</v>
+        <v>486.08</v>
       </c>
       <c r="F145" t="n">
-        <v>150.7570278552372</v>
+        <v>151.5215441358148</v>
       </c>
       <c r="G145" t="n">
-        <v>3771.798401581734</v>
+        <v>6993.642238947837</v>
       </c>
       <c r="H145" t="n">
-        <v>-815.7019460284989</v>
+        <v>-1593.427607877492</v>
       </c>
       <c r="I145" t="n">
-        <v>5.435</v>
+        <v>6.275</v>
       </c>
       <c r="J145" t="n">
-        <v>18.015</v>
+        <v>17.5</v>
       </c>
       <c r="K145" t="n">
-        <v>2.915</v>
+        <v>2.76</v>
       </c>
       <c r="L145" t="n">
-        <v>4.095</v>
+        <v>4.02</v>
       </c>
       <c r="M145" t="n">
-        <v>274.630197781941</v>
+        <v>241.0754108106297</v>
       </c>
       <c r="N145" t="n">
-        <v>5.266216236948693</v>
+        <v>5.27327867551934</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B146" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C146" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D146" t="n">
-        <v>94.03916891240675</v>
+        <v>93.7375789427103</v>
       </c>
       <c r="E146" t="n">
-        <v>491.925</v>
+        <v>474.85</v>
       </c>
       <c r="F146" t="n">
-        <v>149.7211814271218</v>
+        <v>155.1049640381949</v>
       </c>
       <c r="G146" t="n">
-        <v>3824.76185420302</v>
+        <v>5329.081592347652</v>
       </c>
       <c r="H146" t="n">
-        <v>-798.6284022285819</v>
+        <v>-1365.873460059604</v>
       </c>
       <c r="I146" t="n">
-        <v>5.465</v>
+        <v>5.755</v>
       </c>
       <c r="J146" t="n">
-        <v>18.35</v>
+        <v>16.005</v>
       </c>
       <c r="K146" t="n">
-        <v>3.01</v>
+        <v>2.55</v>
       </c>
       <c r="L146" t="n">
-        <v>4.255</v>
+        <v>3.615</v>
       </c>
       <c r="M146" t="n">
-        <v>237.648190391659</v>
+        <v>300.0451389434209</v>
       </c>
       <c r="N146" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276837814785707</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B147" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C147" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D147" t="n">
-        <v>93.99919860159301</v>
+        <v>93.70705125367142</v>
       </c>
       <c r="E147" t="n">
-        <v>499.49</v>
+        <v>477.415</v>
       </c>
       <c r="F147" t="n">
-        <v>147.4535870058197</v>
+        <v>154.2716340574487</v>
       </c>
       <c r="G147" t="n">
-        <v>3927.851428236562</v>
+        <v>5395.828628533539</v>
       </c>
       <c r="H147" t="n">
-        <v>-775.692473444671</v>
+        <v>-1336.413461609626</v>
       </c>
       <c r="I147" t="n">
-        <v>5.625</v>
+        <v>5.915</v>
       </c>
       <c r="J147" t="n">
-        <v>18.82</v>
+        <v>16.465</v>
       </c>
       <c r="K147" t="n">
-        <v>3.105</v>
+        <v>2.649999999999999</v>
       </c>
       <c r="L147" t="n">
-        <v>4.44</v>
+        <v>3.835</v>
       </c>
       <c r="M147" t="n">
-        <v>237.6507318640143</v>
+        <v>274.8280685050329</v>
       </c>
       <c r="N147" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276795302796649</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B148" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C148" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D148" t="n">
-        <v>94.04086327642995</v>
+        <v>93.66736972948365</v>
       </c>
       <c r="E148" t="n">
-        <v>484.745</v>
+        <v>481.67</v>
       </c>
       <c r="F148" t="n">
-        <v>151.9388383037202</v>
+        <v>152.9088217525212</v>
       </c>
       <c r="G148" t="n">
-        <v>3905.628293202783</v>
+        <v>5487.845062078589</v>
       </c>
       <c r="H148" t="n">
-        <v>-886.0263704950112</v>
+        <v>-1303.427722412256</v>
       </c>
       <c r="I148" t="n">
-        <v>5.36</v>
+        <v>6.105</v>
       </c>
       <c r="J148" t="n">
-        <v>17.13</v>
+        <v>16.965</v>
       </c>
       <c r="K148" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="L148" t="n">
-        <v>3.945</v>
+        <v>4.029999999999999</v>
       </c>
       <c r="M148" t="n">
-        <v>274.6602063166179</v>
+        <v>237.9234559192009</v>
       </c>
       <c r="N148" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276795302796649</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B149" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C149" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D149" t="n">
-        <v>94.00996552492347</v>
+        <v>93.70509773020183</v>
       </c>
       <c r="E149" t="n">
-        <v>488.54</v>
+        <v>472.055</v>
       </c>
       <c r="F149" t="n">
-        <v>150.7585707895707</v>
+        <v>156.0233281578139</v>
       </c>
       <c r="G149" t="n">
-        <v>3973.459816008984</v>
+        <v>5529.88772868665</v>
       </c>
       <c r="H149" t="n">
-        <v>-856.3651792493083</v>
+        <v>-1466.999094859334</v>
       </c>
       <c r="I149" t="n">
-        <v>5.405</v>
+        <v>5.75</v>
       </c>
       <c r="J149" t="n">
-        <v>17.48</v>
+        <v>15.4</v>
       </c>
       <c r="K149" t="n">
-        <v>2.89</v>
+        <v>2.455</v>
       </c>
       <c r="L149" t="n">
-        <v>4.105</v>
+        <v>3.52</v>
       </c>
       <c r="M149" t="n">
-        <v>274.6610046422483</v>
+        <v>300.057823899897</v>
       </c>
       <c r="N149" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276849632707642</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B150" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C150" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D150" t="n">
-        <v>93.97787731468296</v>
+        <v>93.67181804630056</v>
       </c>
       <c r="E150" t="n">
-        <v>493.715</v>
+        <v>474.585</v>
       </c>
       <c r="F150" t="n">
-        <v>149.1783562855835</v>
+        <v>155.1915719492544</v>
       </c>
       <c r="G150" t="n">
-        <v>4055.480768439214</v>
+        <v>5602.478434254266</v>
       </c>
       <c r="H150" t="n">
-        <v>-837.237951471551</v>
+        <v>-1434.724518811227</v>
       </c>
       <c r="I150" t="n">
-        <v>5.56</v>
+        <v>5.895</v>
       </c>
       <c r="J150" t="n">
-        <v>17.95</v>
+        <v>15.85</v>
       </c>
       <c r="K150" t="n">
-        <v>2.98</v>
+        <v>2.55</v>
       </c>
       <c r="L150" t="n">
-        <v>4.289999999999999</v>
+        <v>3.715</v>
       </c>
       <c r="M150" t="n">
-        <v>237.7059010028416</v>
+        <v>274.866698194862</v>
       </c>
       <c r="N150" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276816974753548</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B151" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C151" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D151" t="n">
-        <v>94.01779240111325</v>
+        <v>93.64238349983798</v>
       </c>
       <c r="E151" t="n">
-        <v>480.955</v>
+        <v>477.355</v>
       </c>
       <c r="F151" t="n">
-        <v>153.136139916493</v>
+        <v>154.2910248631246</v>
       </c>
       <c r="G151" t="n">
-        <v>4040.706191284653</v>
+        <v>5669.039064292543</v>
       </c>
       <c r="H151" t="n">
-        <v>-949.5494989248116</v>
+        <v>-1408.571100816436</v>
       </c>
       <c r="I151" t="n">
-        <v>5.29</v>
+        <v>6.08</v>
       </c>
       <c r="J151" t="n">
-        <v>16.35</v>
+        <v>16.34</v>
       </c>
       <c r="K151" t="n">
-        <v>2.685</v>
+        <v>2.65</v>
       </c>
       <c r="L151" t="n">
-        <v>3.81</v>
+        <v>3.91</v>
       </c>
       <c r="M151" t="n">
-        <v>274.6900564190772</v>
+        <v>237.9996639240671</v>
       </c>
       <c r="N151" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276816974753548</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B152" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C152" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D152" t="n">
-        <v>93.98926218137629</v>
+        <v>93.66794361387699</v>
       </c>
       <c r="E152" t="n">
-        <v>484.55</v>
+        <v>469.655</v>
       </c>
       <c r="F152" t="n">
-        <v>151.9999838479762</v>
+        <v>156.8206282772181</v>
       </c>
       <c r="G152" t="n">
-        <v>4106.38312675214</v>
+        <v>5741.700304435783</v>
       </c>
       <c r="H152" t="n">
-        <v>-925.2453286608534</v>
+        <v>-1564.573877329694</v>
       </c>
       <c r="I152" t="n">
-        <v>5.350000000000001</v>
+        <v>5.755</v>
       </c>
       <c r="J152" t="n">
-        <v>16.715</v>
+        <v>14.94</v>
       </c>
       <c r="K152" t="n">
-        <v>2.774999999999999</v>
+        <v>2.409999999999999</v>
       </c>
       <c r="L152" t="n">
-        <v>3.97</v>
+        <v>3.47</v>
       </c>
       <c r="M152" t="n">
-        <v>274.6937313449783</v>
+        <v>300.0685310526121</v>
       </c>
       <c r="N152" t="n">
-        <v>5.266216236948693</v>
+        <v>5.27685976993095</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B153" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C153" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D153" t="n">
-        <v>93.95005843954007</v>
+        <v>93.63334590745175</v>
       </c>
       <c r="E153" t="n">
-        <v>490.355</v>
+        <v>471.635</v>
       </c>
       <c r="F153" t="n">
-        <v>150.2005530147278</v>
+        <v>156.1622699196134</v>
       </c>
       <c r="G153" t="n">
-        <v>4202.475191423594</v>
+        <v>5812.801875073716</v>
       </c>
       <c r="H153" t="n">
-        <v>-897.7375467634768</v>
+        <v>-1526.631806797996</v>
       </c>
       <c r="I153" t="n">
-        <v>5.51</v>
+        <v>5.895</v>
       </c>
       <c r="J153" t="n">
-        <v>17.185</v>
+        <v>15.385</v>
       </c>
       <c r="K153" t="n">
-        <v>2.875</v>
+        <v>2.505</v>
       </c>
       <c r="L153" t="n">
-        <v>4.164999999999999</v>
+        <v>3.655</v>
       </c>
       <c r="M153" t="n">
-        <v>237.7804262443778</v>
+        <v>274.9196996246158</v>
       </c>
       <c r="N153" t="n">
-        <v>5.266216236948693</v>
+        <v>5.276826591510677</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B154" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C154" t="n">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="D154" t="n">
-        <v>93.39160536374426</v>
+        <v>93.59397703509872</v>
       </c>
       <c r="E154" t="n">
-        <v>566.975</v>
+        <v>476.305</v>
       </c>
       <c r="F154" t="n">
-        <v>129.9027155933451</v>
+        <v>154.6311547717048</v>
       </c>
       <c r="G154" t="n">
-        <v>5881.019688831716</v>
+        <v>5910.743701685864</v>
       </c>
       <c r="H154" t="n">
-        <v>-824.2581740182918</v>
+        <v>-1500.678319208266</v>
       </c>
       <c r="I154" t="n">
-        <v>5.25</v>
+        <v>6.08</v>
       </c>
       <c r="J154" t="n">
-        <v>15.98</v>
+        <v>15.865</v>
       </c>
       <c r="K154" t="n">
-        <v>2.64</v>
+        <v>2.595000000000001</v>
       </c>
       <c r="L154" t="n">
-        <v>3.7</v>
+        <v>3.845000000000001</v>
       </c>
       <c r="M154" t="n">
-        <v>297.6108788591611</v>
+        <v>238.0733419319008</v>
       </c>
       <c r="N154" t="n">
-        <v>5.307415007540252</v>
+        <v>5.276826591510677</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B155" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C155" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D155" t="n">
-        <v>93.00520274446839</v>
+        <v>94.06137263481666</v>
       </c>
       <c r="E155" t="n">
-        <v>600</v>
+        <v>488.545</v>
       </c>
       <c r="F155" t="n">
-        <v>122.7526536225614</v>
+        <v>150.7570278552372</v>
       </c>
       <c r="G155" t="n">
-        <v>6705.467309209334</v>
+        <v>3771.798401581734</v>
       </c>
       <c r="H155" t="n">
-        <v>-430.9480564697961</v>
+        <v>-815.7019460284989</v>
       </c>
       <c r="I155" t="n">
-        <v>5.445</v>
+        <v>5.435</v>
       </c>
       <c r="J155" t="n">
-        <v>16.495</v>
+        <v>18.015</v>
       </c>
       <c r="K155" t="n">
-        <v>2.82</v>
+        <v>2.915</v>
       </c>
       <c r="L155" t="n">
-        <v>3.96</v>
+        <v>4.095</v>
       </c>
       <c r="M155" t="n">
-        <v>224.2093764810274</v>
+        <v>274.630197781941</v>
       </c>
       <c r="N155" t="n">
-        <v>5.302146700941705</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B156" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C156" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D156" t="n">
-        <v>93.20323324197504</v>
+        <v>94.03916891240675</v>
       </c>
       <c r="E156" t="n">
-        <v>600</v>
+        <v>491.925</v>
       </c>
       <c r="F156" t="n">
-        <v>122.7526536225614</v>
+        <v>149.7211814271218</v>
       </c>
       <c r="G156" t="n">
-        <v>6184.948622227217</v>
+        <v>3824.76185420302</v>
       </c>
       <c r="H156" t="n">
-        <v>-532.8396788580467</v>
+        <v>-798.6284022285819</v>
       </c>
       <c r="I156" t="n">
-        <v>5.705</v>
+        <v>5.465</v>
       </c>
       <c r="J156" t="n">
-        <v>17.07</v>
+        <v>18.35</v>
       </c>
       <c r="K156" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="L156" t="n">
-        <v>4.234999999999999</v>
+        <v>4.255</v>
       </c>
       <c r="M156" t="n">
-        <v>224.1785042995384</v>
+        <v>237.648190391659</v>
       </c>
       <c r="N156" t="n">
-        <v>5.299827897755545</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B157" t="n">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C157" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D157" t="n">
-        <v>93.37405640168669</v>
+        <v>93.99919860159301</v>
       </c>
       <c r="E157" t="n">
-        <v>553</v>
+        <v>499.49</v>
       </c>
       <c r="F157" t="n">
-        <v>133.1855193011517</v>
+        <v>147.4535870058197</v>
       </c>
       <c r="G157" t="n">
-        <v>6043.812569803414</v>
+        <v>3927.851428236562</v>
       </c>
       <c r="H157" t="n">
-        <v>-934.7605154360626</v>
+        <v>-775.692473444671</v>
       </c>
       <c r="I157" t="n">
-        <v>5.215</v>
+        <v>5.625</v>
       </c>
       <c r="J157" t="n">
-        <v>15.32</v>
+        <v>18.82</v>
       </c>
       <c r="K157" t="n">
-        <v>2.545</v>
+        <v>3.105</v>
       </c>
       <c r="L157" t="n">
-        <v>3.605</v>
+        <v>4.44</v>
       </c>
       <c r="M157" t="n">
-        <v>300.0100695797773</v>
+        <v>237.6507318640143</v>
       </c>
       <c r="N157" t="n">
-        <v>5.307415007540252</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B158" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C158" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D158" t="n">
-        <v>92.9160562125255</v>
+        <v>94.04086327642995</v>
       </c>
       <c r="E158" t="n">
-        <v>600</v>
+        <v>484.745</v>
       </c>
       <c r="F158" t="n">
-        <v>122.7526536225614</v>
+        <v>151.9388383037202</v>
       </c>
       <c r="G158" t="n">
-        <v>6996.972720723452</v>
+        <v>3905.628293202783</v>
       </c>
       <c r="H158" t="n">
-        <v>-444.1735990791756</v>
+        <v>-886.0263704950112</v>
       </c>
       <c r="I158" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="J158" t="n">
-        <v>15.82</v>
+        <v>17.13</v>
       </c>
       <c r="K158" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="L158" t="n">
-        <v>3.86</v>
+        <v>3.945</v>
       </c>
       <c r="M158" t="n">
-        <v>224.2907156932552</v>
+        <v>274.6602063166179</v>
       </c>
       <c r="N158" t="n">
-        <v>5.301625897179865</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B159" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C159" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D159" t="n">
-        <v>93.1227778417684</v>
+        <v>94.00996552492347</v>
       </c>
       <c r="E159" t="n">
-        <v>600</v>
+        <v>488.54</v>
       </c>
       <c r="F159" t="n">
-        <v>122.7526536225614</v>
+        <v>150.7585707895707</v>
       </c>
       <c r="G159" t="n">
-        <v>6472.578424628873</v>
+        <v>3973.459816008984</v>
       </c>
       <c r="H159" t="n">
-        <v>-569.462016244643</v>
+        <v>-856.3651792493083</v>
       </c>
       <c r="I159" t="n">
-        <v>5.655</v>
+        <v>5.405</v>
       </c>
       <c r="J159" t="n">
-        <v>16.39</v>
+        <v>17.48</v>
       </c>
       <c r="K159" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="L159" t="n">
-        <v>4.125</v>
+        <v>4.105</v>
       </c>
       <c r="M159" t="n">
-        <v>224.2387539633841</v>
+        <v>274.6610046422483</v>
       </c>
       <c r="N159" t="n">
-        <v>5.299141949620611</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B160" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C160" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D160" t="n">
-        <v>93.31618410638438</v>
+        <v>93.97787731468296</v>
       </c>
       <c r="E160" t="n">
-        <v>546.885</v>
+        <v>493.715</v>
       </c>
       <c r="F160" t="n">
-        <v>134.6747344936081</v>
+        <v>149.1783562855835</v>
       </c>
       <c r="G160" t="n">
-        <v>6255.292482077637</v>
+        <v>4055.480768439214</v>
       </c>
       <c r="H160" t="n">
-        <v>-965.6574981168902</v>
+        <v>-837.237951471551</v>
       </c>
       <c r="I160" t="n">
-        <v>5.19</v>
+        <v>5.56</v>
       </c>
       <c r="J160" t="n">
-        <v>14.74</v>
+        <v>17.95</v>
       </c>
       <c r="K160" t="n">
-        <v>2.47</v>
+        <v>2.98</v>
       </c>
       <c r="L160" t="n">
-        <v>3.53</v>
+        <v>4.289999999999999</v>
       </c>
       <c r="M160" t="n">
-        <v>300.0262041365498</v>
+        <v>237.7059010028416</v>
       </c>
       <c r="N160" t="n">
-        <v>5.307415007540252</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B161" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C161" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D161" t="n">
-        <v>92.82946804348842</v>
+        <v>94.01779240111325</v>
       </c>
       <c r="E161" t="n">
-        <v>600</v>
+        <v>480.955</v>
       </c>
       <c r="F161" t="n">
-        <v>122.7526536225614</v>
+        <v>153.136139916493</v>
       </c>
       <c r="G161" t="n">
-        <v>7290.003077374275</v>
+        <v>4040.706191284653</v>
       </c>
       <c r="H161" t="n">
-        <v>-467.1081029056169</v>
+        <v>-949.5494989248116</v>
       </c>
       <c r="I161" t="n">
-        <v>5.37</v>
+        <v>5.29</v>
       </c>
       <c r="J161" t="n">
-        <v>15.24</v>
+        <v>16.35</v>
       </c>
       <c r="K161" t="n">
-        <v>2.655</v>
+        <v>2.685</v>
       </c>
       <c r="L161" t="n">
-        <v>3.775</v>
+        <v>3.81</v>
       </c>
       <c r="M161" t="n">
-        <v>224.3690081541812</v>
+        <v>274.6900564190772</v>
       </c>
       <c r="N161" t="n">
-        <v>5.300553327759205</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B162" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C162" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D162" t="n">
-        <v>93.04712082832047</v>
+        <v>93.98926218137629</v>
       </c>
       <c r="E162" t="n">
-        <v>600</v>
+        <v>484.55</v>
       </c>
       <c r="F162" t="n">
-        <v>122.7526536225614</v>
+        <v>151.9999838479762</v>
       </c>
       <c r="G162" t="n">
-        <v>6776.654490686403</v>
+        <v>4106.38312675214</v>
       </c>
       <c r="H162" t="n">
-        <v>-638.1252760577953</v>
+        <v>-925.2453286608534</v>
       </c>
       <c r="I162" t="n">
-        <v>5.63</v>
+        <v>5.350000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>15.81</v>
+        <v>16.715</v>
       </c>
       <c r="K162" t="n">
-        <v>2.835</v>
+        <v>2.774999999999999</v>
       </c>
       <c r="L162" t="n">
-        <v>4.045</v>
+        <v>3.97</v>
       </c>
       <c r="M162" t="n">
-        <v>224.3388964030367</v>
+        <v>274.6937313449783</v>
       </c>
       <c r="N162" t="n">
-        <v>5.297623858839702</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="B163" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C163" t="n">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="D163" t="n">
-        <v>93.60780736497125</v>
+        <v>93.95005843954007</v>
       </c>
       <c r="E163" t="n">
-        <v>478.64</v>
+        <v>490.355</v>
       </c>
       <c r="F163" t="n">
-        <v>153.8768012985477</v>
+        <v>150.2005530147278</v>
       </c>
       <c r="G163" t="n">
-        <v>5782.171879982329</v>
+        <v>4202.475191423594</v>
       </c>
       <c r="H163" t="n">
-        <v>-1413.492709881508</v>
+        <v>-897.7375467634768</v>
       </c>
       <c r="I163" t="n">
-        <v>5.815</v>
+        <v>5.51</v>
       </c>
       <c r="J163" t="n">
-        <v>16.535</v>
+        <v>17.185</v>
       </c>
       <c r="K163" t="n">
-        <v>2.58</v>
+        <v>2.875</v>
       </c>
       <c r="L163" t="n">
-        <v>3.65</v>
+        <v>4.164999999999999</v>
       </c>
       <c r="M163" t="n">
-        <v>287.5255286332636</v>
+        <v>237.7804262443778</v>
       </c>
       <c r="N163" t="n">
-        <v>5.272856452064412</v>
+        <v>5.266216236948693</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B164" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C164" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D164" t="n">
-        <v>93.55536518664927</v>
+        <v>93.39160536374426</v>
       </c>
       <c r="E164" t="n">
-        <v>483.25</v>
+        <v>566.975</v>
       </c>
       <c r="F164" t="n">
-        <v>152.4088818904022</v>
+        <v>129.9027155933451</v>
       </c>
       <c r="G164" t="n">
-        <v>5900.50579425959</v>
+        <v>5881.019688831716</v>
       </c>
       <c r="H164" t="n">
-        <v>-1366.665182830038</v>
+        <v>-824.2581740182918</v>
       </c>
       <c r="I164" t="n">
-        <v>6.045</v>
+        <v>5.25</v>
       </c>
       <c r="J164" t="n">
-        <v>16.97</v>
+        <v>15.98</v>
       </c>
       <c r="K164" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="L164" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="M164" t="n">
-        <v>287.5256080259855</v>
+        <v>297.6108788591611</v>
       </c>
       <c r="N164" t="n">
-        <v>5.272279725385319</v>
+        <v>5.307415007540252</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B165" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C165" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D165" t="n">
-        <v>93.49466695286711</v>
+        <v>93.00520274446839</v>
       </c>
       <c r="E165" t="n">
-        <v>490.4</v>
+        <v>600</v>
       </c>
       <c r="F165" t="n">
-        <v>150.1867703375548</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G165" t="n">
-        <v>6050.57464560456</v>
+        <v>6705.467309209334</v>
       </c>
       <c r="H165" t="n">
-        <v>-1325.721340913737</v>
+        <v>-430.9480564697961</v>
       </c>
       <c r="I165" t="n">
-        <v>6.315</v>
+        <v>5.445</v>
       </c>
       <c r="J165" t="n">
-        <v>17.44</v>
+        <v>16.495</v>
       </c>
       <c r="K165" t="n">
-        <v>2.775</v>
+        <v>2.82</v>
       </c>
       <c r="L165" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="M165" t="n">
-        <v>241.1186174329819</v>
+        <v>224.2093764810274</v>
       </c>
       <c r="N165" t="n">
-        <v>5.272279725385319</v>
+        <v>5.302146700941705</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B166" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C166" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D166" t="n">
-        <v>93.56591019123778</v>
+        <v>93.20323324197504</v>
       </c>
       <c r="E166" t="n">
-        <v>475.78</v>
+        <v>600</v>
       </c>
       <c r="F166" t="n">
-        <v>154.8017827011158</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G166" t="n">
-        <v>6013.65684137698</v>
+        <v>6184.948622227217</v>
       </c>
       <c r="H166" t="n">
-        <v>-1516.084332000202</v>
+        <v>-532.8396788580467</v>
       </c>
       <c r="I166" t="n">
-        <v>5.795</v>
+        <v>5.705</v>
       </c>
       <c r="J166" t="n">
-        <v>15.87</v>
+        <v>17.07</v>
       </c>
       <c r="K166" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="L166" t="n">
-        <v>3.545</v>
+        <v>4.234999999999999</v>
       </c>
       <c r="M166" t="n">
-        <v>287.5548554343529</v>
+        <v>224.1785042995384</v>
       </c>
       <c r="N166" t="n">
-        <v>5.272874316835532</v>
+        <v>5.299827897755545</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B167" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C167" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D167" t="n">
-        <v>93.52302999996925</v>
+        <v>93.37405640168669</v>
       </c>
       <c r="E167" t="n">
-        <v>479.245</v>
+        <v>553</v>
       </c>
       <c r="F167" t="n">
-        <v>153.6825468675455</v>
+        <v>133.1855193011517</v>
       </c>
       <c r="G167" t="n">
-        <v>6108.646282534939</v>
+        <v>6043.812569803414</v>
       </c>
       <c r="H167" t="n">
-        <v>-1476.036436451451</v>
+        <v>-934.7605154360626</v>
       </c>
       <c r="I167" t="n">
-        <v>6.01</v>
+        <v>5.215</v>
       </c>
       <c r="J167" t="n">
-        <v>16.285</v>
+        <v>15.32</v>
       </c>
       <c r="K167" t="n">
-        <v>2.575</v>
+        <v>2.545</v>
       </c>
       <c r="L167" t="n">
-        <v>3.73</v>
+        <v>3.605</v>
       </c>
       <c r="M167" t="n">
-        <v>287.5530010097403</v>
+        <v>300.0100695797773</v>
       </c>
       <c r="N167" t="n">
-        <v>5.272301741770099</v>
+        <v>5.307415007540252</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B168" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C168" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D168" t="n">
-        <v>93.47838239701272</v>
+        <v>92.9160562125255</v>
       </c>
       <c r="E168" t="n">
-        <v>483.715</v>
+        <v>600</v>
       </c>
       <c r="F168" t="n">
-        <v>152.2623697291522</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G168" t="n">
-        <v>6214.272162782726</v>
+        <v>6996.972720723452</v>
       </c>
       <c r="H168" t="n">
-        <v>-1441.141490868092</v>
+        <v>-444.1735990791756</v>
       </c>
       <c r="I168" t="n">
-        <v>6.27</v>
+        <v>5.4</v>
       </c>
       <c r="J168" t="n">
-        <v>16.745</v>
+        <v>15.82</v>
       </c>
       <c r="K168" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="L168" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="M168" t="n">
-        <v>241.1753300195797</v>
+        <v>224.2907156932552</v>
       </c>
       <c r="N168" t="n">
-        <v>5.272301741770099</v>
+        <v>5.301625897179865</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B169" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C169" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D169" t="n">
-        <v>93.53083417295163</v>
+        <v>93.1227778417684</v>
       </c>
       <c r="E169" t="n">
-        <v>472.795</v>
+        <v>600</v>
       </c>
       <c r="F169" t="n">
-        <v>155.7791266268401</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G169" t="n">
-        <v>6230.480796751935</v>
+        <v>6472.578424628873</v>
       </c>
       <c r="H169" t="n">
-        <v>-1625.672614200203</v>
+        <v>-569.462016244643</v>
       </c>
       <c r="I169" t="n">
-        <v>5.79</v>
+        <v>5.655</v>
       </c>
       <c r="J169" t="n">
-        <v>15.31</v>
+        <v>16.39</v>
       </c>
       <c r="K169" t="n">
-        <v>2.415</v>
+        <v>2.91</v>
       </c>
       <c r="L169" t="n">
-        <v>3.48</v>
+        <v>4.125</v>
       </c>
       <c r="M169" t="n">
-        <v>287.5847306530924</v>
+        <v>224.2387539633841</v>
       </c>
       <c r="N169" t="n">
-        <v>5.272891224655314</v>
+        <v>5.299141949620611</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B170" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C170" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D170" t="n">
-        <v>93.48377917695814</v>
+        <v>93.31618410638438</v>
       </c>
       <c r="E170" t="n">
-        <v>476.165</v>
+        <v>546.885</v>
       </c>
       <c r="F170" t="n">
-        <v>154.6766187635313</v>
+        <v>134.6747344936081</v>
       </c>
       <c r="G170" t="n">
-        <v>6332.532133712925</v>
+        <v>6255.292482077637</v>
       </c>
       <c r="H170" t="n">
-        <v>-1579.555608603629</v>
+        <v>-965.6574981168902</v>
       </c>
       <c r="I170" t="n">
-        <v>5.99</v>
+        <v>5.19</v>
       </c>
       <c r="J170" t="n">
-        <v>15.71</v>
+        <v>14.74</v>
       </c>
       <c r="K170" t="n">
-        <v>2.510000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="L170" t="n">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="M170" t="n">
-        <v>287.5869654449736</v>
+        <v>300.0262041365498</v>
       </c>
       <c r="N170" t="n">
-        <v>5.272277243669286</v>
+        <v>5.307415007540252</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B171" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C171" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D171" t="n">
-        <v>93.4130935470521</v>
+        <v>92.82946804348842</v>
       </c>
       <c r="E171" t="n">
-        <v>482.785</v>
+        <v>600</v>
       </c>
       <c r="F171" t="n">
-        <v>152.5556762814438</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G171" t="n">
-        <v>6499.879389135563</v>
+        <v>7290.003077374275</v>
       </c>
       <c r="H171" t="n">
-        <v>-1524.493679029795</v>
+        <v>-467.1081029056169</v>
       </c>
       <c r="I171" t="n">
-        <v>6.25</v>
+        <v>5.37</v>
       </c>
       <c r="J171" t="n">
-        <v>16.175</v>
+        <v>15.24</v>
       </c>
       <c r="K171" t="n">
-        <v>2.605</v>
+        <v>2.655</v>
       </c>
       <c r="L171" t="n">
-        <v>3.83</v>
+        <v>3.775</v>
       </c>
       <c r="M171" t="n">
-        <v>241.2524692211172</v>
+        <v>224.3690081541812</v>
       </c>
       <c r="N171" t="n">
-        <v>5.272277243669286</v>
+        <v>5.300553327759205</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>413</v>
+        <v>348</v>
       </c>
       <c r="B172" t="n">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C172" t="n">
-        <v>413</v>
+        <v>348</v>
       </c>
       <c r="D172" t="n">
-        <v>81.17447304756479</v>
+        <v>93.04712082832047</v>
       </c>
       <c r="E172" t="n">
-        <v>472.935</v>
+        <v>600</v>
       </c>
       <c r="F172" t="n">
-        <v>155.7330123030372</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G172" t="n">
-        <v>52513.7615386265</v>
+        <v>6776.654490686403</v>
       </c>
       <c r="H172" t="n">
-        <v>-8235.246021061805</v>
+        <v>-638.1252760577953</v>
       </c>
       <c r="I172" t="n">
-        <v>5.715</v>
+        <v>5.63</v>
       </c>
       <c r="J172" t="n">
-        <v>16.2</v>
+        <v>15.81</v>
       </c>
       <c r="K172" t="n">
-        <v>2.699999999999999</v>
+        <v>2.835</v>
       </c>
       <c r="L172" t="n">
-        <v>3.78</v>
+        <v>4.045</v>
       </c>
       <c r="M172" t="n">
-        <v>299.523947455675</v>
+        <v>224.3388964030367</v>
       </c>
       <c r="N172" t="n">
-        <v>5.319434242601793</v>
+        <v>5.297623858839702</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B173" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C173" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D173" t="n">
-        <v>81.07936296066114</v>
+        <v>93.60780736497125</v>
       </c>
       <c r="E173" t="n">
-        <v>474.66</v>
+        <v>478.64</v>
       </c>
       <c r="F173" t="n">
-        <v>155.1670504646207</v>
+        <v>153.8768012985477</v>
       </c>
       <c r="G173" t="n">
-        <v>52717.38553865819</v>
+        <v>5782.171879982329</v>
       </c>
       <c r="H173" t="n">
-        <v>-8189.63592603311</v>
+        <v>-1413.492709881508</v>
       </c>
       <c r="I173" t="n">
-        <v>5.850000000000001</v>
+        <v>5.815</v>
       </c>
       <c r="J173" t="n">
-        <v>16.53</v>
+        <v>16.535</v>
       </c>
       <c r="K173" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="L173" t="n">
-        <v>3.96</v>
+        <v>3.65</v>
       </c>
       <c r="M173" t="n">
-        <v>299.522924401521</v>
+        <v>287.5255286332636</v>
       </c>
       <c r="N173" t="n">
-        <v>5.324752570945306</v>
+        <v>5.272856452064412</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B174" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C174" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D174" t="n">
-        <v>80.81584820022067</v>
+        <v>93.55536518664927</v>
       </c>
       <c r="E174" t="n">
-        <v>478.805</v>
+        <v>483.25</v>
       </c>
       <c r="F174" t="n">
-        <v>153.8237741325527</v>
+        <v>152.4088818904022</v>
       </c>
       <c r="G174" t="n">
-        <v>53272.7003570364</v>
+        <v>5900.50579425959</v>
       </c>
       <c r="H174" t="n">
-        <v>-8083.121202495097</v>
+        <v>-1366.665182830038</v>
       </c>
       <c r="I174" t="n">
-        <v>5.985</v>
+        <v>6.045</v>
       </c>
       <c r="J174" t="n">
-        <v>16.875</v>
+        <v>16.97</v>
       </c>
       <c r="K174" t="n">
-        <v>2.825</v>
+        <v>2.68</v>
       </c>
       <c r="L174" t="n">
-        <v>4.09</v>
+        <v>3.85</v>
       </c>
       <c r="M174" t="n">
-        <v>299.5218833934957</v>
+        <v>287.5256080259855</v>
       </c>
       <c r="N174" t="n">
-        <v>5.336686842591843</v>
+        <v>5.272279725385319</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B175" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C175" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D175" t="n">
-        <v>80.72172269299428</v>
+        <v>93.49466695286711</v>
       </c>
       <c r="E175" t="n">
-        <v>469.35</v>
+        <v>490.4</v>
       </c>
       <c r="F175" t="n">
-        <v>156.9225357910661</v>
+        <v>150.1867703375548</v>
       </c>
       <c r="G175" t="n">
-        <v>54466.95159486185</v>
+        <v>6050.57464560456</v>
       </c>
       <c r="H175" t="n">
-        <v>-8508.821596508054</v>
+        <v>-1325.721340913737</v>
       </c>
       <c r="I175" t="n">
-        <v>5.575</v>
+        <v>6.315</v>
       </c>
       <c r="J175" t="n">
-        <v>15.43</v>
+        <v>17.44</v>
       </c>
       <c r="K175" t="n">
-        <v>2.555</v>
+        <v>2.775</v>
       </c>
       <c r="L175" t="n">
-        <v>3.59</v>
+        <v>4.04</v>
       </c>
       <c r="M175" t="n">
-        <v>300.0160827483674</v>
+        <v>241.1186174329819</v>
       </c>
       <c r="N175" t="n">
-        <v>5.403059520493683</v>
+        <v>5.272279725385319</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B176" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C176" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D176" t="n">
-        <v>80.65170135905515</v>
+        <v>93.56591019123778</v>
       </c>
       <c r="E176" t="n">
-        <v>470.92</v>
+        <v>475.78</v>
       </c>
       <c r="F176" t="n">
-        <v>156.3993718116386</v>
+        <v>154.8017827011158</v>
       </c>
       <c r="G176" t="n">
-        <v>54646.47492184487</v>
+        <v>6013.65684137698</v>
       </c>
       <c r="H176" t="n">
-        <v>-8484.427867905555</v>
+        <v>-1516.084332000202</v>
       </c>
       <c r="I176" t="n">
-        <v>5.725000000000001</v>
+        <v>5.795</v>
       </c>
       <c r="J176" t="n">
-        <v>15.775</v>
+        <v>15.87</v>
       </c>
       <c r="K176" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="L176" t="n">
-        <v>3.77</v>
+        <v>3.545</v>
       </c>
       <c r="M176" t="n">
-        <v>300.016082197001</v>
+        <v>287.5548554343529</v>
       </c>
       <c r="N176" t="n">
-        <v>5.403205709217267</v>
+        <v>5.272874316835532</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B177" t="n">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C177" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D177" t="n">
-        <v>80.38307485323961</v>
+        <v>93.52302999996925</v>
       </c>
       <c r="E177" t="n">
-        <v>475.005</v>
+        <v>479.245</v>
       </c>
       <c r="F177" t="n">
-        <v>155.0543513721684</v>
+        <v>153.6825468675455</v>
       </c>
       <c r="G177" t="n">
-        <v>55198.94423016463</v>
+        <v>6108.646282534939</v>
       </c>
       <c r="H177" t="n">
-        <v>-8367.536026770043</v>
+        <v>-1476.036436451451</v>
       </c>
       <c r="I177" t="n">
-        <v>5.86</v>
+        <v>6.01</v>
       </c>
       <c r="J177" t="n">
-        <v>16.115</v>
+        <v>16.285</v>
       </c>
       <c r="K177" t="n">
-        <v>2.680000000000001</v>
+        <v>2.575</v>
       </c>
       <c r="L177" t="n">
-        <v>3.905</v>
+        <v>3.73</v>
       </c>
       <c r="M177" t="n">
-        <v>300.0160823418269</v>
+        <v>287.5530010097403</v>
       </c>
       <c r="N177" t="n">
-        <v>5.417753888744446</v>
+        <v>5.272301741770099</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B178" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C178" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D178" t="n">
-        <v>80.30660156667822</v>
+        <v>93.47838239701272</v>
       </c>
       <c r="E178" t="n">
-        <v>466.08</v>
+        <v>483.715</v>
       </c>
       <c r="F178" t="n">
-        <v>158.0234984842449</v>
+        <v>152.2623697291522</v>
       </c>
       <c r="G178" t="n">
-        <v>56344.28841909636</v>
+        <v>6214.272162782726</v>
       </c>
       <c r="H178" t="n">
-        <v>-8782.699860939843</v>
+        <v>-1441.141490868092</v>
       </c>
       <c r="I178" t="n">
-        <v>5.49</v>
+        <v>6.27</v>
       </c>
       <c r="J178" t="n">
-        <v>14.795</v>
+        <v>16.745</v>
       </c>
       <c r="K178" t="n">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="L178" t="n">
-        <v>3.46</v>
+        <v>3.91</v>
       </c>
       <c r="M178" t="n">
-        <v>300.0319778485202</v>
+        <v>241.1753300195797</v>
       </c>
       <c r="N178" t="n">
-        <v>5.481264488374775</v>
+        <v>5.272301741770099</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B179" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C179" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="D179" t="n">
-        <v>80.23709110490057</v>
+        <v>93.53083417295163</v>
       </c>
       <c r="E179" t="n">
-        <v>467.19</v>
+        <v>472.795</v>
       </c>
       <c r="F179" t="n">
-        <v>157.6480493450991</v>
+        <v>155.7791266268401</v>
       </c>
       <c r="G179" t="n">
-        <v>56498.47235689612</v>
+        <v>6230.480796751935</v>
       </c>
       <c r="H179" t="n">
-        <v>-8741.236739706075</v>
+        <v>-1625.672614200203</v>
       </c>
       <c r="I179" t="n">
-        <v>5.615</v>
+        <v>5.79</v>
       </c>
       <c r="J179" t="n">
-        <v>15.11</v>
+        <v>15.31</v>
       </c>
       <c r="K179" t="n">
-        <v>2.5</v>
+        <v>2.415</v>
       </c>
       <c r="L179" t="n">
-        <v>3.61</v>
+        <v>3.48</v>
       </c>
       <c r="M179" t="n">
-        <v>300.0319778451221</v>
+        <v>287.5847306530924</v>
       </c>
       <c r="N179" t="n">
-        <v>5.481361532008621</v>
+        <v>5.272891224655314</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
+        <v>357</v>
+      </c>
+      <c r="B180" t="n">
+        <v>179</v>
+      </c>
+      <c r="C180" t="n">
+        <v>357</v>
+      </c>
+      <c r="D180" t="n">
+        <v>93.48377917695814</v>
+      </c>
+      <c r="E180" t="n">
+        <v>476.165</v>
+      </c>
+      <c r="F180" t="n">
+        <v>154.6766187635313</v>
+      </c>
+      <c r="G180" t="n">
+        <v>6332.532133712925</v>
+      </c>
+      <c r="H180" t="n">
+        <v>-1579.555608603629</v>
+      </c>
+      <c r="I180" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="J180" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="K180" t="n">
+        <v>2.510000000000001</v>
+      </c>
+      <c r="L180" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M180" t="n">
+        <v>287.5869654449736</v>
+      </c>
+      <c r="N180" t="n">
+        <v>5.272277243669286</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>357</v>
+      </c>
+      <c r="B181" t="n">
+        <v>180</v>
+      </c>
+      <c r="C181" t="n">
+        <v>357</v>
+      </c>
+      <c r="D181" t="n">
+        <v>93.4130935470521</v>
+      </c>
+      <c r="E181" t="n">
+        <v>482.785</v>
+      </c>
+      <c r="F181" t="n">
+        <v>152.5556762814438</v>
+      </c>
+      <c r="G181" t="n">
+        <v>6499.879389135563</v>
+      </c>
+      <c r="H181" t="n">
+        <v>-1524.493679029795</v>
+      </c>
+      <c r="I181" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J181" t="n">
+        <v>16.175</v>
+      </c>
+      <c r="K181" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="M181" t="n">
+        <v>241.2524692211172</v>
+      </c>
+      <c r="N181" t="n">
+        <v>5.272277243669286</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
         <v>413</v>
       </c>
-      <c r="B180" t="n">
+      <c r="B182" t="n">
+        <v>181</v>
+      </c>
+      <c r="C182" t="n">
+        <v>413</v>
+      </c>
+      <c r="D182" t="n">
+        <v>81.17447304756479</v>
+      </c>
+      <c r="E182" t="n">
+        <v>472.935</v>
+      </c>
+      <c r="F182" t="n">
+        <v>155.7330123030372</v>
+      </c>
+      <c r="G182" t="n">
+        <v>52513.7615386265</v>
+      </c>
+      <c r="H182" t="n">
+        <v>-8235.246021061805</v>
+      </c>
+      <c r="I182" t="n">
+        <v>5.715</v>
+      </c>
+      <c r="J182" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K182" t="n">
+        <v>2.699999999999999</v>
+      </c>
+      <c r="L182" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M182" t="n">
+        <v>299.523947455675</v>
+      </c>
+      <c r="N182" t="n">
+        <v>5.319434242601793</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>413</v>
+      </c>
+      <c r="B183" t="n">
+        <v>182</v>
+      </c>
+      <c r="C183" t="n">
+        <v>413</v>
+      </c>
+      <c r="D183" t="n">
+        <v>81.07936296066114</v>
+      </c>
+      <c r="E183" t="n">
+        <v>474.66</v>
+      </c>
+      <c r="F183" t="n">
+        <v>155.1670504646207</v>
+      </c>
+      <c r="G183" t="n">
+        <v>52717.38553865819</v>
+      </c>
+      <c r="H183" t="n">
+        <v>-8189.63592603311</v>
+      </c>
+      <c r="I183" t="n">
+        <v>5.850000000000001</v>
+      </c>
+      <c r="J183" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="K183" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L183" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M183" t="n">
+        <v>299.522924401521</v>
+      </c>
+      <c r="N183" t="n">
+        <v>5.324752570945306</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>413</v>
+      </c>
+      <c r="B184" t="n">
+        <v>183</v>
+      </c>
+      <c r="C184" t="n">
+        <v>413</v>
+      </c>
+      <c r="D184" t="n">
+        <v>80.81584820022067</v>
+      </c>
+      <c r="E184" t="n">
+        <v>478.805</v>
+      </c>
+      <c r="F184" t="n">
+        <v>153.8237741325527</v>
+      </c>
+      <c r="G184" t="n">
+        <v>53272.7003570364</v>
+      </c>
+      <c r="H184" t="n">
+        <v>-8083.121202495097</v>
+      </c>
+      <c r="I184" t="n">
+        <v>5.985</v>
+      </c>
+      <c r="J184" t="n">
+        <v>16.875</v>
+      </c>
+      <c r="K184" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="L184" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M184" t="n">
+        <v>299.5218833934957</v>
+      </c>
+      <c r="N184" t="n">
+        <v>5.336686842591843</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>413</v>
+      </c>
+      <c r="B185" t="n">
+        <v>184</v>
+      </c>
+      <c r="C185" t="n">
+        <v>413</v>
+      </c>
+      <c r="D185" t="n">
+        <v>80.72172269299428</v>
+      </c>
+      <c r="E185" t="n">
+        <v>469.35</v>
+      </c>
+      <c r="F185" t="n">
+        <v>156.9225357910661</v>
+      </c>
+      <c r="G185" t="n">
+        <v>54466.95159486185</v>
+      </c>
+      <c r="H185" t="n">
+        <v>-8508.821596508054</v>
+      </c>
+      <c r="I185" t="n">
+        <v>5.575</v>
+      </c>
+      <c r="J185" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="K185" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="L185" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="M185" t="n">
+        <v>300.0160827483674</v>
+      </c>
+      <c r="N185" t="n">
+        <v>5.403059520493683</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>413</v>
+      </c>
+      <c r="B186" t="n">
+        <v>185</v>
+      </c>
+      <c r="C186" t="n">
+        <v>413</v>
+      </c>
+      <c r="D186" t="n">
+        <v>80.65170135905515</v>
+      </c>
+      <c r="E186" t="n">
+        <v>470.92</v>
+      </c>
+      <c r="F186" t="n">
+        <v>156.3993718116386</v>
+      </c>
+      <c r="G186" t="n">
+        <v>54646.47492184487</v>
+      </c>
+      <c r="H186" t="n">
+        <v>-8484.427867905555</v>
+      </c>
+      <c r="I186" t="n">
+        <v>5.725000000000001</v>
+      </c>
+      <c r="J186" t="n">
+        <v>15.775</v>
+      </c>
+      <c r="K186" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L186" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M186" t="n">
+        <v>300.016082197001</v>
+      </c>
+      <c r="N186" t="n">
+        <v>5.403205709217267</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>413</v>
+      </c>
+      <c r="B187" t="n">
+        <v>186</v>
+      </c>
+      <c r="C187" t="n">
+        <v>413</v>
+      </c>
+      <c r="D187" t="n">
+        <v>80.38307485323961</v>
+      </c>
+      <c r="E187" t="n">
+        <v>475.005</v>
+      </c>
+      <c r="F187" t="n">
+        <v>155.0543513721684</v>
+      </c>
+      <c r="G187" t="n">
+        <v>55198.94423016463</v>
+      </c>
+      <c r="H187" t="n">
+        <v>-8367.536026770043</v>
+      </c>
+      <c r="I187" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="J187" t="n">
+        <v>16.115</v>
+      </c>
+      <c r="K187" t="n">
+        <v>2.680000000000001</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="M187" t="n">
+        <v>300.0160823418269</v>
+      </c>
+      <c r="N187" t="n">
+        <v>5.417753888744446</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>413</v>
+      </c>
+      <c r="B188" t="n">
+        <v>187</v>
+      </c>
+      <c r="C188" t="n">
+        <v>413</v>
+      </c>
+      <c r="D188" t="n">
+        <v>80.30660156667822</v>
+      </c>
+      <c r="E188" t="n">
+        <v>466.08</v>
+      </c>
+      <c r="F188" t="n">
+        <v>158.0234984842449</v>
+      </c>
+      <c r="G188" t="n">
+        <v>56344.28841909636</v>
+      </c>
+      <c r="H188" t="n">
+        <v>-8782.699860939843</v>
+      </c>
+      <c r="I188" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="J188" t="n">
+        <v>14.795</v>
+      </c>
+      <c r="K188" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L188" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="M188" t="n">
+        <v>300.0319778485202</v>
+      </c>
+      <c r="N188" t="n">
+        <v>5.481264488374775</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>413</v>
+      </c>
+      <c r="B189" t="n">
+        <v>188</v>
+      </c>
+      <c r="C189" t="n">
+        <v>413</v>
+      </c>
+      <c r="D189" t="n">
+        <v>80.23709110490057</v>
+      </c>
+      <c r="E189" t="n">
+        <v>467.19</v>
+      </c>
+      <c r="F189" t="n">
+        <v>157.6480493450991</v>
+      </c>
+      <c r="G189" t="n">
+        <v>56498.47235689612</v>
+      </c>
+      <c r="H189" t="n">
+        <v>-8741.236739706075</v>
+      </c>
+      <c r="I189" t="n">
+        <v>5.615</v>
+      </c>
+      <c r="J189" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="K189" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L189" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M189" t="n">
+        <v>300.0319778451221</v>
+      </c>
+      <c r="N189" t="n">
+        <v>5.481361532008621</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>413</v>
+      </c>
+      <c r="B190" t="n">
         <v>189</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C190" t="n">
         <v>413</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D190" t="n">
         <v>79.92327980471686</v>
       </c>
-      <c r="E180" t="n">
+      <c r="E190" t="n">
         <v>471.5</v>
       </c>
-      <c r="F180" t="n">
+      <c r="F190" t="n">
         <v>156.2069823404812</v>
       </c>
-      <c r="G180" t="n">
+      <c r="G190" t="n">
         <v>57162.52314702258</v>
       </c>
-      <c r="H180" t="n">
+      <c r="H190" t="n">
         <v>-8623.240824451565</v>
       </c>
-      <c r="I180" t="n">
+      <c r="I190" t="n">
         <v>5.745</v>
       </c>
-      <c r="J180" t="n">
+      <c r="J190" t="n">
         <v>15.445</v>
       </c>
-      <c r="K180" t="n">
+      <c r="K190" t="n">
         <v>2.56</v>
       </c>
-      <c r="L180" t="n">
+      <c r="L190" t="n">
         <v>3.74</v>
       </c>
-      <c r="M180" t="n">
+      <c r="M190" t="n">
         <v>300.0319766099359</v>
       </c>
-      <c r="N180" t="n">
+      <c r="N190" t="n">
         <v>5.498287282739448</v>
       </c>
     </row>
